--- a/Contributions_table.xlsx
+++ b/Contributions_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lc/Library/CloudStorage/Box-Box/backup/Fusionmisc/Job/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01AEC0DB-57F0-5342-B4BD-939AC2B095C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{507F0DAA-6A2A-7845-94AA-8B1907E8B8A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="19920" xr2:uid="{5AA491FB-7947-2140-ACD9-201A623594D0}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="319">
   <si>
     <t xml:space="preserve">EMNLP (under review) </t>
   </si>
@@ -1059,6 +1059,12 @@
   </si>
   <si>
     <t>singh2024global</t>
+  </si>
+  <si>
+    <t>ICLR</t>
+  </si>
+  <si>
+    <t>ArXiv</t>
   </si>
 </sst>
 </file>
@@ -17078,7 +17084,7 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>271</v>
+        <v>318</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>272</v>
@@ -17144,7 +17150,7 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>271</v>
+        <v>317</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>290</v>
@@ -17436,7 +17442,7 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>271</v>
+        <v>317</v>
       </c>
       <c r="C75" s="5" t="s">
         <v>301</v>
@@ -22862,7 +22868,7 @@
       </c>
       <c r="B68" t="str">
         <f>Sheet1!B70</f>
-        <v>ICLR (under review)</v>
+        <v>ArXiv</v>
       </c>
       <c r="C68" t="str">
         <f>Sheet1!C70</f>
@@ -27913,7 +27919,7 @@
       </c>
       <c r="B68" t="str">
         <f>Sheet1!B70</f>
-        <v>ICLR (under review)</v>
+        <v>ArXiv</v>
       </c>
       <c r="C68" t="str">
         <f>Sheet1!C70</f>

--- a/Contributions_table.xlsx
+++ b/Contributions_table.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lc/PycharmProjects/publications/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46A956C6-95D9-6B41-81F2-13B269F931CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77F21575-6670-ED40-ADF6-0A7E47834D2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="860" windowWidth="34560" windowHeight="19920" xr2:uid="{5AA491FB-7947-2140-ACD9-201A623594D0}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{5AA491FB-7947-2140-ACD9-201A623594D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -63,14 +63,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="369">
   <si>
     <t xml:space="preserve">EMNLP (under review) </t>
   </si>
   <si>
-    <t xml:space="preserve">ARR^ (under review) </t>
-  </si>
-  <si>
     <t xml:space="preserve">ARR (under review) </t>
   </si>
   <si>
@@ -78,9 +75,6 @@
   </si>
   <si>
     <t>inspired framework for evaluating basic world knowledge in language models” 5th from end, numerous authors.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMLR (under review) </t>
   </si>
   <si>
     <t xml:space="preserve">ACL 2024 </t>
@@ -688,20 +682,6 @@
     <t>The Future of Open Human Feedback</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Nature Machine Intelligence^ (under review) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Many authors, led by me.</t>
   </si>
   <si>
@@ -904,9 +884,6 @@
   </si>
   <si>
     <t>zhang2024unforgettable</t>
-  </si>
-  <si>
-    <t>ICLR (under review)</t>
   </si>
   <si>
     <t>Compeft: Compression for communicating parameter efficient updates via sparsification and quantization</t>
@@ -1169,9 +1146,6 @@
     <t>Zipnn: Lossless compression for ai models</t>
   </si>
   <si>
-    <t>IEEE</t>
-  </si>
-  <si>
     <t>JML</t>
   </si>
   <si>
@@ -1185,6 +1159,84 @@
   </si>
   <si>
     <t>Beyond binary rewards: Training lms to reason about their uncertainty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nature Machine Intelligence^ </t>
+  </si>
+  <si>
+    <t>ArXiv</t>
+  </si>
+  <si>
+    <t>CLOUD (IEEE)</t>
+  </si>
+  <si>
+    <t>ashurytahan2025mightytorrbenchmarktable</t>
+  </si>
+  <si>
+    <t>EACL</t>
+  </si>
+  <si>
+    <t>damani2026beyond</t>
+  </si>
+  <si>
+    <t>vetzler2025crisp</t>
+  </si>
+  <si>
+    <t>BabyBabelLM: A Multilingual Benchmark of Developmentally Plausible Training Data</t>
+  </si>
+  <si>
+    <t>Need to update bib when anthology has it (currently manual</t>
+  </si>
+  <si>
+    <t>Global piqa: Evaluating physical commonsense reasoning across 100+ languages and cultures</t>
+  </si>
+  <si>
+    <t>chang2025globalpiqaevaluatingphysical</t>
+  </si>
+  <si>
+    <t>jumelet2025babybabellm</t>
+  </si>
+  <si>
+    <t>Findings of the Third BabyLM Challenge: Accelerating Language Modeling Research with Cognitively Plausible Data</t>
+  </si>
+  <si>
+    <t>charpentier-etal-2025-findings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMLR </t>
+  </si>
+  <si>
+    <t>A Latent Variable Framework for Scaling Laws in Large Language Models</t>
+  </si>
+  <si>
+    <t>suarez2026commonlid</t>
+  </si>
+  <si>
+    <t>CommonLID: Re-evaluating State-of-the-Art Language Identification Performance on Web Data</t>
+  </si>
+  <si>
+    <t>Will it Merge? On The Causes of Model Mergeability</t>
+  </si>
+  <si>
+    <t>rahamim2026will</t>
+  </si>
+  <si>
+    <t>ErrorMap and ErrorAtlas: Charting the Failure Landscape of Large Language Models</t>
+  </si>
+  <si>
+    <t>Robustness as an Emergent Property of Task Performance</t>
+  </si>
+  <si>
+    <t>ashury2026robustness</t>
+  </si>
+  <si>
+    <t>ashury2026errormap</t>
+  </si>
+  <si>
+    <t>tam2024llm</t>
+  </si>
+  <si>
+    <t>BabyLM</t>
   </si>
 </sst>
 </file>
@@ -12198,115 +12250,115 @@
   <sheetData>
     <row r="1" spans="1:37">
       <c r="A1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B1" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="C1" t="s">
+        <v>289</v>
+      </c>
+      <c r="D1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F1" t="s">
+        <v>132</v>
+      </c>
+      <c r="G1" t="s">
+        <v>130</v>
+      </c>
+      <c r="H1" t="s">
+        <v>259</v>
+      </c>
+      <c r="I1" t="s">
+        <v>288</v>
+      </c>
+      <c r="J1" t="s">
+        <v>287</v>
+      </c>
+      <c r="K1" t="s">
+        <v>284</v>
+      </c>
+      <c r="L1" t="s">
+        <v>283</v>
+      </c>
+      <c r="M1" t="s">
+        <v>286</v>
+      </c>
+      <c r="N1" t="s">
+        <v>285</v>
+      </c>
+      <c r="O1" t="s">
+        <v>261</v>
+      </c>
+      <c r="P1" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>260</v>
+      </c>
+      <c r="R1" t="s">
+        <v>156</v>
+      </c>
+      <c r="S1" t="s">
+        <v>171</v>
+      </c>
+      <c r="T1" t="s">
+        <v>157</v>
+      </c>
+      <c r="U1" t="s">
+        <v>158</v>
+      </c>
+      <c r="V1" t="s">
+        <v>262</v>
+      </c>
+      <c r="W1" t="s">
+        <v>159</v>
+      </c>
+      <c r="X1" t="s">
+        <v>160</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>258</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>164</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>161</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>294</v>
+      </c>
+      <c r="AC1" t="s">
         <v>293</v>
       </c>
-      <c r="D1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="AD1" t="s">
+        <v>181</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>257</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>248</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>248</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>249</v>
+      </c>
+      <c r="AI1" t="s">
         <v>250</v>
       </c>
-      <c r="F1" t="s">
-        <v>134</v>
-      </c>
-      <c r="G1" t="s">
-        <v>132</v>
-      </c>
-      <c r="H1" t="s">
-        <v>263</v>
-      </c>
-      <c r="I1" t="s">
-        <v>292</v>
-      </c>
-      <c r="J1" t="s">
-        <v>291</v>
-      </c>
-      <c r="K1" t="s">
-        <v>288</v>
-      </c>
-      <c r="L1" t="s">
-        <v>287</v>
-      </c>
-      <c r="M1" t="s">
+      <c r="AJ1" t="s">
+        <v>257</v>
+      </c>
+      <c r="AK1" t="s">
         <v>290</v>
-      </c>
-      <c r="N1" t="s">
-        <v>289</v>
-      </c>
-      <c r="O1" t="s">
-        <v>265</v>
-      </c>
-      <c r="P1" t="s">
-        <v>267</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>264</v>
-      </c>
-      <c r="R1" t="s">
-        <v>158</v>
-      </c>
-      <c r="S1" t="s">
-        <v>173</v>
-      </c>
-      <c r="T1" t="s">
-        <v>159</v>
-      </c>
-      <c r="U1" t="s">
-        <v>160</v>
-      </c>
-      <c r="V1" t="s">
-        <v>266</v>
-      </c>
-      <c r="W1" t="s">
-        <v>161</v>
-      </c>
-      <c r="X1" t="s">
-        <v>162</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>262</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>166</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>163</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>298</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>297</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>183</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>261</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>251</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>251</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>252</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>253</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>261</v>
-      </c>
-      <c r="AK1" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="2" spans="1:37">
@@ -12314,20 +12366,20 @@
         <v>1</v>
       </c>
       <c r="B2" t="str" cm="1">
-        <f t="array" ref="B2">_xlfn.IFS(ISBLANK(D2),"",ISBLANK(C2),"no venue",ISBLANK(E2),"no bib",ISNUMBER(SEARCH("xiv", C2)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B2">_xlfn.IFS(ISBLANK(D2),"",ISBLANK(C2),"no venue",ISBLANK(E2),"no bib",ISNUMBER(SEARCH("xiv", C2)),"arxiv",SUM(I2:AA2)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C2" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="F2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G2">
         <v>2018</v>
@@ -12379,20 +12431,20 @@
         <v>2</v>
       </c>
       <c r="B3" t="str" cm="1">
-        <f t="array" ref="B3">_xlfn.IFS(ISBLANK(D3),"",ISBLANK(C3),"no venue",ISBLANK(E3),"no bib",ISNUMBER(SEARCH("xiv", C3)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B3">_xlfn.IFS(ISBLANK(D3),"",ISBLANK(C3),"no venue",ISBLANK(E3),"no bib",ISNUMBER(SEARCH("xiv", C3)),"arxiv",SUM(I3:AA3)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C3" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E3" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="F3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G3">
         <v>2018</v>
@@ -12454,20 +12506,20 @@
         <v>3</v>
       </c>
       <c r="B4" t="str" cm="1">
-        <f t="array" ref="B4">_xlfn.IFS(ISBLANK(D4),"",ISBLANK(C4),"no venue",ISBLANK(E4),"no bib",ISNUMBER(SEARCH("xiv", C4)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B4">_xlfn.IFS(ISBLANK(D4),"",ISBLANK(C4),"no venue",ISBLANK(E4),"no bib",ISNUMBER(SEARCH("xiv", C4)),"arxiv",SUM(I4:AA4)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C4" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E4" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G4">
         <v>2018</v>
@@ -12527,20 +12579,20 @@
         <v>4</v>
       </c>
       <c r="B5" t="str" cm="1">
-        <f t="array" ref="B5">_xlfn.IFS(ISBLANK(D5),"",ISBLANK(C5),"no venue",ISBLANK(E5),"no bib",ISNUMBER(SEARCH("xiv", C5)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B5">_xlfn.IFS(ISBLANK(D5),"",ISBLANK(C5),"no venue",ISBLANK(E5),"no bib",ISNUMBER(SEARCH("xiv", C5)),"arxiv",SUM(I5:AA5)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C5" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E5" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="F5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G5">
         <v>2018</v>
@@ -12614,20 +12666,20 @@
         <v>5</v>
       </c>
       <c r="B6" t="str" cm="1">
-        <f t="array" ref="B6">_xlfn.IFS(ISBLANK(D6),"",ISBLANK(C6),"no venue",ISBLANK(E6),"no bib",ISNUMBER(SEARCH("xiv", C6)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B6">_xlfn.IFS(ISBLANK(D6),"",ISBLANK(C6),"no venue",ISBLANK(E6),"no bib",ISNUMBER(SEARCH("xiv", C6)),"arxiv",SUM(I6:AA6)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C6" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E6" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="F6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G6">
         <v>2018</v>
@@ -12689,20 +12741,20 @@
         <v>6</v>
       </c>
       <c r="B7" t="str" cm="1">
-        <f t="array" ref="B7">_xlfn.IFS(ISBLANK(D7),"",ISBLANK(C7),"no venue",ISBLANK(E7),"no bib",ISNUMBER(SEARCH("xiv", C7)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B7">_xlfn.IFS(ISBLANK(D7),"",ISBLANK(C7),"no venue",ISBLANK(E7),"no bib",ISNUMBER(SEARCH("xiv", C7)),"arxiv",SUM(I7:AA7)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C7" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E7" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="F7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G7">
         <v>2019</v>
@@ -12779,20 +12831,20 @@
         <v>7</v>
       </c>
       <c r="B8" t="str" cm="1">
-        <f t="array" ref="B8">_xlfn.IFS(ISBLANK(D8),"",ISBLANK(C8),"no venue",ISBLANK(E8),"no bib",ISNUMBER(SEARCH("xiv", C8)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B8">_xlfn.IFS(ISBLANK(D8),"",ISBLANK(C8),"no venue",ISBLANK(E8),"no bib",ISNUMBER(SEARCH("xiv", C8)),"arxiv",SUM(I8:AA8)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C8" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E8" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F8" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G8">
         <v>2019</v>
@@ -12849,20 +12901,20 @@
         <v>8</v>
       </c>
       <c r="B9" t="str" cm="1">
-        <f t="array" ref="B9">_xlfn.IFS(ISBLANK(D9),"",ISBLANK(C9),"no venue",ISBLANK(E9),"no bib",ISNUMBER(SEARCH("xiv", C9)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B9">_xlfn.IFS(ISBLANK(D9),"",ISBLANK(C9),"no venue",ISBLANK(E9),"no bib",ISNUMBER(SEARCH("xiv", C9)),"arxiv",SUM(I9:AA9)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C9" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E9" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F9" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G9">
         <v>2019</v>
@@ -12924,20 +12976,20 @@
         <v>9</v>
       </c>
       <c r="B10" t="str" cm="1">
-        <f t="array" ref="B10">_xlfn.IFS(ISBLANK(D10),"",ISBLANK(C10),"no venue",ISBLANK(E10),"no bib",ISNUMBER(SEARCH("xiv", C10)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B10">_xlfn.IFS(ISBLANK(D10),"",ISBLANK(C10),"no venue",ISBLANK(E10),"no bib",ISNUMBER(SEARCH("xiv", C10)),"arxiv",SUM(I10:AA10)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C10" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E10" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F10" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G10">
         <v>2019</v>
@@ -13012,20 +13064,20 @@
         <v>10</v>
       </c>
       <c r="B11" t="str" cm="1">
-        <f t="array" ref="B11">_xlfn.IFS(ISBLANK(D11),"",ISBLANK(C11),"no venue",ISBLANK(E11),"no bib",ISNUMBER(SEARCH("xiv", C11)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B11">_xlfn.IFS(ISBLANK(D11),"",ISBLANK(C11),"no venue",ISBLANK(E11),"no bib",ISNUMBER(SEARCH("xiv", C11)),"arxiv",SUM(I11:AA11)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C11" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D11" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E11" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="F11" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G11">
         <v>2019</v>
@@ -13102,20 +13154,20 @@
         <v>11</v>
       </c>
       <c r="B12" t="str" cm="1">
-        <f t="array" ref="B12">_xlfn.IFS(ISBLANK(D12),"",ISBLANK(C12),"no venue",ISBLANK(E12),"no bib",ISNUMBER(SEARCH("xiv", C12)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B12">_xlfn.IFS(ISBLANK(D12),"",ISBLANK(C12),"no venue",ISBLANK(E12),"no bib",ISNUMBER(SEARCH("xiv", C12)),"arxiv",SUM(I12:AA12)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C12" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E12" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="F12" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G12">
         <v>2020</v>
@@ -13181,20 +13233,20 @@
         <v>12</v>
       </c>
       <c r="B13" t="str" cm="1">
-        <f t="array" ref="B13">_xlfn.IFS(ISBLANK(D13),"",ISBLANK(C13),"no venue",ISBLANK(E13),"no bib",ISNUMBER(SEARCH("xiv", C13)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B13">_xlfn.IFS(ISBLANK(D13),"",ISBLANK(C13),"no venue",ISBLANK(E13),"no bib",ISNUMBER(SEARCH("xiv", C13)),"arxiv",SUM(I13:AA13)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C13" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D13" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E13" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F13" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G13">
         <v>2020</v>
@@ -13258,20 +13310,20 @@
         <v>13</v>
       </c>
       <c r="B14" t="str" cm="1">
-        <f t="array" ref="B14">_xlfn.IFS(ISBLANK(D14),"",ISBLANK(C14),"no venue",ISBLANK(E14),"no bib",ISNUMBER(SEARCH("xiv", C14)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B14">_xlfn.IFS(ISBLANK(D14),"",ISBLANK(C14),"no venue",ISBLANK(E14),"no bib",ISNUMBER(SEARCH("xiv", C14)),"arxiv",SUM(I14:AA14)&lt;2,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C14" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D14" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E14" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F14" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G14">
         <v>2020</v>
@@ -13324,20 +13376,20 @@
         <v>14</v>
       </c>
       <c r="B15" t="str" cm="1">
-        <f t="array" ref="B15">_xlfn.IFS(ISBLANK(D15),"",ISBLANK(C15),"no venue",ISBLANK(E15),"no bib",ISNUMBER(SEARCH("xiv", C15)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B15">_xlfn.IFS(ISBLANK(D15),"",ISBLANK(C15),"no venue",ISBLANK(E15),"no bib",ISNUMBER(SEARCH("xiv", C15)),"arxiv",SUM(I15:AA15)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C15" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D15" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E15" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="F15" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G15">
         <v>2020</v>
@@ -13401,20 +13453,20 @@
         <v>15</v>
       </c>
       <c r="B16" t="str" cm="1">
-        <f t="array" ref="B16">_xlfn.IFS(ISBLANK(D16),"",ISBLANK(C16),"no venue",ISBLANK(E16),"no bib",ISNUMBER(SEARCH("xiv", C16)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B16">_xlfn.IFS(ISBLANK(D16),"",ISBLANK(C16),"no venue",ISBLANK(E16),"no bib",ISNUMBER(SEARCH("xiv", C16)),"arxiv",SUM(I16:AA16)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C16" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D16" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E16" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F16" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G16">
         <v>2020</v>
@@ -13487,20 +13539,20 @@
         <v>16</v>
       </c>
       <c r="B17" t="str" cm="1">
-        <f t="array" ref="B17">_xlfn.IFS(ISBLANK(D17),"",ISBLANK(C17),"no venue",ISBLANK(E17),"no bib",ISNUMBER(SEARCH("xiv", C17)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B17">_xlfn.IFS(ISBLANK(D17),"",ISBLANK(C17),"no venue",ISBLANK(E17),"no bib",ISNUMBER(SEARCH("xiv", C17)),"arxiv",SUM(I17:AA17)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C17" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D17" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E17" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F17" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G17">
         <v>2020</v>
@@ -13565,20 +13617,20 @@
         <v>17</v>
       </c>
       <c r="B18" t="str" cm="1">
-        <f t="array" ref="B18">_xlfn.IFS(ISBLANK(D18),"",ISBLANK(C18),"no venue",ISBLANK(E18),"no bib",ISNUMBER(SEARCH("xiv", C18)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B18">_xlfn.IFS(ISBLANK(D18),"",ISBLANK(C18),"no venue",ISBLANK(E18),"no bib",ISNUMBER(SEARCH("xiv", C18)),"arxiv",SUM(I18:AA18)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C18" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D18" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E18" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F18" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G18" s="4">
         <v>2021</v>
@@ -13644,20 +13696,20 @@
         <v>18</v>
       </c>
       <c r="B19" t="str" cm="1">
-        <f t="array" ref="B19">_xlfn.IFS(ISBLANK(D19),"",ISBLANK(C19),"no venue",ISBLANK(E19),"no bib",ISNUMBER(SEARCH("xiv", C19)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B19">_xlfn.IFS(ISBLANK(D19),"",ISBLANK(C19),"no venue",ISBLANK(E19),"no bib",ISNUMBER(SEARCH("xiv", C19)),"arxiv",SUM(I19:AA19)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C19" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D19" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E19" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F19" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G19" s="4">
         <v>2021</v>
@@ -13716,16 +13768,16 @@
         <v>19</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D20" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E20" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="F20" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G20" s="4">
         <v>2021</v>
@@ -13796,16 +13848,16 @@
         <v>20</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D21" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E21" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G21" s="4">
         <v>2021</v>
@@ -13867,16 +13919,16 @@
         <v>21</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D22" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E22" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F22" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G22">
         <v>2022</v>
@@ -13932,16 +13984,16 @@
         <v>22</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D23" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E23" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F23" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G23">
         <v>2022</v>
@@ -14000,16 +14052,16 @@
         <v>23</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D24" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E24" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="F24" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G24">
         <v>2022</v>
@@ -14078,16 +14130,16 @@
         <v>24</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D25" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E25" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G25">
         <v>2022</v>
@@ -14158,16 +14210,16 @@
         <v>25</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D26" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E26" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F26" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G26">
         <v>2023</v>
@@ -14234,16 +14286,16 @@
         <v>26</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D27" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E27" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="F27" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G27">
         <v>2023</v>
@@ -14317,20 +14369,20 @@
         <v>27</v>
       </c>
       <c r="B28" t="str" cm="1">
-        <f t="array" ref="B28">_xlfn.IFS(ISBLANK(D28),"",ISBLANK(C28),"no venue",ISBLANK(E28),"no bib",ISNUMBER(SEARCH("xiv", C28)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B28">_xlfn.IFS(ISBLANK(D28),"",ISBLANK(C28),"no venue",ISBLANK(E28),"no bib",ISNUMBER(SEARCH("xiv", C28)),"arxiv",SUM(I28:AA28)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C28" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D28" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E28" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="F28" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G28">
         <v>2023</v>
@@ -14388,20 +14440,20 @@
         <v>28</v>
       </c>
       <c r="B29" t="str" cm="1">
-        <f t="array" ref="B29">_xlfn.IFS(ISBLANK(D29),"",ISBLANK(C29),"no venue",ISBLANK(E29),"no bib",ISNUMBER(SEARCH("xiv", C29)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B29">_xlfn.IFS(ISBLANK(D29),"",ISBLANK(C29),"no venue",ISBLANK(E29),"no bib",ISNUMBER(SEARCH("xiv", C29)),"arxiv",SUM(I29:AA29)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C29" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D29" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E29" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F29" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G29">
         <v>2023</v>
@@ -14457,20 +14509,20 @@
         <v>29</v>
       </c>
       <c r="B30" t="str" cm="1">
-        <f t="array" ref="B30">_xlfn.IFS(ISBLANK(D30),"",ISBLANK(C30),"no venue",ISBLANK(E30),"no bib",ISNUMBER(SEARCH("xiv", C30)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B30">_xlfn.IFS(ISBLANK(D30),"",ISBLANK(C30),"no venue",ISBLANK(E30),"no bib",ISNUMBER(SEARCH("xiv", C30)),"arxiv",SUM(I30:AA30)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C30" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D30" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E30" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F30" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G30">
         <v>2023</v>
@@ -14540,20 +14592,20 @@
         <v>30</v>
       </c>
       <c r="B31" t="str" cm="1">
-        <f t="array" ref="B31">_xlfn.IFS(ISBLANK(D31),"",ISBLANK(C31),"no venue",ISBLANK(E31),"no bib",ISNUMBER(SEARCH("xiv", C31)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B31">_xlfn.IFS(ISBLANK(D31),"",ISBLANK(C31),"no venue",ISBLANK(E31),"no bib",ISNUMBER(SEARCH("xiv", C31)),"arxiv",SUM(I31:AA31)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C31" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D31" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F31" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G31">
         <v>2023</v>
@@ -14611,20 +14663,20 @@
         <v>31</v>
       </c>
       <c r="B32" t="str" cm="1">
-        <f t="array" ref="B32">_xlfn.IFS(ISBLANK(D32),"",ISBLANK(C32),"no venue",ISBLANK(E32),"no bib",ISNUMBER(SEARCH("xiv", C32)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B32">_xlfn.IFS(ISBLANK(D32),"",ISBLANK(C32),"no venue",ISBLANK(E32),"no bib",ISNUMBER(SEARCH("xiv", C32)),"arxiv",SUM(I32:AA32)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C32" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="F32" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G32">
         <v>2023</v>
@@ -14691,20 +14743,20 @@
         <v>32</v>
       </c>
       <c r="B33" t="str" cm="1">
-        <f t="array" ref="B33">_xlfn.IFS(ISBLANK(D33),"",ISBLANK(C33),"no venue",ISBLANK(E33),"no bib",ISNUMBER(SEARCH("xiv", C33)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B33">_xlfn.IFS(ISBLANK(D33),"",ISBLANK(C33),"no venue",ISBLANK(E33),"no bib",ISNUMBER(SEARCH("xiv", C33)),"arxiv",SUM(I33:AA33)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C33" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D33" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E33" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F33" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G33">
         <v>2023</v>
@@ -14760,20 +14812,20 @@
         <v>33</v>
       </c>
       <c r="B34" t="str" cm="1">
-        <f t="array" ref="B34">_xlfn.IFS(ISBLANK(D34),"",ISBLANK(C34),"no venue",ISBLANK(E34),"no bib",ISNUMBER(SEARCH("xiv", C34)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B34">_xlfn.IFS(ISBLANK(D34),"",ISBLANK(C34),"no venue",ISBLANK(E34),"no bib",ISNUMBER(SEARCH("xiv", C34)),"arxiv",SUM(I34:AA34)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C34" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D34" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E34" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F34" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G34">
         <v>2023</v>
@@ -14831,20 +14883,20 @@
         <v>34</v>
       </c>
       <c r="B35" t="str" cm="1">
-        <f t="array" ref="B35">_xlfn.IFS(ISBLANK(D35),"",ISBLANK(C35),"no venue",ISBLANK(E35),"no bib",ISNUMBER(SEARCH("xiv", C35)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B35">_xlfn.IFS(ISBLANK(D35),"",ISBLANK(C35),"no venue",ISBLANK(E35),"no bib",ISNUMBER(SEARCH("xiv", C35)),"arxiv",SUM(I35:AA35)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C35" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D35" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E35" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F35" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G35">
         <v>2023</v>
@@ -14902,20 +14954,20 @@
         <v>35</v>
       </c>
       <c r="B36" t="str" cm="1">
-        <f t="array" ref="B36">_xlfn.IFS(ISBLANK(D36),"",ISBLANK(C36),"no venue",ISBLANK(E36),"no bib",ISNUMBER(SEARCH("xiv", C36)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B36">_xlfn.IFS(ISBLANK(D36),"",ISBLANK(C36),"no venue",ISBLANK(E36),"no bib",ISNUMBER(SEARCH("xiv", C36)),"arxiv",SUM(I36:AA36)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C36" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D36" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E36" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F36" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G36">
         <v>2023</v>
@@ -14981,20 +15033,20 @@
         <v>36</v>
       </c>
       <c r="B37" t="str" cm="1">
-        <f t="array" ref="B37">_xlfn.IFS(ISBLANK(D37),"",ISBLANK(C37),"no venue",ISBLANK(E37),"no bib",ISNUMBER(SEARCH("xiv", C37)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B37">_xlfn.IFS(ISBLANK(D37),"",ISBLANK(C37),"no venue",ISBLANK(E37),"no bib",ISNUMBER(SEARCH("xiv", C37)),"arxiv",SUM(I37:AA37)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C37" s="1" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="D37" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="E37" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="F37" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="G37">
         <v>2023</v>
@@ -15075,20 +15127,20 @@
         <v>37</v>
       </c>
       <c r="B38" t="str" cm="1">
-        <f t="array" ref="B38">_xlfn.IFS(ISBLANK(D38),"",ISBLANK(C38),"no venue",ISBLANK(E38),"no bib",ISNUMBER(SEARCH("xiv", C38)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B38">_xlfn.IFS(ISBLANK(D38),"",ISBLANK(C38),"no venue",ISBLANK(E38),"no bib",ISNUMBER(SEARCH("xiv", C38)),"arxiv",SUM(I38:AA38)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C38" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D38" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E38" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F38" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G38">
         <v>2023</v>
@@ -15166,20 +15218,20 @@
         <v>38</v>
       </c>
       <c r="B39" t="str" cm="1">
-        <f t="array" ref="B39">_xlfn.IFS(ISBLANK(D39),"",ISBLANK(C39),"no venue",ISBLANK(E39),"no bib",ISNUMBER(SEARCH("xiv", C39)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B39">_xlfn.IFS(ISBLANK(D39),"",ISBLANK(C39),"no venue",ISBLANK(E39),"no bib",ISNUMBER(SEARCH("xiv", C39)),"arxiv",SUM(I39:AA39)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C39" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D39" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E39" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F39" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G39">
         <v>2023</v>
@@ -15231,20 +15283,20 @@
         <v>39</v>
       </c>
       <c r="B40" t="str" cm="1">
-        <f t="array" ref="B40">_xlfn.IFS(ISBLANK(D40),"",ISBLANK(C40),"no venue",ISBLANK(E40),"no bib",ISNUMBER(SEARCH("xiv", C40)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B40">_xlfn.IFS(ISBLANK(D40),"",ISBLANK(C40),"no venue",ISBLANK(E40),"no bib",ISNUMBER(SEARCH("xiv", C40)),"arxiv",SUM(I40:AA40)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C40" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D40" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E40" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F40" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G40">
         <v>2023</v>
@@ -15306,20 +15358,20 @@
         <v>40</v>
       </c>
       <c r="B41" t="str" cm="1">
-        <f t="array" ref="B41">_xlfn.IFS(ISBLANK(D41),"",ISBLANK(C41),"no venue",ISBLANK(E41),"no bib",ISNUMBER(SEARCH("xiv", C41)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B41">_xlfn.IFS(ISBLANK(D41),"",ISBLANK(C41),"no venue",ISBLANK(E41),"no bib",ISNUMBER(SEARCH("xiv", C41)),"arxiv",SUM(I41:AA41)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C41" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D41" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E41" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F41" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G41">
         <v>2023</v>
@@ -15384,20 +15436,20 @@
         <v>41</v>
       </c>
       <c r="B42" t="str" cm="1">
-        <f t="array" ref="B42">_xlfn.IFS(ISBLANK(D42),"",ISBLANK(C42),"no venue",ISBLANK(E42),"no bib",ISNUMBER(SEARCH("xiv", C42)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B42">_xlfn.IFS(ISBLANK(D42),"",ISBLANK(C42),"no venue",ISBLANK(E42),"no bib",ISNUMBER(SEARCH("xiv", C42)),"arxiv",SUM(I42:AA42)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C42" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D42" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E42" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F42" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G42">
         <v>2023</v>
@@ -15458,20 +15510,20 @@
         <v>42</v>
       </c>
       <c r="B43" t="str" cm="1">
-        <f t="array" ref="B43">_xlfn.IFS(ISBLANK(D43),"",ISBLANK(C43),"no venue",ISBLANK(E43),"no bib",ISNUMBER(SEARCH("xiv", C43)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B43">_xlfn.IFS(ISBLANK(D43),"",ISBLANK(C43),"no venue",ISBLANK(E43),"no bib",ISNUMBER(SEARCH("xiv", C43)),"arxiv",SUM(I43:AA43)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C43" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D43" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E43" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F43" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G43">
         <v>2024</v>
@@ -15545,20 +15597,20 @@
         <v>43</v>
       </c>
       <c r="B44" t="str" cm="1">
-        <f t="array" ref="B44">_xlfn.IFS(ISBLANK(D44),"",ISBLANK(C44),"no venue",ISBLANK(E44),"no bib",ISNUMBER(SEARCH("xiv", C44)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B44">_xlfn.IFS(ISBLANK(D44),"",ISBLANK(C44),"no venue",ISBLANK(E44),"no bib",ISNUMBER(SEARCH("xiv", C44)),"arxiv",SUM(I44:AA44)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C44" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D44" t="s">
+        <v>177</v>
+      </c>
+      <c r="E44" t="s">
+        <v>195</v>
+      </c>
+      <c r="F44" t="s">
         <v>178</v>
-      </c>
-      <c r="D44" t="s">
-        <v>179</v>
-      </c>
-      <c r="E44" t="s">
-        <v>198</v>
-      </c>
-      <c r="F44" t="s">
-        <v>180</v>
       </c>
       <c r="G44">
         <v>2024</v>
@@ -15617,20 +15669,20 @@
         <v>44</v>
       </c>
       <c r="B45" t="str" cm="1">
-        <f t="array" ref="B45">_xlfn.IFS(ISBLANK(D45),"",ISBLANK(C45),"no venue",ISBLANK(E45),"no bib",ISNUMBER(SEARCH("xiv", C45)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B45">_xlfn.IFS(ISBLANK(D45),"",ISBLANK(C45),"no venue",ISBLANK(E45),"no bib",ISNUMBER(SEARCH("xiv", C45)),"arxiv",SUM(I45:AA45)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C45" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D45" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="E45" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="F45" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="G45">
         <v>2024</v>
@@ -15695,20 +15747,20 @@
         <v>45</v>
       </c>
       <c r="B46" t="str" cm="1">
-        <f t="array" ref="B46">_xlfn.IFS(ISBLANK(D46),"",ISBLANK(C46),"no venue",ISBLANK(E46),"no bib",ISNUMBER(SEARCH("xiv", C46)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B46">_xlfn.IFS(ISBLANK(D46),"",ISBLANK(C46),"no venue",ISBLANK(E46),"no bib",ISNUMBER(SEARCH("xiv", C46)),"arxiv",SUM(I46:AA46)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C46" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D46" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="F46" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G46">
         <v>2024</v>
@@ -15770,20 +15822,20 @@
         <v>46</v>
       </c>
       <c r="B47" t="str" cm="1">
-        <f t="array" ref="B47">_xlfn.IFS(ISBLANK(D47),"",ISBLANK(C47),"no venue",ISBLANK(E47),"no bib",ISNUMBER(SEARCH("xiv", C47)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B47">_xlfn.IFS(ISBLANK(D47),"",ISBLANK(C47),"no venue",ISBLANK(E47),"no bib",ISNUMBER(SEARCH("xiv", C47)),"arxiv",SUM(I47:AA47)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C47" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D47" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E47" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F47" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G47">
         <v>2024</v>
@@ -15841,20 +15893,20 @@
         <v>47</v>
       </c>
       <c r="B48" t="str" cm="1">
-        <f t="array" ref="B48">_xlfn.IFS(ISBLANK(D48),"",ISBLANK(C48),"no venue",ISBLANK(E48),"no bib",ISNUMBER(SEARCH("xiv", C48)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B48">_xlfn.IFS(ISBLANK(D48),"",ISBLANK(C48),"no venue",ISBLANK(E48),"no bib",ISNUMBER(SEARCH("xiv", C48)),"arxiv",SUM(I48:AA48)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C48" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D48" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="E48" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="F48" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="G48">
         <v>2024</v>
@@ -15942,20 +15994,20 @@
         <v>48</v>
       </c>
       <c r="B49" t="str" cm="1">
-        <f t="array" ref="B49">_xlfn.IFS(ISBLANK(D49),"",ISBLANK(C49),"no venue",ISBLANK(E49),"no bib",ISNUMBER(SEARCH("xiv", C49)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B49">_xlfn.IFS(ISBLANK(D49),"",ISBLANK(C49),"no venue",ISBLANK(E49),"no bib",ISNUMBER(SEARCH("xiv", C49)),"arxiv",SUM(I49:AA49)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C49" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D49" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E49" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F49" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="G49">
         <v>2024</v>
@@ -16019,20 +16071,20 @@
         <v>49</v>
       </c>
       <c r="B50" t="str" cm="1">
-        <f t="array" ref="B50">_xlfn.IFS(ISBLANK(D50),"",ISBLANK(C50),"no venue",ISBLANK(E50),"no bib",ISNUMBER(SEARCH("xiv", C50)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B50">_xlfn.IFS(ISBLANK(D50),"",ISBLANK(C50),"no venue",ISBLANK(E50),"no bib",ISNUMBER(SEARCH("xiv", C50)),"arxiv",SUM(I50:AA50)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C50" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D50" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E50" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F50" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G50">
         <v>2024</v>
@@ -16093,20 +16145,20 @@
         <v>50</v>
       </c>
       <c r="B51" t="str" cm="1">
-        <f t="array" ref="B51">_xlfn.IFS(ISBLANK(D51),"",ISBLANK(C51),"no venue",ISBLANK(E51),"no bib",ISNUMBER(SEARCH("xiv", C51)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B51">_xlfn.IFS(ISBLANK(D51),"",ISBLANK(C51),"no venue",ISBLANK(E51),"no bib",ISNUMBER(SEARCH("xiv", C51)),"arxiv",SUM(I51:AA51)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C51" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D51" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E51" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F51" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G51">
         <v>2024</v>
@@ -16174,20 +16226,20 @@
         <v>51</v>
       </c>
       <c r="B52" t="str" cm="1">
-        <f t="array" ref="B52">_xlfn.IFS(ISBLANK(D52),"",ISBLANK(C52),"no venue",ISBLANK(E52),"no bib",ISNUMBER(SEARCH("xiv", C52)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B52">_xlfn.IFS(ISBLANK(D52),"",ISBLANK(C52),"no venue",ISBLANK(E52),"no bib",ISNUMBER(SEARCH("xiv", C52)),"arxiv",SUM(I52:AA52)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C52" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D52" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E52" s="14" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F52" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G52">
         <v>2024</v>
@@ -16261,20 +16313,20 @@
         <v>52</v>
       </c>
       <c r="B53" t="str" cm="1">
-        <f t="array" ref="B53">_xlfn.IFS(ISBLANK(D53),"",ISBLANK(C53),"no venue",ISBLANK(E53),"no bib",ISNUMBER(SEARCH("xiv", C53)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B53">_xlfn.IFS(ISBLANK(D53),"",ISBLANK(C53),"no venue",ISBLANK(E53),"no bib",ISNUMBER(SEARCH("xiv", C53)),"arxiv",SUM(I53:AA53)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C53" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D53" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E53" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="F53" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G53">
         <v>2024</v>
@@ -16342,20 +16394,20 @@
         <v>53</v>
       </c>
       <c r="B54" t="str" cm="1">
-        <f t="array" ref="B54">_xlfn.IFS(ISBLANK(D54),"",ISBLANK(C54),"no venue",ISBLANK(E54),"no bib",ISNUMBER(SEARCH("xiv", C54)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B54">_xlfn.IFS(ISBLANK(D54),"",ISBLANK(C54),"no venue",ISBLANK(E54),"no bib",ISNUMBER(SEARCH("xiv", C54)),"arxiv",SUM(I54:AA54)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C54" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D54" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E54" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F54" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G54">
         <v>2024</v>
@@ -16423,20 +16475,20 @@
         <v>54</v>
       </c>
       <c r="B55" t="str" cm="1">
-        <f t="array" ref="B55">_xlfn.IFS(ISBLANK(D55),"",ISBLANK(C55),"no venue",ISBLANK(E55),"no bib",ISNUMBER(SEARCH("xiv", C55)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B55">_xlfn.IFS(ISBLANK(D55),"",ISBLANK(C55),"no venue",ISBLANK(E55),"no bib",ISNUMBER(SEARCH("xiv", C55)),"arxiv",SUM(I55:AA55)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C55" s="2" t="s">
-        <v>5</v>
+        <v>357</v>
       </c>
       <c r="D55" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E55" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F55" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G55">
         <v>2024</v>
@@ -16500,20 +16552,20 @@
         <v>55</v>
       </c>
       <c r="B56" t="str" cm="1">
-        <f t="array" ref="B56">_xlfn.IFS(ISBLANK(D56),"",ISBLANK(C56),"no venue",ISBLANK(E56),"no bib",ISNUMBER(SEARCH("xiv", C56)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B56">_xlfn.IFS(ISBLANK(D56),"",ISBLANK(C56),"no venue",ISBLANK(E56),"no bib",ISNUMBER(SEARCH("xiv", C56)),"arxiv",SUM(I56:AA56)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C56" s="2" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="E56" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F56" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G56">
         <v>2024</v>
@@ -16581,20 +16633,20 @@
         <v>56</v>
       </c>
       <c r="B57" t="str" cm="1">
-        <f t="array" ref="B57">_xlfn.IFS(ISBLANK(D57),"",ISBLANK(C57),"no venue",ISBLANK(E57),"no bib",ISNUMBER(SEARCH("xiv", C57)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B57">_xlfn.IFS(ISBLANK(D57),"",ISBLANK(C57),"no venue",ISBLANK(E57),"no bib",ISNUMBER(SEARCH("xiv", C57)),"arxiv",SUM(I57:AA57)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C57" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D57" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E57" s="12" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="F57" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G57">
         <v>2024</v>
@@ -16659,20 +16711,20 @@
         <v>57</v>
       </c>
       <c r="B58" t="str" cm="1">
-        <f t="array" ref="B58">_xlfn.IFS(ISBLANK(D58),"",ISBLANK(C58),"no venue",ISBLANK(E58),"no bib",ISNUMBER(SEARCH("xiv", C58)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B58">_xlfn.IFS(ISBLANK(D58),"",ISBLANK(C58),"no venue",ISBLANK(E58),"no bib",ISNUMBER(SEARCH("xiv", C58)),"arxiv",SUM(I58:AA58)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C58" s="2" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D58" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E58" s="12" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="F58" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G58">
         <v>2024</v>
@@ -16727,20 +16779,20 @@
         <v>58</v>
       </c>
       <c r="B59" t="str" cm="1">
-        <f t="array" ref="B59">_xlfn.IFS(ISBLANK(D59),"",ISBLANK(C59),"no venue",ISBLANK(E59),"no bib",ISNUMBER(SEARCH("xiv", C59)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B59">_xlfn.IFS(ISBLANK(D59),"",ISBLANK(C59),"no venue",ISBLANK(E59),"no bib",ISNUMBER(SEARCH("xiv", C59)),"arxiv",SUM(I59:AA59)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C59" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D59" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E59" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F59" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G59">
         <v>2024</v>
@@ -16802,20 +16854,20 @@
         <v>59</v>
       </c>
       <c r="B60" t="str" cm="1">
-        <f t="array" ref="B60">_xlfn.IFS(ISBLANK(D60),"",ISBLANK(C60),"no venue",ISBLANK(E60),"no bib",ISNUMBER(SEARCH("xiv", C60)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B60">_xlfn.IFS(ISBLANK(D60),"",ISBLANK(C60),"no venue",ISBLANK(E60),"no bib",ISNUMBER(SEARCH("xiv", C60)),"arxiv",SUM(I60:AA60)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C60" s="2" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="D60" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E60" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="F60" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G60">
         <v>2024</v>
@@ -16871,20 +16923,20 @@
         <v>60</v>
       </c>
       <c r="B61" t="str" cm="1">
-        <f t="array" ref="B61">_xlfn.IFS(ISBLANK(D61),"",ISBLANK(C61),"no venue",ISBLANK(E61),"no bib",ISNUMBER(SEARCH("xiv", C61)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B61">_xlfn.IFS(ISBLANK(D61),"",ISBLANK(C61),"no venue",ISBLANK(E61),"no bib",ISNUMBER(SEARCH("xiv", C61)),"arxiv",SUM(I61:AA61)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C61" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D61" t="s">
+        <v>49</v>
+      </c>
+      <c r="E61" t="s">
+        <v>246</v>
+      </c>
+      <c r="F61" t="s">
         <v>2</v>
-      </c>
-      <c r="D61" t="s">
-        <v>51</v>
-      </c>
-      <c r="E61" t="s">
-        <v>249</v>
-      </c>
-      <c r="F61" t="s">
-        <v>3</v>
       </c>
       <c r="G61">
         <v>2024</v>
@@ -16940,20 +16992,20 @@
         <v>61</v>
       </c>
       <c r="B62" t="str" cm="1">
-        <f t="array" ref="B62">_xlfn.IFS(ISBLANK(D62),"",ISBLANK(C62),"no venue",ISBLANK(E62),"no bib",ISNUMBER(SEARCH("xiv", C62)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B62">_xlfn.IFS(ISBLANK(D62),"",ISBLANK(C62),"no venue",ISBLANK(E62),"no bib",ISNUMBER(SEARCH("xiv", C62)),"arxiv",SUM(I62:AA62)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C62" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D62" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="F62" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G62">
         <v>2024</v>
@@ -17026,20 +17078,20 @@
         <v>62</v>
       </c>
       <c r="B63" t="str" cm="1">
-        <f t="array" ref="B63">_xlfn.IFS(ISBLANK(D63),"",ISBLANK(C63),"no venue",ISBLANK(E63),"no bib",ISNUMBER(SEARCH("xiv", C63)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B63">_xlfn.IFS(ISBLANK(D63),"",ISBLANK(C63),"no venue",ISBLANK(E63),"no bib",ISNUMBER(SEARCH("xiv", C63)),"arxiv",SUM(I63:AA63)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C63" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D63" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E63" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F63" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G63">
         <v>2024</v>
@@ -17106,21 +17158,17 @@
         <f t="shared" si="6"/>
         <v>63</v>
       </c>
-      <c r="B64" t="str" cm="1">
-        <f t="array" ref="B64">_xlfn.IFS(ISBLANK(D64),"",ISBLANK(C64),"no venue",ISBLANK(E64),"no bib",ISNUMBER(SEARCH("xiv", C64)),"arxiv",TRUE,"")</f>
-        <v/>
-      </c>
       <c r="C64" s="2" t="s">
-        <v>1</v>
+        <v>344</v>
       </c>
       <c r="D64" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E64" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F64" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G64">
         <v>2024</v>
@@ -17182,20 +17230,20 @@
         <v>64</v>
       </c>
       <c r="B65" t="str" cm="1">
-        <f t="array" ref="B65">_xlfn.IFS(ISBLANK(D65),"",ISBLANK(C65),"no venue",ISBLANK(E65),"no bib",ISNUMBER(SEARCH("xiv", C65)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B65">_xlfn.IFS(ISBLANK(D65),"",ISBLANK(C65),"no venue",ISBLANK(E65),"no bib",ISNUMBER(SEARCH("xiv", C65)),"arxiv",SUM(I65:AA65)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C65" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D65" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="F65" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G65">
         <v>2024</v>
@@ -17260,20 +17308,20 @@
         <v>65</v>
       </c>
       <c r="B66" t="str" cm="1">
-        <f t="array" ref="B66">_xlfn.IFS(ISBLANK(D66),"",ISBLANK(C66),"no venue",ISBLANK(E66),"no bib",ISNUMBER(SEARCH("xiv", C66)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B66">_xlfn.IFS(ISBLANK(D66),"",ISBLANK(C66),"no venue",ISBLANK(E66),"no bib",ISNUMBER(SEARCH("xiv", C66)),"arxiv",SUM(I66:AA66)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C66" s="2" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="D66" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E66" s="12" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="F66" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G66">
         <v>2024</v>
@@ -17352,20 +17400,20 @@
         <v>66</v>
       </c>
       <c r="B67" t="str" cm="1">
-        <f t="array" ref="B67">_xlfn.IFS(ISBLANK(D67),"",ISBLANK(C67),"no venue",ISBLANK(E67),"no bib",ISNUMBER(SEARCH("xiv", C67)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B67">_xlfn.IFS(ISBLANK(D67),"",ISBLANK(C67),"no venue",ISBLANK(E67),"no bib",ISNUMBER(SEARCH("xiv", C67)),"arxiv",SUM(I67:AA67)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C67" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D67" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E67" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F67" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G67">
         <v>2024</v>
@@ -17432,20 +17480,20 @@
         <v>67</v>
       </c>
       <c r="B68" t="str" cm="1">
-        <f t="array" ref="B68">_xlfn.IFS(ISBLANK(D68),"",ISBLANK(C68),"no venue",ISBLANK(E68),"no bib",ISNUMBER(SEARCH("xiv", C68)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B68">_xlfn.IFS(ISBLANK(D68),"",ISBLANK(C68),"no venue",ISBLANK(E68),"no bib",ISNUMBER(SEARCH("xiv", C68)),"arxiv",SUM(I68:AA68)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C68" s="1" t="s">
-        <v>189</v>
+        <v>343</v>
       </c>
       <c r="D68" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="E68" t="s">
         <v>188</v>
       </c>
-      <c r="E68" t="s">
-        <v>191</v>
-      </c>
       <c r="F68" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="G68">
         <v>2024</v>
@@ -17506,20 +17554,20 @@
         <v>68</v>
       </c>
       <c r="B69" t="str" cm="1">
-        <f t="array" ref="B69">_xlfn.IFS(ISBLANK(D69),"",ISBLANK(C69),"no venue",ISBLANK(E69),"no bib",ISNUMBER(SEARCH("xiv", C69)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B69">_xlfn.IFS(ISBLANK(D69),"",ISBLANK(C69),"no venue",ISBLANK(E69),"no bib",ISNUMBER(SEARCH("xiv", C69)),"arxiv",SUM(I69:AA69)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C69" t="s">
+        <v>251</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="E69" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="D69" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>257</v>
-      </c>
       <c r="F69" s="10" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="G69">
         <v>2024</v>
@@ -17574,20 +17622,20 @@
         <v>69</v>
       </c>
       <c r="B70" t="str" cm="1">
-        <f t="array" ref="B70">_xlfn.IFS(ISBLANK(D70),"",ISBLANK(C70),"no venue",ISBLANK(E70),"no bib",ISNUMBER(SEARCH("xiv", C70)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B70">_xlfn.IFS(ISBLANK(D70),"",ISBLANK(C70),"no venue",ISBLANK(E70),"no bib",ISNUMBER(SEARCH("xiv", C70)),"arxiv",SUM(I70:AA70)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C70" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="E70" s="9" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F70" s="10" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="G70">
         <v>2024</v>
@@ -17645,20 +17693,20 @@
         <v>70</v>
       </c>
       <c r="B71" t="str" cm="1">
-        <f t="array" ref="B71">_xlfn.IFS(ISBLANK(D71),"",ISBLANK(C71),"no venue",ISBLANK(E71),"no bib",ISNUMBER(SEARCH("xiv", C71)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B71">_xlfn.IFS(ISBLANK(D71),"",ISBLANK(C71),"no venue",ISBLANK(E71),"no bib",ISNUMBER(SEARCH("xiv", C71)),"arxiv",SUM(I71:AA71)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C71" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D71" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="E71" s="12" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="F71" s="10" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="G71">
         <v>2024</v>
@@ -17739,20 +17787,20 @@
         <v>71</v>
       </c>
       <c r="B72" t="str" cm="1">
-        <f t="array" ref="B72">_xlfn.IFS(ISBLANK(D72),"",ISBLANK(C72),"no venue",ISBLANK(E72),"no bib",ISNUMBER(SEARCH("xiv", C72)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B72">_xlfn.IFS(ISBLANK(D72),"",ISBLANK(C72),"no venue",ISBLANK(E72),"no bib",ISNUMBER(SEARCH("xiv", C72)),"arxiv",SUM(I72:AA72)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C72" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="D72" s="13" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="E72" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F72" s="10" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="G72">
         <v>2024</v>
@@ -17821,20 +17869,20 @@
         <v>72</v>
       </c>
       <c r="B73" t="str" cm="1">
-        <f t="array" ref="B73">_xlfn.IFS(ISBLANK(D73),"",ISBLANK(C73),"no venue",ISBLANK(E73),"no bib",ISNUMBER(SEARCH("xiv", C73)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B73">_xlfn.IFS(ISBLANK(D73),"",ISBLANK(C73),"no venue",ISBLANK(E73),"no bib",ISNUMBER(SEARCH("xiv", C73)),"arxiv",SUM(I73:AA73)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C73" t="s">
-        <v>258</v>
+        <v>292</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="E73" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="G73">
         <v>2024</v>
@@ -17897,20 +17945,20 @@
         <v>73</v>
       </c>
       <c r="B74" t="str" cm="1">
-        <f t="array" ref="B74">_xlfn.IFS(ISBLANK(D74),"",ISBLANK(C74),"no venue",ISBLANK(E74),"no bib",ISNUMBER(SEARCH("xiv", C74)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B74">_xlfn.IFS(ISBLANK(D74),"",ISBLANK(C74),"no venue",ISBLANK(E74),"no bib",ISNUMBER(SEARCH("xiv", C74)),"arxiv",SUM(I74:AA74)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C74" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="E74" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="G74">
         <v>2024</v>
@@ -17982,16 +18030,16 @@
         <v>74</v>
       </c>
       <c r="C75" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="E75" s="12" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="G75">
         <v>2024</v>
@@ -18046,20 +18094,20 @@
         <v>75</v>
       </c>
       <c r="B76" t="str" cm="1">
-        <f t="array" ref="B76">_xlfn.IFS(ISBLANK(D76),"",ISBLANK(C76),"no venue",ISBLANK(E76),"no bib",ISNUMBER(SEARCH("xiv", C76)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B76">_xlfn.IFS(ISBLANK(D76),"",ISBLANK(C76),"no venue",ISBLANK(E76),"no bib",ISNUMBER(SEARCH("xiv", C76)),"arxiv",SUM(I76:AA76)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C76" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="E76" s="9" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="G76">
         <v>2024</v>
@@ -18094,17 +18142,17 @@
         <v>76</v>
       </c>
       <c r="B77" t="str" cm="1">
-        <f t="array" ref="B77">_xlfn.IFS(ISBLANK(D77),"",ISBLANK(C77),"no venue",ISBLANK(E77),"no bib",ISNUMBER(SEARCH("xiv", C77)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B77">_xlfn.IFS(ISBLANK(D77),"",ISBLANK(C77),"no venue",ISBLANK(E77),"no bib",ISNUMBER(SEARCH("xiv", C77)),"arxiv",SUM(I77:AA77)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C77" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="E77" s="12" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="G77">
         <v>2024</v>
@@ -18180,17 +18228,17 @@
         <v>77</v>
       </c>
       <c r="B78" t="str" cm="1">
-        <f t="array" ref="B78">_xlfn.IFS(ISBLANK(D78),"",ISBLANK(C78),"no venue",ISBLANK(E78),"no bib",ISNUMBER(SEARCH("xiv", C78)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B78">_xlfn.IFS(ISBLANK(D78),"",ISBLANK(C78),"no venue",ISBLANK(E78),"no bib",ISNUMBER(SEARCH("xiv", C78)),"arxiv",SUM(I78:AA78)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C78" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="E78" s="12" t="s">
-        <v>330</v>
+        <v>305</v>
+      </c>
+      <c r="E78" s="9" t="s">
+        <v>367</v>
       </c>
       <c r="G78">
         <v>2024</v>
@@ -18238,15 +18286,15 @@
       </c>
       <c r="AG78" t="str">
         <f>IF(AF78,E78,"")</f>
-        <v>saroufim2025neurips</v>
+        <v>tam2024llm</v>
       </c>
       <c r="AH78" t="str">
         <f>IF(W78,E78,"")</f>
-        <v>saroufim2025neurips</v>
+        <v>tam2024llm</v>
       </c>
       <c r="AI78" t="str">
         <f>IF(Y78,E78,"")</f>
-        <v>saroufim2025neurips</v>
+        <v>tam2024llm</v>
       </c>
       <c r="AJ78" t="str">
         <f>IF(AE78,E78,"")</f>
@@ -18259,17 +18307,17 @@
         <v>78</v>
       </c>
       <c r="B79" t="str" cm="1">
-        <f t="array" ref="B79">_xlfn.IFS(ISBLANK(D79),"",ISBLANK(C79),"no venue",ISBLANK(E79),"no bib",ISNUMBER(SEARCH("xiv", C79)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B79">_xlfn.IFS(ISBLANK(D79),"",ISBLANK(C79),"no venue",ISBLANK(E79),"no bib",ISNUMBER(SEARCH("xiv", C79)),"arxiv",SUM(I79:AA79)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="C79" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D79" s="11" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="E79" s="12" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="G79">
         <v>2024</v>
@@ -18310,15 +18358,14 @@
         <f t="shared" si="23"/>
         <v>79</v>
       </c>
-      <c r="B80" t="str" cm="1">
-        <f t="array" ref="B80">_xlfn.IFS(ISBLANK(D80),"",ISBLANK(C80),"no venue",ISBLANK(E80),"no bib",ISNUMBER(SEARCH("xiv", C80)),"arxiv",TRUE,"")</f>
-        <v>no bib</v>
-      </c>
       <c r="C80" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>325</v>
+        <v>321</v>
+      </c>
+      <c r="E80" s="12" t="s">
+        <v>346</v>
       </c>
       <c r="G80">
         <v>2025</v>
@@ -18336,17 +18383,17 @@
         <v>80</v>
       </c>
       <c r="B81" t="str" cm="1">
-        <f t="array" ref="B81">_xlfn.IFS(ISBLANK(D81),"",ISBLANK(C81),"no venue",ISBLANK(E81),"no bib",ISNUMBER(SEARCH("xiv", C81)),"arxiv",TRUE,"")</f>
-        <v/>
+        <f t="array" ref="B81">_xlfn.IFS(ISBLANK(D81),"",ISBLANK(C81),"no venue",ISBLANK(E81),"no bib",ISNUMBER(SEARCH("xiv", C81)),"arxiv",SUM(I81:AA81)&lt;3,"no categories",TRUE,"")</f>
+        <v>no categories</v>
       </c>
       <c r="C81" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="E81" s="12" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="G81">
         <v>2025</v>
@@ -18364,17 +18411,17 @@
         <v>81</v>
       </c>
       <c r="B82" t="str" cm="1">
-        <f t="array" ref="B82">_xlfn.IFS(ISBLANK(D82),"",ISBLANK(C82),"no venue",ISBLANK(E82),"no bib",ISNUMBER(SEARCH("xiv", C82)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B82">_xlfn.IFS(ISBLANK(D82),"",ISBLANK(C82),"no venue",ISBLANK(E82),"no bib",ISNUMBER(SEARCH("xiv", C82)),"arxiv",SUM(I82:AA82)&lt;3,"no categories",TRUE,"")</f>
         <v>arxiv</v>
       </c>
       <c r="C82" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E82" s="12" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="G82">
         <v>2025</v>
@@ -18391,21 +18438,20 @@
         <f t="shared" si="23"/>
         <v>82</v>
       </c>
-      <c r="B83" t="str" cm="1">
-        <f t="array" ref="B83">_xlfn.IFS(ISBLANK(D83),"",ISBLANK(C83),"no venue",ISBLANK(E83),"no bib",ISNUMBER(SEARCH("xiv", C83)),"arxiv",TRUE,"")</f>
-        <v>arxiv</v>
+      <c r="B83" t="s">
+        <v>351</v>
       </c>
       <c r="C83" t="s">
-        <v>30</v>
+        <v>347</v>
       </c>
       <c r="D83" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="E83" s="12" t="s">
         <v>331</v>
       </c>
-      <c r="E83" s="12" t="s">
-        <v>335</v>
-      </c>
       <c r="G83">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H83">
         <v>1</v>
@@ -18420,17 +18466,17 @@
         <v>83</v>
       </c>
       <c r="B84" t="str" cm="1">
-        <f t="array" ref="B84">_xlfn.IFS(ISBLANK(D84),"",ISBLANK(C84),"no venue",ISBLANK(E84),"no bib",ISNUMBER(SEARCH("xiv", C84)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B84">_xlfn.IFS(ISBLANK(D84),"",ISBLANK(C84),"no venue",ISBLANK(E84),"no bib",ISNUMBER(SEARCH("xiv", C84)),"arxiv",SUM(I84:AA84)&lt;3,"no categories",TRUE,"")</f>
         <v>arxiv</v>
       </c>
       <c r="C84" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="E84" s="12" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="G84">
         <v>2025</v>
@@ -18448,17 +18494,17 @@
         <v>84</v>
       </c>
       <c r="B85" t="str" cm="1">
-        <f t="array" ref="B85">_xlfn.IFS(ISBLANK(D85),"",ISBLANK(C85),"no venue",ISBLANK(E85),"no bib",ISNUMBER(SEARCH("xiv", C85)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B85">_xlfn.IFS(ISBLANK(D85),"",ISBLANK(C85),"no venue",ISBLANK(E85),"no bib",ISNUMBER(SEARCH("xiv", C85)),"arxiv",SUM(I85:AA85)&lt;3,"no categories",TRUE,"")</f>
         <v>arxiv</v>
       </c>
       <c r="C85" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="E85" s="12" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="G85">
         <v>2025</v>
@@ -18477,76 +18523,22 @@
         <v>85</v>
       </c>
       <c r="B86" t="str" cm="1">
-        <f t="array" ref="B86">_xlfn.IFS(ISBLANK(D86),"",ISBLANK(C86),"no venue",ISBLANK(#REF!),"no bib",ISNUMBER(SEARCH("xiv", C86)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B86">_xlfn.IFS(ISBLANK(D86),"",ISBLANK(C86),"no venue",ISBLANK(E86),"no bib",ISNUMBER(SEARCH("xiv", C86)),"arxiv",SUM(I86:AA86)&lt;3,"no categories",TRUE,"")</f>
         <v>arxiv</v>
       </c>
       <c r="C86" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E86" s="12" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G86">
         <v>2025</v>
       </c>
       <c r="H86">
-        <v>1</v>
-      </c>
-      <c r="I86">
-        <v>1</v>
-      </c>
-      <c r="J86">
-        <v>1</v>
-      </c>
-      <c r="K86">
-        <v>1</v>
-      </c>
-      <c r="L86">
-        <v>1</v>
-      </c>
-      <c r="M86">
-        <v>1</v>
-      </c>
-      <c r="N86">
-        <v>1</v>
-      </c>
-      <c r="O86">
-        <v>1</v>
-      </c>
-      <c r="P86">
-        <v>1</v>
-      </c>
-      <c r="Q86">
-        <v>1</v>
-      </c>
-      <c r="R86">
-        <v>1</v>
-      </c>
-      <c r="S86">
-        <v>1</v>
-      </c>
-      <c r="T86">
-        <v>1</v>
-      </c>
-      <c r="U86">
-        <v>1</v>
-      </c>
-      <c r="V86">
-        <v>1</v>
-      </c>
-      <c r="W86">
-        <v>1</v>
-      </c>
-      <c r="X86">
-        <v>1</v>
-      </c>
-      <c r="Y86">
-        <v>1</v>
-      </c>
-      <c r="Z86">
         <v>1</v>
       </c>
       <c r="AA86">
@@ -18560,17 +18552,17 @@
         <v>86</v>
       </c>
       <c r="B87" t="str" cm="1">
-        <f t="array" ref="B87">_xlfn.IFS(ISBLANK(D87),"",ISBLANK(C87),"no venue",ISBLANK(#REF!),"no bib",ISNUMBER(SEARCH("xiv", C87)),"arxiv",TRUE,"")</f>
-        <v/>
+        <f t="array" ref="B87">_xlfn.IFS(ISBLANK(D87),"",ISBLANK(C87),"no venue",ISBLANK(E87),"no bib",ISNUMBER(SEARCH("xiv", C87)),"arxiv",SUM(I87:AA87)&lt;3,"no categories",TRUE,"")</f>
+        <v>no categories</v>
       </c>
       <c r="C87" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="E87" s="12" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="G87">
         <v>2025</v>
@@ -18589,11 +18581,17 @@
         <v>87</v>
       </c>
       <c r="B88" t="str" cm="1">
-        <f t="array" ref="B88">_xlfn.IFS(ISBLANK(D88),"",ISBLANK(C88),"no venue",ISBLANK(E88),"no bib",ISNUMBER(SEARCH("xiv", C88)),"arxiv",TRUE,"")</f>
-        <v>no venue</v>
+        <f t="array" ref="B88">_xlfn.IFS(ISBLANK(D88),"",ISBLANK(C88),"no venue",ISBLANK(E88),"no bib",ISNUMBER(SEARCH("xiv", C88)),"arxiv",SUM(I88:AA88)&lt;3,"no categories",TRUE,"")</f>
+        <v>no categories</v>
+      </c>
+      <c r="C88" t="s">
+        <v>292</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>347</v>
+        <v>342</v>
+      </c>
+      <c r="E88" s="9" t="s">
+        <v>348</v>
       </c>
       <c r="G88">
         <v>2025</v>
@@ -18612,14 +18610,17 @@
         <v>88</v>
       </c>
       <c r="B89" t="str" cm="1">
-        <f t="array" ref="B89">_xlfn.IFS(ISBLANK(D89),"",ISBLANK(C89),"no venue",ISBLANK(E89),"no bib",ISNUMBER(SEARCH("xiv", C89)),"arxiv",TRUE,"")</f>
-        <v>no bib</v>
+        <f t="array" ref="B89">_xlfn.IFS(ISBLANK(D89),"",ISBLANK(C89),"no venue",ISBLANK(E89),"no bib",ISNUMBER(SEARCH("xiv", C89)),"arxiv",SUM(I89:AA89)&lt;3,"no categories",TRUE,"")</f>
+        <v>arxiv</v>
       </c>
       <c r="C89" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>346</v>
+        <v>341</v>
+      </c>
+      <c r="E89" s="12" t="s">
+        <v>349</v>
       </c>
       <c r="G89">
         <v>2025</v>
@@ -18637,12 +18638,20 @@
         <f t="shared" si="23"/>
         <v>89</v>
       </c>
-      <c r="B90" t="str" cm="1">
-        <f t="array" ref="B90">_xlfn.IFS(ISBLANK(D90),"",ISBLANK(C90),"no venue",ISBLANK(E90),"no bib",ISNUMBER(SEARCH("xiv", C90)),"arxiv",TRUE,"")</f>
-        <v/>
+      <c r="B90" t="s">
+        <v>351</v>
+      </c>
+      <c r="C90" t="s">
+        <v>347</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="E90" s="12" t="s">
+        <v>354</v>
       </c>
       <c r="G90">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H90">
         <v>1</v>
@@ -18658,8 +18667,23 @@
         <v>90</v>
       </c>
       <c r="B91" t="str" cm="1">
-        <f t="array" ref="B91">_xlfn.IFS(ISBLANK(D91),"",ISBLANK(C91),"no venue",ISBLANK(E91),"no bib",ISNUMBER(SEARCH("xiv", C91)),"arxiv",TRUE,"")</f>
-        <v/>
+        <f t="array" ref="B91">_xlfn.IFS(ISBLANK(D91),"",ISBLANK(C91),"no venue",ISBLANK(E91),"no bib",ISNUMBER(SEARCH("xiv", C91)),"arxiv",SUM(I91:AA91)&lt;3,"no categories",TRUE,"")</f>
+        <v>arxiv</v>
+      </c>
+      <c r="C91" t="s">
+        <v>344</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="E91" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="G91">
+        <v>2026</v>
+      </c>
+      <c r="H91">
+        <v>1</v>
       </c>
       <c r="AG91" s="8"/>
     </row>
@@ -18669,8 +18693,23 @@
         <v>91</v>
       </c>
       <c r="B92" t="str" cm="1">
-        <f t="array" ref="B92">_xlfn.IFS(ISBLANK(D92),"",ISBLANK(C92),"no venue",ISBLANK(E92),"no bib",ISNUMBER(SEARCH("xiv", C92)),"arxiv",TRUE,"")</f>
-        <v/>
+        <f t="array" ref="B92">_xlfn.IFS(ISBLANK(D92),"",ISBLANK(C92),"no venue",ISBLANK(E92),"no bib",ISNUMBER(SEARCH("xiv", C92)),"arxiv",SUM(I92:AA92)&lt;3,"no categories",TRUE,"")</f>
+        <v>no categories</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="E92" s="12" t="s">
+        <v>356</v>
+      </c>
+      <c r="G92">
+        <v>2026</v>
+      </c>
+      <c r="H92">
+        <v>1</v>
       </c>
       <c r="AG92" s="8"/>
     </row>
@@ -18680,8 +18719,20 @@
         <v>92</v>
       </c>
       <c r="B93" t="str" cm="1">
-        <f t="array" ref="B93">_xlfn.IFS(ISBLANK(D93),"",ISBLANK(C93),"no venue",ISBLANK(E93),"no bib",ISNUMBER(SEARCH("xiv", C93)),"arxiv",TRUE,"")</f>
-        <v/>
+        <f t="array" ref="B93">_xlfn.IFS(ISBLANK(D93),"",ISBLANK(C93),"no venue",ISBLANK(E93),"no bib",ISNUMBER(SEARCH("xiv", C93)),"arxiv",SUM(I93:AA93)&lt;3,"no categories",TRUE,"")</f>
+        <v>no bib</v>
+      </c>
+      <c r="C93" t="s">
+        <v>344</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="G93">
+        <v>2026</v>
+      </c>
+      <c r="H93">
+        <v>1</v>
       </c>
       <c r="AG93" s="8"/>
     </row>
@@ -18691,8 +18742,23 @@
         <v>93</v>
       </c>
       <c r="B94" t="str" cm="1">
-        <f t="array" ref="B94">_xlfn.IFS(ISBLANK(D94),"",ISBLANK(C94),"no venue",ISBLANK(E94),"no bib",ISNUMBER(SEARCH("xiv", C94)),"arxiv",TRUE,"")</f>
-        <v/>
+        <f t="array" ref="B94">_xlfn.IFS(ISBLANK(D94),"",ISBLANK(C94),"no venue",ISBLANK(E94),"no bib",ISNUMBER(SEARCH("xiv", C94)),"arxiv",SUM(I94:AA94)&lt;3,"no categories",TRUE,"")</f>
+        <v>arxiv</v>
+      </c>
+      <c r="C94" t="s">
+        <v>344</v>
+      </c>
+      <c r="D94" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="E94" s="12" t="s">
+        <v>359</v>
+      </c>
+      <c r="G94">
+        <v>2026</v>
+      </c>
+      <c r="H94">
+        <v>1</v>
       </c>
       <c r="AG94" s="8"/>
     </row>
@@ -18702,8 +18768,23 @@
         <v>94</v>
       </c>
       <c r="B95" t="str" cm="1">
-        <f t="array" ref="B95">_xlfn.IFS(ISBLANK(D95),"",ISBLANK(C95),"no venue",ISBLANK(E95),"no bib",ISNUMBER(SEARCH("xiv", C95)),"arxiv",TRUE,"")</f>
-        <v/>
+        <f t="array" ref="B95">_xlfn.IFS(ISBLANK(D95),"",ISBLANK(C95),"no venue",ISBLANK(E95),"no bib",ISNUMBER(SEARCH("xiv", C95)),"arxiv",SUM(I95:AA95)&lt;3,"no categories",TRUE,"")</f>
+        <v>arxiv</v>
+      </c>
+      <c r="C95" t="s">
+        <v>344</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="E95" s="12" t="s">
+        <v>362</v>
+      </c>
+      <c r="G95">
+        <v>2026</v>
+      </c>
+      <c r="H95">
+        <v>1</v>
       </c>
       <c r="AG95" s="8"/>
     </row>
@@ -18713,8 +18794,23 @@
         <v>95</v>
       </c>
       <c r="B96" t="str" cm="1">
-        <f t="array" ref="B96">_xlfn.IFS(ISBLANK(D96),"",ISBLANK(C96),"no venue",ISBLANK(E96),"no bib",ISNUMBER(SEARCH("xiv", C96)),"arxiv",TRUE,"")</f>
-        <v/>
+        <f t="array" ref="B96">_xlfn.IFS(ISBLANK(D96),"",ISBLANK(C96),"no venue",ISBLANK(E96),"no bib",ISNUMBER(SEARCH("xiv", C96)),"arxiv",SUM(I96:AA96)&lt;3,"no categories",TRUE,"")</f>
+        <v>arxiv</v>
+      </c>
+      <c r="C96" t="s">
+        <v>344</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="E96" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="G96">
+        <v>2026</v>
+      </c>
+      <c r="H96">
+        <v>1</v>
       </c>
       <c r="AG96" s="8"/>
     </row>
@@ -18724,8 +18820,23 @@
         <v>96</v>
       </c>
       <c r="B97" t="str" cm="1">
-        <f t="array" ref="B97">_xlfn.IFS(ISBLANK(D97),"",ISBLANK(C97),"no venue",ISBLANK(E97),"no bib",ISNUMBER(SEARCH("xiv", C97)),"arxiv",TRUE,"")</f>
-        <v/>
+        <f t="array" ref="B97">_xlfn.IFS(ISBLANK(D97),"",ISBLANK(C97),"no venue",ISBLANK(E97),"no bib",ISNUMBER(SEARCH("xiv", C97)),"arxiv",SUM(I97:AA97)&lt;3,"no categories",TRUE,"")</f>
+        <v>arxiv</v>
+      </c>
+      <c r="C97" t="s">
+        <v>344</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="E97" s="12" t="s">
+        <v>365</v>
+      </c>
+      <c r="G97">
+        <v>2026</v>
+      </c>
+      <c r="H97">
+        <v>1</v>
       </c>
       <c r="AG97" s="8"/>
     </row>
@@ -18735,8 +18846,14 @@
         <v>97</v>
       </c>
       <c r="B98" t="str" cm="1">
-        <f t="array" ref="B98">_xlfn.IFS(ISBLANK(D98),"",ISBLANK(C98),"no venue",ISBLANK(E98),"no bib",ISNUMBER(SEARCH("xiv", C98)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B98">_xlfn.IFS(ISBLANK(D98),"",ISBLANK(C98),"no venue",ISBLANK(E98),"no bib",ISNUMBER(SEARCH("xiv", C98)),"arxiv",SUM(I98:AA98)&lt;3,"no categories",TRUE,"")</f>
         <v/>
+      </c>
+      <c r="C98" t="s">
+        <v>344</v>
+      </c>
+      <c r="G98">
+        <v>2026</v>
       </c>
       <c r="AG98" s="8"/>
     </row>
@@ -18746,8 +18863,14 @@
         <v>98</v>
       </c>
       <c r="B99" t="str" cm="1">
-        <f t="array" ref="B99">_xlfn.IFS(ISBLANK(D99),"",ISBLANK(C99),"no venue",ISBLANK(E99),"no bib",ISNUMBER(SEARCH("xiv", C99)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B99">_xlfn.IFS(ISBLANK(D99),"",ISBLANK(C99),"no venue",ISBLANK(E99),"no bib",ISNUMBER(SEARCH("xiv", C99)),"arxiv",SUM(I99:AA99)&lt;3,"no categories",TRUE,"")</f>
         <v/>
+      </c>
+      <c r="C99" t="s">
+        <v>344</v>
+      </c>
+      <c r="G99">
+        <v>2026</v>
       </c>
       <c r="AG99" s="8"/>
     </row>
@@ -18757,8 +18880,11 @@
         <v>99</v>
       </c>
       <c r="B100" t="str" cm="1">
-        <f t="array" ref="B100">_xlfn.IFS(ISBLANK(D100),"",ISBLANK(C100),"no venue",ISBLANK(E100),"no bib",ISNUMBER(SEARCH("xiv", C100)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B100">_xlfn.IFS(ISBLANK(D100),"",ISBLANK(C100),"no venue",ISBLANK(E100),"no bib",ISNUMBER(SEARCH("xiv", C100)),"arxiv",SUM(I100:AA100)&lt;3,"no categories",TRUE,"")</f>
         <v/>
+      </c>
+      <c r="C100" t="s">
+        <v>344</v>
       </c>
       <c r="AG100" s="8"/>
     </row>
@@ -18768,7 +18894,7 @@
         <v>100</v>
       </c>
       <c r="B101" t="str" cm="1">
-        <f t="array" ref="B101">_xlfn.IFS(ISBLANK(D101),"",ISBLANK(C101),"no venue",ISBLANK(E101),"no bib",ISNUMBER(SEARCH("xiv", C101)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B101">_xlfn.IFS(ISBLANK(D101),"",ISBLANK(C101),"no venue",ISBLANK(E101),"no bib",ISNUMBER(SEARCH("xiv", C101)),"arxiv",SUM(I101:AA101)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="AG101" s="8"/>
@@ -18779,7 +18905,7 @@
         <v>101</v>
       </c>
       <c r="B102" t="str" cm="1">
-        <f t="array" ref="B102">_xlfn.IFS(ISBLANK(D102),"",ISBLANK(C102),"no venue",ISBLANK(E102),"no bib",ISNUMBER(SEARCH("xiv", C102)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B102">_xlfn.IFS(ISBLANK(D102),"",ISBLANK(C102),"no venue",ISBLANK(E102),"no bib",ISNUMBER(SEARCH("xiv", C102)),"arxiv",SUM(I102:AA102)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="AG102" s="8"/>
@@ -18790,7 +18916,7 @@
         <v>102</v>
       </c>
       <c r="B103" t="str" cm="1">
-        <f t="array" ref="B103">_xlfn.IFS(ISBLANK(D103),"",ISBLANK(C103),"no venue",ISBLANK(E103),"no bib",ISNUMBER(SEARCH("xiv", C103)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B103">_xlfn.IFS(ISBLANK(D103),"",ISBLANK(C103),"no venue",ISBLANK(E103),"no bib",ISNUMBER(SEARCH("xiv", C103)),"arxiv",SUM(I103:AA103)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="AG103" s="8"/>
@@ -18801,7 +18927,7 @@
         <v>103</v>
       </c>
       <c r="B104" t="str" cm="1">
-        <f t="array" ref="B104">_xlfn.IFS(ISBLANK(D104),"",ISBLANK(C104),"no venue",ISBLANK(E104),"no bib",ISNUMBER(SEARCH("xiv", C104)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B104">_xlfn.IFS(ISBLANK(D104),"",ISBLANK(C104),"no venue",ISBLANK(E104),"no bib",ISNUMBER(SEARCH("xiv", C104)),"arxiv",SUM(I104:AA104)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="AG104" s="8"/>
@@ -18812,7 +18938,7 @@
         <v>104</v>
       </c>
       <c r="B105" t="str" cm="1">
-        <f t="array" ref="B105">_xlfn.IFS(ISBLANK(D105),"",ISBLANK(C105),"no venue",ISBLANK(E105),"no bib",ISNUMBER(SEARCH("xiv", C105)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B105">_xlfn.IFS(ISBLANK(D105),"",ISBLANK(C105),"no venue",ISBLANK(E105),"no bib",ISNUMBER(SEARCH("xiv", C105)),"arxiv",SUM(I105:AA105)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="AG105" s="8"/>
@@ -18823,7 +18949,7 @@
         <v>105</v>
       </c>
       <c r="B106" t="str" cm="1">
-        <f t="array" ref="B106">_xlfn.IFS(ISBLANK(D106),"",ISBLANK(C106),"no venue",ISBLANK(E106),"no bib",ISNUMBER(SEARCH("xiv", C106)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B106">_xlfn.IFS(ISBLANK(D106),"",ISBLANK(C106),"no venue",ISBLANK(E106),"no bib",ISNUMBER(SEARCH("xiv", C106)),"arxiv",SUM(I106:AA106)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="AG106" s="8"/>
@@ -18834,7 +18960,7 @@
         <v>106</v>
       </c>
       <c r="B107" t="str" cm="1">
-        <f t="array" ref="B107">_xlfn.IFS(ISBLANK(D107),"",ISBLANK(C107),"no venue",ISBLANK(E107),"no bib",ISNUMBER(SEARCH("xiv", C107)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B107">_xlfn.IFS(ISBLANK(D107),"",ISBLANK(C107),"no venue",ISBLANK(E107),"no bib",ISNUMBER(SEARCH("xiv", C107)),"arxiv",SUM(I107:AA107)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="AG107" s="8"/>
@@ -18845,7 +18971,7 @@
         <v>107</v>
       </c>
       <c r="B108" t="str" cm="1">
-        <f t="array" ref="B108">_xlfn.IFS(ISBLANK(D108),"",ISBLANK(C108),"no venue",ISBLANK(E108),"no bib",ISNUMBER(SEARCH("xiv", C108)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B108">_xlfn.IFS(ISBLANK(D108),"",ISBLANK(C108),"no venue",ISBLANK(E108),"no bib",ISNUMBER(SEARCH("xiv", C108)),"arxiv",SUM(I108:AA108)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="AG108" s="8"/>
@@ -18856,7 +18982,7 @@
         <v>108</v>
       </c>
       <c r="B109" t="str" cm="1">
-        <f t="array" ref="B109">_xlfn.IFS(ISBLANK(D109),"",ISBLANK(C109),"no venue",ISBLANK(E109),"no bib",ISNUMBER(SEARCH("xiv", C109)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B109">_xlfn.IFS(ISBLANK(D109),"",ISBLANK(C109),"no venue",ISBLANK(E109),"no bib",ISNUMBER(SEARCH("xiv", C109)),"arxiv",SUM(I109:AA109)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="AG109" s="8"/>
@@ -18867,7 +18993,7 @@
         <v>109</v>
       </c>
       <c r="B110" t="str" cm="1">
-        <f t="array" ref="B110">_xlfn.IFS(ISBLANK(D110),"",ISBLANK(C110),"no venue",ISBLANK(E110),"no bib",ISNUMBER(SEARCH("xiv", C110)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B110">_xlfn.IFS(ISBLANK(D110),"",ISBLANK(C110),"no venue",ISBLANK(E110),"no bib",ISNUMBER(SEARCH("xiv", C110)),"arxiv",SUM(I110:AA110)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="AG110" s="8"/>
@@ -18878,7 +19004,7 @@
         <v>110</v>
       </c>
       <c r="B111" t="str" cm="1">
-        <f t="array" ref="B111">_xlfn.IFS(ISBLANK(D111),"",ISBLANK(C111),"no venue",ISBLANK(E111),"no bib",ISNUMBER(SEARCH("xiv", C111)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B111">_xlfn.IFS(ISBLANK(D111),"",ISBLANK(C111),"no venue",ISBLANK(E111),"no bib",ISNUMBER(SEARCH("xiv", C111)),"arxiv",SUM(I111:AA111)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="AG111" s="8"/>
@@ -18889,7 +19015,7 @@
         <v>111</v>
       </c>
       <c r="B112" t="str" cm="1">
-        <f t="array" ref="B112">_xlfn.IFS(ISBLANK(D112),"",ISBLANK(C112),"no venue",ISBLANK(E112),"no bib",ISNUMBER(SEARCH("xiv", C112)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B112">_xlfn.IFS(ISBLANK(D112),"",ISBLANK(C112),"no venue",ISBLANK(E112),"no bib",ISNUMBER(SEARCH("xiv", C112)),"arxiv",SUM(I112:AA112)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="AG112" s="8"/>
@@ -18900,7 +19026,7 @@
         <v>112</v>
       </c>
       <c r="B113" t="str" cm="1">
-        <f t="array" ref="B113">_xlfn.IFS(ISBLANK(D113),"",ISBLANK(C113),"no venue",ISBLANK(E113),"no bib",ISNUMBER(SEARCH("xiv", C113)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B113">_xlfn.IFS(ISBLANK(D113),"",ISBLANK(C113),"no venue",ISBLANK(E113),"no bib",ISNUMBER(SEARCH("xiv", C113)),"arxiv",SUM(I113:AA113)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="AG113" s="8"/>
@@ -18911,7 +19037,7 @@
         <v>113</v>
       </c>
       <c r="B114" t="str" cm="1">
-        <f t="array" ref="B114">_xlfn.IFS(ISBLANK(D114),"",ISBLANK(C114),"no venue",ISBLANK(E114),"no bib",ISNUMBER(SEARCH("xiv", C114)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B114">_xlfn.IFS(ISBLANK(D114),"",ISBLANK(C114),"no venue",ISBLANK(E114),"no bib",ISNUMBER(SEARCH("xiv", C114)),"arxiv",SUM(I114:AA114)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="AG114" s="8"/>
@@ -18922,7 +19048,7 @@
         <v>114</v>
       </c>
       <c r="B115" t="str" cm="1">
-        <f t="array" ref="B115">_xlfn.IFS(ISBLANK(D115),"",ISBLANK(C115),"no venue",ISBLANK(E115),"no bib",ISNUMBER(SEARCH("xiv", C115)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B115">_xlfn.IFS(ISBLANK(D115),"",ISBLANK(C115),"no venue",ISBLANK(E115),"no bib",ISNUMBER(SEARCH("xiv", C115)),"arxiv",SUM(I115:AA115)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="AG115" s="8"/>
@@ -18933,7 +19059,7 @@
         <v>115</v>
       </c>
       <c r="B116" t="str" cm="1">
-        <f t="array" ref="B116">_xlfn.IFS(ISBLANK(D116),"",ISBLANK(C116),"no venue",ISBLANK(E116),"no bib",ISNUMBER(SEARCH("xiv", C116)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B116">_xlfn.IFS(ISBLANK(D116),"",ISBLANK(C116),"no venue",ISBLANK(E116),"no bib",ISNUMBER(SEARCH("xiv", C116)),"arxiv",SUM(I116:AA116)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="AG116" s="8"/>
@@ -18944,7 +19070,7 @@
         <v>116</v>
       </c>
       <c r="B117" t="str" cm="1">
-        <f t="array" ref="B117">_xlfn.IFS(ISBLANK(D117),"",ISBLANK(C117),"no venue",ISBLANK(E117),"no bib",ISNUMBER(SEARCH("xiv", C117)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B117">_xlfn.IFS(ISBLANK(D117),"",ISBLANK(C117),"no venue",ISBLANK(E117),"no bib",ISNUMBER(SEARCH("xiv", C117)),"arxiv",SUM(I117:AA117)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="AG117" s="8"/>
@@ -18955,7 +19081,7 @@
         <v>117</v>
       </c>
       <c r="B118" t="str" cm="1">
-        <f t="array" ref="B118">_xlfn.IFS(ISBLANK(D118),"",ISBLANK(C118),"no venue",ISBLANK(E118),"no bib",ISNUMBER(SEARCH("xiv", C118)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B118">_xlfn.IFS(ISBLANK(D118),"",ISBLANK(C118),"no venue",ISBLANK(E118),"no bib",ISNUMBER(SEARCH("xiv", C118)),"arxiv",SUM(I118:AA118)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="AG118" s="8"/>
@@ -18966,7 +19092,7 @@
         <v>118</v>
       </c>
       <c r="B119" t="str" cm="1">
-        <f t="array" ref="B119">_xlfn.IFS(ISBLANK(D119),"",ISBLANK(C119),"no venue",ISBLANK(E119),"no bib",ISNUMBER(SEARCH("xiv", C119)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B119">_xlfn.IFS(ISBLANK(D119),"",ISBLANK(C119),"no venue",ISBLANK(E119),"no bib",ISNUMBER(SEARCH("xiv", C119)),"arxiv",SUM(I119:AA119)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="AG119" s="8"/>
@@ -18977,7 +19103,7 @@
         <v>119</v>
       </c>
       <c r="B120" t="str" cm="1">
-        <f t="array" ref="B120">_xlfn.IFS(ISBLANK(D120),"",ISBLANK(C120),"no venue",ISBLANK(E120),"no bib",ISNUMBER(SEARCH("xiv", C120)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B120">_xlfn.IFS(ISBLANK(D120),"",ISBLANK(C120),"no venue",ISBLANK(E120),"no bib",ISNUMBER(SEARCH("xiv", C120)),"arxiv",SUM(I120:AA120)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="AG120" s="8"/>
@@ -18988,7 +19114,7 @@
         <v>120</v>
       </c>
       <c r="B121" t="str" cm="1">
-        <f t="array" ref="B121">_xlfn.IFS(ISBLANK(D121),"",ISBLANK(C121),"no venue",ISBLANK(E121),"no bib",ISNUMBER(SEARCH("xiv", C121)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B121">_xlfn.IFS(ISBLANK(D121),"",ISBLANK(C121),"no venue",ISBLANK(E121),"no bib",ISNUMBER(SEARCH("xiv", C121)),"arxiv",SUM(I121:AA121)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="AG121" s="8"/>
@@ -18999,7 +19125,7 @@
         <v>121</v>
       </c>
       <c r="B122" t="str" cm="1">
-        <f t="array" ref="B122">_xlfn.IFS(ISBLANK(D122),"",ISBLANK(C122),"no venue",ISBLANK(E122),"no bib",ISNUMBER(SEARCH("xiv", C122)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B122">_xlfn.IFS(ISBLANK(D122),"",ISBLANK(C122),"no venue",ISBLANK(E122),"no bib",ISNUMBER(SEARCH("xiv", C122)),"arxiv",SUM(I122:AA122)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="AG122" s="8"/>
@@ -19010,7 +19136,7 @@
         <v>122</v>
       </c>
       <c r="B123" t="str" cm="1">
-        <f t="array" ref="B123">_xlfn.IFS(ISBLANK(D123),"",ISBLANK(C123),"no venue",ISBLANK(E123),"no bib",ISNUMBER(SEARCH("xiv", C123)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B123">_xlfn.IFS(ISBLANK(D123),"",ISBLANK(C123),"no venue",ISBLANK(E123),"no bib",ISNUMBER(SEARCH("xiv", C123)),"arxiv",SUM(I123:AA123)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="AG123" s="8"/>
@@ -19021,7 +19147,7 @@
         <v>123</v>
       </c>
       <c r="B124" t="str" cm="1">
-        <f t="array" ref="B124">_xlfn.IFS(ISBLANK(D124),"",ISBLANK(C124),"no venue",ISBLANK(E124),"no bib",ISNUMBER(SEARCH("xiv", C124)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B124">_xlfn.IFS(ISBLANK(D124),"",ISBLANK(C124),"no venue",ISBLANK(E124),"no bib",ISNUMBER(SEARCH("xiv", C124)),"arxiv",SUM(I124:AA124)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="AG124" s="8"/>
@@ -19032,7 +19158,7 @@
         <v>124</v>
       </c>
       <c r="B125" t="str" cm="1">
-        <f t="array" ref="B125">_xlfn.IFS(ISBLANK(D125),"",ISBLANK(C125),"no venue",ISBLANK(E125),"no bib",ISNUMBER(SEARCH("xiv", C125)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B125">_xlfn.IFS(ISBLANK(D125),"",ISBLANK(C125),"no venue",ISBLANK(E125),"no bib",ISNUMBER(SEARCH("xiv", C125)),"arxiv",SUM(I125:AA125)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="AG125" s="8"/>
@@ -19043,7 +19169,7 @@
         <v>125</v>
       </c>
       <c r="B126" t="str" cm="1">
-        <f t="array" ref="B126">_xlfn.IFS(ISBLANK(D126),"",ISBLANK(C126),"no venue",ISBLANK(E126),"no bib",ISNUMBER(SEARCH("xiv", C126)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B126">_xlfn.IFS(ISBLANK(D126),"",ISBLANK(C126),"no venue",ISBLANK(E126),"no bib",ISNUMBER(SEARCH("xiv", C126)),"arxiv",SUM(I126:AA126)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="AG126" s="8"/>
@@ -19054,7 +19180,7 @@
         <v>126</v>
       </c>
       <c r="B127" t="str" cm="1">
-        <f t="array" ref="B127">_xlfn.IFS(ISBLANK(D127),"",ISBLANK(C127),"no venue",ISBLANK(E127),"no bib",ISNUMBER(SEARCH("xiv", C127)),"arxiv",TRUE,"")</f>
+        <f t="array" ref="B127">_xlfn.IFS(ISBLANK(D127),"",ISBLANK(C127),"no venue",ISBLANK(E127),"no bib",ISNUMBER(SEARCH("xiv", C127)),"arxiv",SUM(I127:AA127)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="AG127" s="8"/>
@@ -19085,34 +19211,34 @@
     </row>
     <row r="137" spans="7:36">
       <c r="G137" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H137">
         <f>SUM(H2:H79)</f>
         <v>77</v>
       </c>
       <c r="I137">
-        <f>SUM(I2:I78)</f>
+        <f t="shared" ref="I137:N137" si="28">SUM(I2:I78)</f>
         <v>6</v>
       </c>
       <c r="J137">
-        <f>SUM(J2:J78)</f>
+        <f t="shared" si="28"/>
         <v>5</v>
       </c>
       <c r="K137">
-        <f>SUM(K2:K78)</f>
+        <f t="shared" si="28"/>
         <v>11</v>
       </c>
       <c r="L137">
-        <f>SUM(L2:L78)</f>
+        <f t="shared" si="28"/>
         <v>2</v>
       </c>
       <c r="M137">
-        <f>SUM(M2:M78)</f>
+        <f t="shared" si="28"/>
         <v>4</v>
       </c>
       <c r="N137">
-        <f>SUM(N2:N78)</f>
+        <f t="shared" si="28"/>
         <v>4</v>
       </c>
       <c r="O137">
@@ -19179,105 +19305,105 @@
         <f>SUM(AF2:AF79)</f>
         <v>62</v>
       </c>
-      <c r="AG137">
+      <c r="AG137" t="str">
         <f>IF(AF137,E80,"")</f>
-        <v>0</v>
-      </c>
-      <c r="AH137">
+        <v>ashurytahan2025mightytorrbenchmarktable</v>
+      </c>
+      <c r="AH137" t="str">
         <f>IF(W137,E80,"")</f>
-        <v>0</v>
-      </c>
-      <c r="AI137">
+        <v>ashurytahan2025mightytorrbenchmarktable</v>
+      </c>
+      <c r="AI137" t="str">
         <f>IF(Y137,E80,"")</f>
-        <v>0</v>
-      </c>
-      <c r="AJ137">
+        <v>ashurytahan2025mightytorrbenchmarktable</v>
+      </c>
+      <c r="AJ137" t="str">
         <f>IF(AE137,E80,"")</f>
-        <v>0</v>
+        <v>ashurytahan2025mightytorrbenchmarktable</v>
       </c>
     </row>
     <row r="138" spans="7:36">
       <c r="G138" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H138" s="7">
-        <f>H137/$AD$137</f>
+        <f t="shared" ref="H138:AA138" si="29">H137/$AD$137</f>
         <v>1</v>
       </c>
       <c r="I138" s="7">
-        <f>I137/$AD$137</f>
+        <f t="shared" si="29"/>
         <v>7.792207792207792E-2</v>
       </c>
       <c r="J138" s="7">
-        <f>J137/$AD$137</f>
+        <f t="shared" si="29"/>
         <v>6.4935064935064929E-2</v>
       </c>
       <c r="K138" s="7">
-        <f>K137/$AD$137</f>
+        <f t="shared" si="29"/>
         <v>0.14285714285714285</v>
       </c>
       <c r="L138" s="7">
-        <f>L137/$AD$137</f>
+        <f t="shared" si="29"/>
         <v>2.5974025974025976E-2</v>
       </c>
       <c r="M138" s="7">
-        <f>M137/$AD$137</f>
+        <f t="shared" si="29"/>
         <v>5.1948051948051951E-2</v>
       </c>
       <c r="N138" s="7">
-        <f>N137/$AD$137</f>
+        <f t="shared" si="29"/>
         <v>5.1948051948051951E-2</v>
       </c>
       <c r="O138" s="7">
-        <f>O137/$AD$137</f>
+        <f t="shared" si="29"/>
         <v>0.50649350649350644</v>
       </c>
       <c r="P138" s="7">
-        <f>P137/$AD$137</f>
+        <f t="shared" si="29"/>
         <v>0.54545454545454541</v>
       </c>
       <c r="Q138" s="7">
-        <f>Q137/$AD$137</f>
+        <f t="shared" si="29"/>
         <v>0.55844155844155841</v>
       </c>
       <c r="R138" s="7">
-        <f>R137/$AD$137</f>
+        <f t="shared" si="29"/>
         <v>0.27272727272727271</v>
       </c>
       <c r="S138" s="7">
-        <f>S137/$AD$137</f>
+        <f t="shared" si="29"/>
         <v>0.41558441558441561</v>
       </c>
       <c r="T138" s="7">
-        <f>T137/$AD$137</f>
+        <f t="shared" si="29"/>
         <v>0.51948051948051943</v>
       </c>
       <c r="U138" s="7">
-        <f>U137/$AD$137</f>
+        <f t="shared" si="29"/>
         <v>0.19480519480519481</v>
       </c>
       <c r="V138" s="7">
-        <f>V137/$AD$137</f>
+        <f t="shared" si="29"/>
         <v>0.40259740259740262</v>
       </c>
       <c r="W138" s="7">
-        <f>W137/$AD$137</f>
+        <f t="shared" si="29"/>
         <v>0.42857142857142855</v>
       </c>
       <c r="X138" s="7">
-        <f>X137/$AD$137</f>
+        <f t="shared" si="29"/>
         <v>0.45454545454545453</v>
       </c>
       <c r="Y138" s="7">
-        <f>Y137/$AD$137</f>
+        <f t="shared" si="29"/>
         <v>0.45454545454545453</v>
       </c>
       <c r="Z138" s="7">
-        <f>Z137/$AD$137</f>
+        <f t="shared" si="29"/>
         <v>0.51948051948051943</v>
       </c>
       <c r="AA138" s="7">
-        <f>AA137/$AD$137</f>
+        <f t="shared" si="29"/>
         <v>0.96103896103896103</v>
       </c>
       <c r="AB138" s="7"/>
@@ -19361,6 +19487,14 @@
     <hyperlink ref="D87" r:id="rId41" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=8b8IhUYAAAAJ&amp;sortby=pubdate&amp;citation_for_view=8b8IhUYAAAAJ:cFHS6HbyZ2cC" xr:uid="{012D4D4B-F7DB-534F-929E-F3980EB01887}"/>
     <hyperlink ref="D89" r:id="rId42" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=8b8IhUYAAAAJ&amp;sortby=pubdate&amp;citation_for_view=8b8IhUYAAAAJ:OU6Ihb5iCvQC" xr:uid="{83F89CA5-9C53-454A-82C0-5B114240419E}"/>
     <hyperlink ref="D88" r:id="rId43" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=8b8IhUYAAAAJ&amp;sortby=pubdate&amp;citation_for_view=8b8IhUYAAAAJ:p2g8aNsByqUC" xr:uid="{F1C14A89-89CC-4F40-8425-EE9E1FA18475}"/>
+    <hyperlink ref="D90" r:id="rId44" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=8b8IhUYAAAAJ&amp;sortby=pubdate&amp;citation_for_view=8b8IhUYAAAAJ:738O_yMBCRsC" xr:uid="{7F06036E-46CB-7B4A-B5A9-01BD9FEB494D}"/>
+    <hyperlink ref="D91" r:id="rId45" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=8b8IhUYAAAAJ&amp;sortby=pubdate&amp;citation_for_view=8b8IhUYAAAAJ:K3LRdlH-MEoC" xr:uid="{E3BF1F50-9A61-BD47-80DD-3E7FA5F51488}"/>
+    <hyperlink ref="D92" r:id="rId46" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=8b8IhUYAAAAJ&amp;sortby=pubdate&amp;citation_for_view=8b8IhUYAAAAJ:tOudhMTPpwUC" xr:uid="{A1EF67F5-E28E-A14D-A57D-7545932AF158}"/>
+    <hyperlink ref="C92" r:id="rId47" display="BabyLM@EMNLP" xr:uid="{D8DDEF9E-B21E-CD40-A406-DFC0EB019B6A}"/>
+    <hyperlink ref="D93" r:id="rId48" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=8b8IhUYAAAAJ&amp;sortby=pubdate&amp;citation_for_view=8b8IhUYAAAAJ:4fKUyHm3Qg0C" xr:uid="{63AC3719-785D-4045-842F-51673617DEA4}"/>
+    <hyperlink ref="D95" r:id="rId49" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=8b8IhUYAAAAJ&amp;sortby=pubdate&amp;citation_for_view=8b8IhUYAAAAJ:B3FOqHPlNUQC" xr:uid="{4655ADB8-FEB9-6148-99F7-03736D7EB3B9}"/>
+    <hyperlink ref="D96" r:id="rId50" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=8b8IhUYAAAAJ&amp;sortby=pubdate&amp;citation_for_view=8b8IhUYAAAAJ:sSrBHYA8nusC" xr:uid="{94FB61E5-5F04-5645-A99F-119289B9E81D}"/>
+    <hyperlink ref="D97" r:id="rId51" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=8b8IhUYAAAAJ&amp;sortby=pubdate&amp;citation_for_view=8b8IhUYAAAAJ:5Ul4iDaHHb8C" xr:uid="{AC018292-7C41-B947-89FB-2E8002093149}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -23019,7 +23153,7 @@
       </c>
       <c r="B53" t="str">
         <f>Sheet1!C55</f>
-        <v xml:space="preserve">TMLR (under review) </v>
+        <v xml:space="preserve">TMLR </v>
       </c>
       <c r="C53" t="str">
         <f>Sheet1!D55</f>
@@ -23649,7 +23783,7 @@
       </c>
       <c r="B62" t="str">
         <f>Sheet1!C64</f>
-        <v xml:space="preserve">ARR^ (under review) </v>
+        <v>ArXiv</v>
       </c>
       <c r="C62" t="str">
         <f>Sheet1!D64</f>
@@ -23929,7 +24063,7 @@
       </c>
       <c r="B66" t="str">
         <f>Sheet1!C68</f>
-        <v xml:space="preserve">Nature Machine Intelligence^ (under review)  </v>
+        <v xml:space="preserve">Nature Machine Intelligence^ </v>
       </c>
       <c r="C66" t="str">
         <f>Sheet1!D68</f>
@@ -28070,7 +28204,7 @@
       </c>
       <c r="B53" t="str">
         <f>Sheet1!C55</f>
-        <v xml:space="preserve">TMLR (under review) </v>
+        <v xml:space="preserve">TMLR </v>
       </c>
       <c r="C53" t="str">
         <f>Sheet1!D55</f>
@@ -28700,7 +28834,7 @@
       </c>
       <c r="B62" t="str">
         <f>Sheet1!C64</f>
-        <v xml:space="preserve">ARR^ (under review) </v>
+        <v>ArXiv</v>
       </c>
       <c r="C62" t="str">
         <f>Sheet1!D64</f>
@@ -28980,7 +29114,7 @@
       </c>
       <c r="B66" t="str">
         <f>Sheet1!C68</f>
-        <v xml:space="preserve">Nature Machine Intelligence^ (under review)  </v>
+        <v xml:space="preserve">Nature Machine Intelligence^ </v>
       </c>
       <c r="C66" t="str">
         <f>Sheet1!D68</f>

--- a/Contributions_table.xlsx
+++ b/Contributions_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lc/PycharmProjects/publications/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77F21575-6670-ED40-ADF6-0A7E47834D2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65C033A6-B9F8-F441-960D-161BD8012A45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{5AA491FB-7947-2140-ACD9-201A623594D0}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="368">
   <si>
     <t xml:space="preserve">EMNLP (under review) </t>
   </si>
@@ -1234,9 +1234,6 @@
   </si>
   <si>
     <t>tam2024llm</t>
-  </si>
-  <si>
-    <t>BabyLM</t>
   </si>
 </sst>
 </file>
@@ -1375,7 +1372,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
@@ -1391,6 +1388,9 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -12242,122 +12242,124 @@
     <col min="4" max="4" width="29.5" customWidth="1"/>
     <col min="5" max="5" width="38" customWidth="1"/>
     <col min="6" max="6" width="12.83203125" customWidth="1"/>
-    <col min="15" max="15" width="14" customWidth="1"/>
+    <col min="13" max="13" width="20.33203125" customWidth="1"/>
+    <col min="14" max="15" width="14" customWidth="1"/>
+    <col min="16" max="16" width="15" customWidth="1"/>
     <col min="21" max="21" width="10.5" customWidth="1"/>
     <col min="22" max="22" width="13.6640625" customWidth="1"/>
     <col min="25" max="25" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37">
-      <c r="A1" t="s">
+    <row r="1" spans="1:37" s="15" customFormat="1" ht="51">
+      <c r="A1" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="15" t="s">
         <v>329</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="15" t="s">
         <v>289</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="15" t="s">
         <v>247</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="15" t="s">
         <v>259</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="15" t="s">
         <v>288</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="15" t="s">
         <v>284</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="15" t="s">
         <v>283</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="15" t="s">
         <v>285</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="15" t="s">
         <v>261</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="15" t="s">
         <v>263</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="15" t="s">
         <v>260</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" s="15" t="s">
         <v>262</v>
       </c>
-      <c r="W1" t="s">
+      <c r="W1" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="X1" t="s">
+      <c r="X1" s="15" t="s">
         <v>160</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Y1" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="Z1" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AA1" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AB1" s="15" t="s">
         <v>294</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AC1" s="15" t="s">
         <v>293</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AD1" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AE1" s="15" t="s">
         <v>257</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AF1" s="15" t="s">
         <v>248</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AG1" s="15" t="s">
         <v>248</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AH1" s="15" t="s">
         <v>249</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AI1" s="15" t="s">
         <v>250</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AJ1" s="15" t="s">
         <v>257</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AK1" s="15" t="s">
         <v>290</v>
       </c>
     </row>
@@ -17454,7 +17456,7 @@
         <v>0</v>
       </c>
       <c r="AF67">
-        <f t="shared" ref="AF67:AF79" si="22">IF(SUM(T67,P67)&gt;0,1,0)</f>
+        <f t="shared" ref="AF67:AF81" si="22">IF(SUM(T67,P67)&gt;0,1,0)</f>
         <v>1</v>
       </c>
       <c r="AG67" t="str">
@@ -17843,24 +17845,24 @@
         <v>0</v>
       </c>
       <c r="AF72">
-        <f t="shared" si="22"/>
+        <f t="shared" ref="AF72:AF98" si="24">IF(SUM(T72,P72)&gt;0,1,0)</f>
         <v>1</v>
       </c>
       <c r="AG72" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="AG72:AG98" si="25">IF(AF72,E72,"")</f>
         <v>knots</v>
       </c>
       <c r="AH72" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="AH72:AH98" si="26">IF(W72,E72,"")</f>
         <v>knots</v>
       </c>
       <c r="AI72" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" ref="AI72:AI98" si="27">IF(Y72,E72,"")</f>
         <v>knots</v>
       </c>
-      <c r="AJ72" t="str">
-        <f t="shared" si="14"/>
-        <v/>
+      <c r="AK72">
+        <f t="shared" ref="AK72:AK98" si="28">IF(Z72+T72&gt;1,1,0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:37">
@@ -17931,11 +17933,23 @@
         <v>0</v>
       </c>
       <c r="AF73">
-        <f t="shared" si="22"/>
-        <v>1</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
+      </c>
+      <c r="AG73" t="str">
+        <f t="shared" si="25"/>
+        <v>polo2024sloth</v>
+      </c>
+      <c r="AH73" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="AI73" t="str">
+        <f t="shared" si="27"/>
+        <v>polo2024sloth</v>
       </c>
       <c r="AK73">
-        <f t="shared" ref="AK73:AK77" si="24">IF(Z73+T73&gt;1,1,0)</f>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
     </row>
@@ -18016,11 +18030,23 @@
         <v>0</v>
       </c>
       <c r="AF74">
-        <f t="shared" si="22"/>
-        <v>1</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
+      </c>
+      <c r="AG74" t="str">
+        <f t="shared" si="25"/>
+        <v>choshen2024hitchhiker</v>
+      </c>
+      <c r="AH74" t="str">
+        <f t="shared" si="26"/>
+        <v>choshen2024hitchhiker</v>
+      </c>
+      <c r="AI74" t="str">
+        <f t="shared" si="27"/>
+        <v>choshen2024hitchhiker</v>
       </c>
       <c r="AK74">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
     </row>
@@ -18076,15 +18102,27 @@
         <v>2</v>
       </c>
       <c r="AE75">
-        <f t="shared" ref="AE75" si="25">IF(SUM(Y75,T75,P75,W75),0,1)</f>
+        <f t="shared" ref="AE75" si="29">IF(SUM(Y75,T75,P75,W75),0,1)</f>
         <v>0</v>
       </c>
       <c r="AF75">
-        <f t="shared" ref="AF75" si="26">IF(SUM(T75,P75)&gt;0,1,0)</f>
-        <v>1</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
+      </c>
+      <c r="AG75" t="str">
+        <f t="shared" si="25"/>
+        <v>perlitz2024llm</v>
+      </c>
+      <c r="AH75" t="str">
+        <f t="shared" si="26"/>
+        <v>perlitz2024llm</v>
+      </c>
+      <c r="AI75" t="str">
+        <f t="shared" si="27"/>
+        <v/>
       </c>
       <c r="AK75">
-        <f t="shared" ref="AK75" si="27">IF(Z75+T75&gt;1,1,0)</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
     </row>
@@ -18131,8 +18169,24 @@
       <c r="AE76">
         <v>1</v>
       </c>
+      <c r="AF76">
+        <f t="shared" si="24"/>
+        <v>1</v>
+      </c>
+      <c r="AG76" t="str">
+        <f t="shared" si="25"/>
+        <v>shabtay2025livexiv</v>
+      </c>
+      <c r="AH76" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="AI76" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
       <c r="AK76">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
     </row>
@@ -18198,27 +18252,23 @@
         <v>0</v>
       </c>
       <c r="AF77">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="AG77" t="str">
-        <f>IF(AF77,E77,"")</f>
+        <f t="shared" si="25"/>
         <v>hu-etal-2024-findings</v>
       </c>
       <c r="AH77" t="str">
-        <f>IF(W77,E77,"")</f>
+        <f t="shared" si="26"/>
         <v>hu-etal-2024-findings</v>
       </c>
       <c r="AI77" t="str">
-        <f>IF(Y77,E77,"")</f>
+        <f t="shared" si="27"/>
         <v>hu-etal-2024-findings</v>
       </c>
-      <c r="AJ77" t="str">
-        <f>IF(AE77,E77,"")</f>
-        <v/>
-      </c>
       <c r="AK77">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
     </row>
@@ -18281,24 +18331,24 @@
         <v>0</v>
       </c>
       <c r="AF78">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="AG78" t="str">
-        <f>IF(AF78,E78,"")</f>
+        <f t="shared" si="25"/>
         <v>tam2024llm</v>
       </c>
       <c r="AH78" t="str">
-        <f>IF(W78,E78,"")</f>
+        <f t="shared" si="26"/>
         <v>tam2024llm</v>
       </c>
       <c r="AI78" t="str">
-        <f>IF(Y78,E78,"")</f>
+        <f t="shared" si="27"/>
         <v>tam2024llm</v>
       </c>
-      <c r="AJ78" t="str">
-        <f>IF(AE78,E78,"")</f>
-        <v/>
+      <c r="AK78">
+        <f t="shared" si="28"/>
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:37">
@@ -18344,13 +18394,32 @@
       <c r="AA79">
         <v>1</v>
       </c>
+      <c r="AD79">
+        <v>1</v>
+      </c>
       <c r="AE79">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AF79">
-        <f t="shared" si="22"/>
-        <v>1</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
+      </c>
+      <c r="AG79" t="str">
+        <f t="shared" si="25"/>
+        <v>singh-etal-2025-global</v>
+      </c>
+      <c r="AH79" t="str">
+        <f t="shared" si="26"/>
+        <v>singh-etal-2025-global</v>
+      </c>
+      <c r="AI79" t="str">
+        <f t="shared" si="27"/>
+        <v>singh-etal-2025-global</v>
+      </c>
+      <c r="AK79">
+        <f t="shared" si="28"/>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:37">
@@ -18373,18 +18442,53 @@
       <c r="H80">
         <v>1</v>
       </c>
+      <c r="O80">
+        <v>1</v>
+      </c>
+      <c r="R80">
+        <v>1</v>
+      </c>
+      <c r="T80">
+        <v>1</v>
+      </c>
+      <c r="X80">
+        <v>1</v>
+      </c>
       <c r="AA80">
         <v>1</v>
       </c>
+      <c r="AD80">
+        <v>1</v>
+      </c>
+      <c r="AF80">
+        <f t="shared" si="24"/>
+        <v>1</v>
+      </c>
+      <c r="AG80" t="str">
+        <f t="shared" si="25"/>
+        <v>ashurytahan2025mightytorrbenchmarktable</v>
+      </c>
+      <c r="AH80" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="AI80" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AK80">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="81" spans="1:33">
+    <row r="81" spans="1:37">
       <c r="A81">
         <f t="shared" si="23"/>
         <v>80</v>
       </c>
       <c r="B81" t="str" cm="1">
         <f t="array" ref="B81">_xlfn.IFS(ISBLANK(D81),"",ISBLANK(C81),"no venue",ISBLANK(E81),"no bib",ISNUMBER(SEARCH("xiv", C81)),"arxiv",SUM(I81:AA81)&lt;3,"no categories",TRUE,"")</f>
-        <v>no categories</v>
+        <v/>
       </c>
       <c r="C81" t="s">
         <v>312</v>
@@ -18401,11 +18505,61 @@
       <c r="H81">
         <v>1</v>
       </c>
+      <c r="K81">
+        <v>1</v>
+      </c>
+      <c r="O81">
+        <v>1</v>
+      </c>
+      <c r="Q81">
+        <v>1</v>
+      </c>
+      <c r="R81">
+        <v>1</v>
+      </c>
+      <c r="T81">
+        <v>1</v>
+      </c>
+      <c r="U81">
+        <v>1</v>
+      </c>
+      <c r="W81">
+        <v>1</v>
+      </c>
+      <c r="X81">
+        <v>1</v>
+      </c>
+      <c r="Y81">
+        <v>1</v>
+      </c>
       <c r="AA81">
         <v>1</v>
       </c>
+      <c r="AD81">
+        <v>1</v>
+      </c>
+      <c r="AF81">
+        <f t="shared" si="24"/>
+        <v>1</v>
+      </c>
+      <c r="AG81" t="str">
+        <f t="shared" si="25"/>
+        <v>habba-etal-2025-dove</v>
+      </c>
+      <c r="AH81" t="str">
+        <f t="shared" si="26"/>
+        <v>habba-etal-2025-dove</v>
+      </c>
+      <c r="AI81" t="str">
+        <f t="shared" si="27"/>
+        <v>habba-etal-2025-dove</v>
+      </c>
+      <c r="AK81">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="82" spans="1:33">
+    <row r="82" spans="1:37">
       <c r="A82">
         <f t="shared" si="23"/>
         <v>81</v>
@@ -18429,11 +18583,52 @@
       <c r="H82">
         <v>1</v>
       </c>
-      <c r="AA82">
-        <v>1</v>
+      <c r="O82">
+        <v>1</v>
+      </c>
+      <c r="Q82">
+        <v>1</v>
+      </c>
+      <c r="S82">
+        <v>1</v>
+      </c>
+      <c r="U82">
+        <v>1</v>
+      </c>
+      <c r="X82">
+        <v>1</v>
+      </c>
+      <c r="Y82">
+        <v>1</v>
+      </c>
+      <c r="Z82">
+        <v>1</v>
+      </c>
+      <c r="AD82">
+        <v>1</v>
+      </c>
+      <c r="AF82">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AG82" t="str">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="AH82" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="AI82" t="str">
+        <f t="shared" si="27"/>
+        <v>saroufim2025neurips</v>
+      </c>
+      <c r="AK82">
+        <f t="shared" si="28"/>
+        <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:33">
+    <row r="83" spans="1:37">
       <c r="A83">
         <f t="shared" si="23"/>
         <v>82</v>
@@ -18456,11 +18651,49 @@
       <c r="H83">
         <v>1</v>
       </c>
+      <c r="I83">
+        <v>1</v>
+      </c>
+      <c r="N83">
+        <v>1</v>
+      </c>
+      <c r="Q83">
+        <v>1</v>
+      </c>
+      <c r="S83">
+        <v>1</v>
+      </c>
+      <c r="V83">
+        <v>1</v>
+      </c>
       <c r="AA83">
         <v>1</v>
       </c>
+      <c r="AD83">
+        <v>1</v>
+      </c>
+      <c r="AF83">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AG83" t="str">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="AH83" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="AI83" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AK83">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="1:33">
+    <row r="84" spans="1:37">
       <c r="A84">
         <f t="shared" si="23"/>
         <v>83</v>
@@ -18487,8 +18720,31 @@
       <c r="AA84">
         <v>1</v>
       </c>
+      <c r="AD84">
+        <v>1</v>
+      </c>
+      <c r="AF84">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AG84" t="str">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="AH84" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="AI84" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AK84">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="1:33" ht="17">
+    <row r="85" spans="1:37">
       <c r="A85">
         <f t="shared" si="23"/>
         <v>84</v>
@@ -18515,9 +18771,31 @@
       <c r="AA85">
         <v>1</v>
       </c>
-      <c r="AG85" s="8"/>
+      <c r="AD85">
+        <v>1</v>
+      </c>
+      <c r="AF85">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AG85" t="str">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="AH85" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="AI85" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AK85">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="1:33" ht="17">
+    <row r="86" spans="1:37">
       <c r="A86">
         <f t="shared" si="23"/>
         <v>85</v>
@@ -18544,9 +18822,31 @@
       <c r="AA86">
         <v>1</v>
       </c>
-      <c r="AG86" s="8"/>
+      <c r="AD86">
+        <v>1</v>
+      </c>
+      <c r="AF86">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AG86" t="str">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="AH86" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="AI86" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AK86">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="1:33" ht="17">
+    <row r="87" spans="1:37">
       <c r="A87">
         <f t="shared" si="23"/>
         <v>86</v>
@@ -18573,9 +18873,31 @@
       <c r="AA87">
         <v>1</v>
       </c>
-      <c r="AG87" s="8"/>
+      <c r="AD87">
+        <v>1</v>
+      </c>
+      <c r="AF87">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AG87" t="str">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="AH87" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="AI87" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AK87">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="1:33" ht="17">
+    <row r="88" spans="1:37">
       <c r="A88">
         <f t="shared" si="23"/>
         <v>87</v>
@@ -18602,9 +18924,31 @@
       <c r="AA88">
         <v>1</v>
       </c>
-      <c r="AG88" s="8"/>
+      <c r="AD88">
+        <v>1</v>
+      </c>
+      <c r="AF88">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AG88" t="str">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="AH88" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="AI88" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AK88">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="1:33" ht="17">
+    <row r="89" spans="1:37">
       <c r="A89">
         <f t="shared" si="23"/>
         <v>88</v>
@@ -18631,9 +18975,31 @@
       <c r="AA89">
         <v>1</v>
       </c>
-      <c r="AG89" s="8"/>
+      <c r="AD89">
+        <v>1</v>
+      </c>
+      <c r="AF89">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AG89" t="str">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="AH89" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="AI89" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AK89">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="90" spans="1:33" ht="17">
+    <row r="90" spans="1:37">
       <c r="A90">
         <f t="shared" si="23"/>
         <v>89</v>
@@ -18659,9 +19025,31 @@
       <c r="AA90">
         <v>1</v>
       </c>
-      <c r="AG90" s="8"/>
+      <c r="AD90">
+        <v>1</v>
+      </c>
+      <c r="AF90">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AG90" t="str">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="AH90" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="AI90" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AK90">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="91" spans="1:33" ht="17">
+    <row r="91" spans="1:37">
       <c r="A91">
         <f t="shared" si="23"/>
         <v>90</v>
@@ -18685,19 +19073,59 @@
       <c r="H91">
         <v>1</v>
       </c>
-      <c r="AG91" s="8"/>
+      <c r="N91">
+        <v>1</v>
+      </c>
+      <c r="O91">
+        <v>1</v>
+      </c>
+      <c r="R91">
+        <v>1</v>
+      </c>
+      <c r="U91">
+        <v>1</v>
+      </c>
+      <c r="Y91">
+        <v>1</v>
+      </c>
+      <c r="AA91">
+        <v>1</v>
+      </c>
+      <c r="AD91">
+        <v>1</v>
+      </c>
+      <c r="AF91">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AG91" t="str">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="AH91" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="AI91" t="str">
+        <f t="shared" si="27"/>
+        <v>chang2025globalpiqaevaluatingphysical</v>
+      </c>
+      <c r="AK91">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="1:33" ht="17">
+    <row r="92" spans="1:37">
       <c r="A92">
         <f t="shared" si="23"/>
         <v>91</v>
       </c>
       <c r="B92" t="str" cm="1">
         <f t="array" ref="B92">_xlfn.IFS(ISBLANK(D92),"",ISBLANK(C92),"no venue",ISBLANK(E92),"no bib",ISNUMBER(SEARCH("xiv", C92)),"arxiv",SUM(I92:AA92)&lt;3,"no categories",TRUE,"")</f>
-        <v>no categories</v>
+        <v/>
       </c>
       <c r="C92" s="2" t="s">
-        <v>368</v>
+        <v>310</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>355</v>
@@ -18711,9 +19139,67 @@
       <c r="H92">
         <v>1</v>
       </c>
-      <c r="AG92" s="8"/>
+      <c r="I92">
+        <v>1</v>
+      </c>
+      <c r="N92">
+        <v>1</v>
+      </c>
+      <c r="O92">
+        <v>1</v>
+      </c>
+      <c r="Q92">
+        <v>1</v>
+      </c>
+      <c r="R92">
+        <v>1</v>
+      </c>
+      <c r="S92">
+        <v>1</v>
+      </c>
+      <c r="T92">
+        <v>1</v>
+      </c>
+      <c r="U92">
+        <v>1</v>
+      </c>
+      <c r="V92">
+        <v>1</v>
+      </c>
+      <c r="Z92">
+        <v>1</v>
+      </c>
+      <c r="AA92">
+        <v>1</v>
+      </c>
+      <c r="AB92">
+        <v>1</v>
+      </c>
+      <c r="AD92">
+        <v>1</v>
+      </c>
+      <c r="AF92">
+        <f t="shared" si="24"/>
+        <v>1</v>
+      </c>
+      <c r="AG92" t="str">
+        <f t="shared" si="25"/>
+        <v>charpentier-etal-2025-findings</v>
+      </c>
+      <c r="AH92" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="AI92" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AK92">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
     </row>
-    <row r="93" spans="1:33" ht="17">
+    <row r="93" spans="1:37">
       <c r="A93">
         <f t="shared" si="23"/>
         <v>92</v>
@@ -18734,9 +19220,55 @@
       <c r="H93">
         <v>1</v>
       </c>
-      <c r="AG93" s="8"/>
+      <c r="I93">
+        <v>1</v>
+      </c>
+      <c r="L93">
+        <v>1</v>
+      </c>
+      <c r="N93">
+        <v>1</v>
+      </c>
+      <c r="Q93">
+        <v>1</v>
+      </c>
+      <c r="S93">
+        <v>1</v>
+      </c>
+      <c r="Y93">
+        <v>1</v>
+      </c>
+      <c r="Z93">
+        <v>1</v>
+      </c>
+      <c r="AA93">
+        <v>1</v>
+      </c>
+      <c r="AD93">
+        <v>1</v>
+      </c>
+      <c r="AF93">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AG93" t="str">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="AH93" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="AI93">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AK93">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="1:33" ht="17">
+    <row r="94" spans="1:37">
       <c r="A94">
         <f t="shared" si="23"/>
         <v>93</v>
@@ -18760,9 +19292,52 @@
       <c r="H94">
         <v>1</v>
       </c>
-      <c r="AG94" s="8"/>
+      <c r="O94">
+        <v>1</v>
+      </c>
+      <c r="R94">
+        <v>1</v>
+      </c>
+      <c r="S94">
+        <v>1</v>
+      </c>
+      <c r="U94">
+        <v>1</v>
+      </c>
+      <c r="W94">
+        <v>1</v>
+      </c>
+      <c r="Y94">
+        <v>1</v>
+      </c>
+      <c r="AA94">
+        <v>1</v>
+      </c>
+      <c r="AD94">
+        <v>1</v>
+      </c>
+      <c r="AF94">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AG94" t="str">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="AH94" t="str">
+        <f t="shared" si="26"/>
+        <v>suarez2026commonlid</v>
+      </c>
+      <c r="AI94" t="str">
+        <f t="shared" si="27"/>
+        <v>suarez2026commonlid</v>
+      </c>
+      <c r="AK94">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="1:33" ht="17">
+    <row r="95" spans="1:37">
       <c r="A95">
         <f t="shared" si="23"/>
         <v>94</v>
@@ -18786,9 +19361,52 @@
       <c r="H95">
         <v>1</v>
       </c>
-      <c r="AG95" s="8"/>
+      <c r="K95">
+        <v>1</v>
+      </c>
+      <c r="Q95">
+        <v>1</v>
+      </c>
+      <c r="S95">
+        <v>1</v>
+      </c>
+      <c r="W95">
+        <v>1</v>
+      </c>
+      <c r="Y95">
+        <v>1</v>
+      </c>
+      <c r="Z95">
+        <v>1</v>
+      </c>
+      <c r="AA95">
+        <v>1</v>
+      </c>
+      <c r="AD95">
+        <v>1</v>
+      </c>
+      <c r="AF95">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AG95" t="str">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="AH95" t="str">
+        <f t="shared" si="26"/>
+        <v>rahamim2026will</v>
+      </c>
+      <c r="AI95" t="str">
+        <f t="shared" si="27"/>
+        <v>rahamim2026will</v>
+      </c>
+      <c r="AK95">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="96" spans="1:33" ht="17">
+    <row r="96" spans="1:37">
       <c r="A96">
         <f t="shared" si="23"/>
         <v>95</v>
@@ -18812,9 +19430,43 @@
       <c r="H96">
         <v>1</v>
       </c>
-      <c r="AG96" s="8"/>
+      <c r="O96">
+        <v>1</v>
+      </c>
+      <c r="Q96">
+        <v>1</v>
+      </c>
+      <c r="T96">
+        <v>1</v>
+      </c>
+      <c r="AA96">
+        <v>1</v>
+      </c>
+      <c r="AD96">
+        <v>1</v>
+      </c>
+      <c r="AF96">
+        <f t="shared" si="24"/>
+        <v>1</v>
+      </c>
+      <c r="AG96" t="str">
+        <f t="shared" si="25"/>
+        <v>ashury2026errormap</v>
+      </c>
+      <c r="AH96" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="AI96" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AK96">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="1:33" ht="17">
+    <row r="97" spans="1:37">
       <c r="A97">
         <f t="shared" si="23"/>
         <v>96</v>
@@ -18838,9 +19490,46 @@
       <c r="H97">
         <v>1</v>
       </c>
-      <c r="AG97" s="8"/>
+      <c r="O97">
+        <v>1</v>
+      </c>
+      <c r="P97">
+        <v>1</v>
+      </c>
+      <c r="T97">
+        <v>1</v>
+      </c>
+      <c r="X97">
+        <v>1</v>
+      </c>
+      <c r="AA97">
+        <v>1</v>
+      </c>
+      <c r="AD97">
+        <v>1</v>
+      </c>
+      <c r="AF97">
+        <f t="shared" si="24"/>
+        <v>1</v>
+      </c>
+      <c r="AG97" t="str">
+        <f t="shared" si="25"/>
+        <v>ashury2026robustness</v>
+      </c>
+      <c r="AH97" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="AI97" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AK97">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="1:33" ht="17">
+    <row r="98" spans="1:37">
       <c r="A98">
         <f t="shared" si="23"/>
         <v>97</v>
@@ -18855,9 +19544,28 @@
       <c r="G98">
         <v>2026</v>
       </c>
-      <c r="AG98" s="8"/>
+      <c r="AF98">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AG98" t="str">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="AH98" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="AI98" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AK98">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="1:33" ht="17">
+    <row r="99" spans="1:37" ht="17">
       <c r="A99">
         <f t="shared" si="23"/>
         <v>98</v>
@@ -18874,7 +19582,7 @@
       </c>
       <c r="AG99" s="8"/>
     </row>
-    <row r="100" spans="1:33" ht="17">
+    <row r="100" spans="1:37" ht="17">
       <c r="A100">
         <f t="shared" si="23"/>
         <v>99</v>
@@ -18888,7 +19596,7 @@
       </c>
       <c r="AG100" s="8"/>
     </row>
-    <row r="101" spans="1:33" ht="17">
+    <row r="101" spans="1:37" ht="17">
       <c r="A101">
         <f t="shared" si="23"/>
         <v>100</v>
@@ -18899,7 +19607,7 @@
       </c>
       <c r="AG101" s="8"/>
     </row>
-    <row r="102" spans="1:33" ht="17">
+    <row r="102" spans="1:37" ht="17">
       <c r="A102">
         <f t="shared" si="23"/>
         <v>101</v>
@@ -18910,7 +19618,7 @@
       </c>
       <c r="AG102" s="8"/>
     </row>
-    <row r="103" spans="1:33" ht="17">
+    <row r="103" spans="1:37" ht="17">
       <c r="A103">
         <f t="shared" si="23"/>
         <v>102</v>
@@ -18921,7 +19629,7 @@
       </c>
       <c r="AG103" s="8"/>
     </row>
-    <row r="104" spans="1:33" ht="17">
+    <row r="104" spans="1:37" ht="17">
       <c r="A104">
         <f t="shared" si="23"/>
         <v>103</v>
@@ -18932,7 +19640,7 @@
       </c>
       <c r="AG104" s="8"/>
     </row>
-    <row r="105" spans="1:33" ht="17">
+    <row r="105" spans="1:37" ht="17">
       <c r="A105">
         <f t="shared" si="23"/>
         <v>104</v>
@@ -18943,7 +19651,7 @@
       </c>
       <c r="AG105" s="8"/>
     </row>
-    <row r="106" spans="1:33" ht="17">
+    <row r="106" spans="1:37" ht="17">
       <c r="A106">
         <f t="shared" si="23"/>
         <v>105</v>
@@ -18954,7 +19662,7 @@
       </c>
       <c r="AG106" s="8"/>
     </row>
-    <row r="107" spans="1:33" ht="17">
+    <row r="107" spans="1:37" ht="17">
       <c r="A107">
         <f t="shared" si="23"/>
         <v>106</v>
@@ -18965,7 +19673,7 @@
       </c>
       <c r="AG107" s="8"/>
     </row>
-    <row r="108" spans="1:33" ht="17">
+    <row r="108" spans="1:37" ht="17">
       <c r="A108">
         <f t="shared" si="23"/>
         <v>107</v>
@@ -18976,7 +19684,7 @@
       </c>
       <c r="AG108" s="8"/>
     </row>
-    <row r="109" spans="1:33" ht="17">
+    <row r="109" spans="1:37" ht="17">
       <c r="A109">
         <f t="shared" si="23"/>
         <v>108</v>
@@ -18987,7 +19695,7 @@
       </c>
       <c r="AG109" s="8"/>
     </row>
-    <row r="110" spans="1:33" ht="17">
+    <row r="110" spans="1:37" ht="17">
       <c r="A110">
         <f t="shared" si="23"/>
         <v>109</v>
@@ -18998,7 +19706,7 @@
       </c>
       <c r="AG110" s="8"/>
     </row>
-    <row r="111" spans="1:33" ht="17">
+    <row r="111" spans="1:37" ht="17">
       <c r="A111">
         <f t="shared" si="23"/>
         <v>110</v>
@@ -19009,7 +19717,7 @@
       </c>
       <c r="AG111" s="8"/>
     </row>
-    <row r="112" spans="1:33" ht="17">
+    <row r="112" spans="1:37" ht="17">
       <c r="A112">
         <f t="shared" si="23"/>
         <v>111</v>
@@ -19218,27 +19926,27 @@
         <v>77</v>
       </c>
       <c r="I137">
-        <f t="shared" ref="I137:N137" si="28">SUM(I2:I78)</f>
+        <f t="shared" ref="I137:N137" si="30">SUM(I2:I78)</f>
         <v>6</v>
       </c>
       <c r="J137">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>5</v>
       </c>
       <c r="K137">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>11</v>
       </c>
       <c r="L137">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>2</v>
       </c>
       <c r="M137">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>4</v>
       </c>
       <c r="N137">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>4</v>
       </c>
       <c r="O137">
@@ -19303,7 +20011,7 @@
       </c>
       <c r="AF137">
         <f>SUM(AF2:AF79)</f>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AG137" t="str">
         <f>IF(AF137,E80,"")</f>
@@ -19327,83 +20035,83 @@
         <v>180</v>
       </c>
       <c r="H138" s="7">
-        <f t="shared" ref="H138:AA138" si="29">H137/$AD$137</f>
+        <f t="shared" ref="H138:AA138" si="31">H137/$AD$137</f>
         <v>1</v>
       </c>
       <c r="I138" s="7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>7.792207792207792E-2</v>
       </c>
       <c r="J138" s="7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>6.4935064935064929E-2</v>
       </c>
       <c r="K138" s="7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.14285714285714285</v>
       </c>
       <c r="L138" s="7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>2.5974025974025976E-2</v>
       </c>
       <c r="M138" s="7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>5.1948051948051951E-2</v>
       </c>
       <c r="N138" s="7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>5.1948051948051951E-2</v>
       </c>
       <c r="O138" s="7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.50649350649350644</v>
       </c>
       <c r="P138" s="7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.54545454545454541</v>
       </c>
       <c r="Q138" s="7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.55844155844155841</v>
       </c>
       <c r="R138" s="7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.27272727272727271</v>
       </c>
       <c r="S138" s="7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.41558441558441561</v>
       </c>
       <c r="T138" s="7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.51948051948051943</v>
       </c>
       <c r="U138" s="7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.19480519480519481</v>
       </c>
       <c r="V138" s="7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.40259740259740262</v>
       </c>
       <c r="W138" s="7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.42857142857142855</v>
       </c>
       <c r="X138" s="7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.45454545454545453</v>
       </c>
       <c r="Y138" s="7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.45454545454545453</v>
       </c>
       <c r="Z138" s="7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.51948051948051943</v>
       </c>
       <c r="AA138" s="7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.96103896103896103</v>
       </c>
       <c r="AB138" s="7"/>

--- a/Contributions_table.xlsx
+++ b/Contributions_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lc/PycharmProjects/publications/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65C033A6-B9F8-F441-960D-161BD8012A45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F523ED88-BD44-3340-8BC2-590AB4447B0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{5AA491FB-7947-2140-ACD9-201A623594D0}"/>
   </bookViews>
@@ -19229,6 +19229,9 @@
       <c r="N93">
         <v>1</v>
       </c>
+      <c r="P93">
+        <v>1</v>
+      </c>
       <c r="Q93">
         <v>1</v>
       </c>
@@ -19249,11 +19252,11 @@
       </c>
       <c r="AF93">
         <f t="shared" si="24"/>
+        <v>1</v>
+      </c>
+      <c r="AG93">
+        <f t="shared" si="25"/>
         <v>0</v>
-      </c>
-      <c r="AG93" t="str">
-        <f t="shared" si="25"/>
-        <v/>
       </c>
       <c r="AH93" t="str">
         <f t="shared" si="26"/>
@@ -19364,6 +19367,9 @@
       <c r="K95">
         <v>1</v>
       </c>
+      <c r="P95">
+        <v>1</v>
+      </c>
       <c r="Q95">
         <v>1</v>
       </c>
@@ -19387,11 +19393,11 @@
       </c>
       <c r="AF95">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG95" t="str">
         <f t="shared" si="25"/>
-        <v/>
+        <v>rahamim2026will</v>
       </c>
       <c r="AH95" t="str">
         <f t="shared" si="26"/>

--- a/Contributions_table.xlsx
+++ b/Contributions_table.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lc/PycharmProjects/publications/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F523ED88-BD44-3340-8BC2-590AB4447B0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A9244A3-14BF-234E-B5D8-A328E44EA3C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{5AA491FB-7947-2140-ACD9-201A623594D0}"/>
   </bookViews>
@@ -1092,9 +1092,6 @@
     <t>hu-etal-2024-findings</t>
   </si>
   <si>
-    <t>singh-etal-2025-global</t>
-  </si>
-  <si>
     <t>The mighty torr: A benchmark for table reasoning and robustness</t>
   </si>
   <si>
@@ -1149,9 +1146,6 @@
     <t>JML</t>
   </si>
   <si>
-    <t>wilcox2025bigger</t>
-  </si>
-  <si>
     <t>zipnn</t>
   </si>
   <si>
@@ -1234,6 +1228,12 @@
   </si>
   <si>
     <t>tam2024llm</t>
+  </si>
+  <si>
+    <t>wilcox2024bigger</t>
+  </si>
+  <si>
+    <t>singh2024global</t>
   </si>
 </sst>
 </file>
@@ -12255,7 +12255,7 @@
         <v>182</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C1" s="15" t="s">
         <v>289</v>
@@ -15210,7 +15210,7 @@
         <v>DBLP:conf/emnlp/ChoshenVDSK23</v>
       </c>
       <c r="AJ38" t="str">
-        <f t="shared" ref="AJ38:AJ72" si="14">IF(AE38,E38,"")</f>
+        <f t="shared" ref="AJ38:AJ70" si="14">IF(AE38,E38,"")</f>
         <v/>
       </c>
     </row>
@@ -16481,7 +16481,7 @@
         <v/>
       </c>
       <c r="C55" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D55" t="s">
         <v>57</v>
@@ -17161,7 +17161,7 @@
         <v>63</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D64" t="s">
         <v>53</v>
@@ -17314,13 +17314,13 @@
         <v/>
       </c>
       <c r="C66" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D66" t="s">
         <v>163</v>
       </c>
       <c r="E66" s="12" t="s">
-        <v>339</v>
+        <v>366</v>
       </c>
       <c r="F66" t="s">
         <v>162</v>
@@ -17376,16 +17376,16 @@
         <v>1</v>
       </c>
       <c r="AG66" t="str">
-        <f t="shared" ref="AG66:AG72" si="19">IF(AF66,E66,"")</f>
-        <v>wilcox2025bigger</v>
+        <f t="shared" ref="AG66:AG71" si="19">IF(AF66,E66,"")</f>
+        <v>wilcox2024bigger</v>
       </c>
       <c r="AH66" t="str">
-        <f t="shared" ref="AH66:AH72" si="20">IF(W66,E66,"")</f>
-        <v>wilcox2025bigger</v>
+        <f t="shared" ref="AH66:AH71" si="20">IF(W66,E66,"")</f>
+        <v>wilcox2024bigger</v>
       </c>
       <c r="AI66" t="str">
-        <f t="shared" ref="AI66:AI72" si="21">IF(Y66,E66,"")</f>
-        <v>wilcox2025bigger</v>
+        <f t="shared" ref="AI66:AI71" si="21">IF(Y66,E66,"")</f>
+        <v>wilcox2024bigger</v>
       </c>
       <c r="AJ66" t="str">
         <f t="shared" si="14"/>
@@ -17456,7 +17456,7 @@
         <v>0</v>
       </c>
       <c r="AF67">
-        <f t="shared" ref="AF67:AF81" si="22">IF(SUM(T67,P67)&gt;0,1,0)</f>
+        <f t="shared" ref="AF67:AF71" si="22">IF(SUM(T67,P67)&gt;0,1,0)</f>
         <v>1</v>
       </c>
       <c r="AG67" t="str">
@@ -17486,7 +17486,7 @@
         <v/>
       </c>
       <c r="C68" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>186</v>
@@ -17875,7 +17875,7 @@
         <v/>
       </c>
       <c r="C73" t="s">
-        <v>292</v>
+        <v>185</v>
       </c>
       <c r="D73" s="5" t="s">
         <v>275</v>
@@ -18288,7 +18288,7 @@
         <v>305</v>
       </c>
       <c r="E78" s="9" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="G78">
         <v>2024</v>
@@ -18367,7 +18367,7 @@
         <v>295</v>
       </c>
       <c r="E79" s="12" t="s">
-        <v>320</v>
+        <v>367</v>
       </c>
       <c r="G79">
         <v>2024</v>
@@ -18407,15 +18407,15 @@
       </c>
       <c r="AG79" t="str">
         <f t="shared" si="25"/>
-        <v>singh-etal-2025-global</v>
+        <v>singh2024global</v>
       </c>
       <c r="AH79" t="str">
         <f t="shared" si="26"/>
-        <v>singh-etal-2025-global</v>
+        <v>singh2024global</v>
       </c>
       <c r="AI79" t="str">
         <f t="shared" si="27"/>
-        <v>singh-etal-2025-global</v>
+        <v>singh2024global</v>
       </c>
       <c r="AK79">
         <f t="shared" si="28"/>
@@ -18428,13 +18428,13 @@
         <v>79</v>
       </c>
       <c r="C80" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E80" s="12" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G80">
         <v>2025</v>
@@ -18494,10 +18494,10 @@
         <v>312</v>
       </c>
       <c r="D81" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="E81" s="12" t="s">
         <v>323</v>
-      </c>
-      <c r="E81" s="12" t="s">
-        <v>324</v>
       </c>
       <c r="G81">
         <v>2025</v>
@@ -18572,10 +18572,10 @@
         <v>28</v>
       </c>
       <c r="D82" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="E82" s="12" t="s">
         <v>325</v>
-      </c>
-      <c r="E82" s="12" t="s">
-        <v>326</v>
       </c>
       <c r="G82">
         <v>2025</v>
@@ -18634,16 +18634,16 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C83" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E83" s="12" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G83">
         <v>2026</v>
@@ -18706,10 +18706,10 @@
         <v>291</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E84" s="12" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G84">
         <v>2025</v>
@@ -18717,6 +18717,30 @@
       <c r="H84">
         <v>1</v>
       </c>
+      <c r="O84">
+        <v>1</v>
+      </c>
+      <c r="Q84">
+        <v>1</v>
+      </c>
+      <c r="R84">
+        <v>1</v>
+      </c>
+      <c r="S84">
+        <v>1</v>
+      </c>
+      <c r="T84">
+        <v>1</v>
+      </c>
+      <c r="U84">
+        <v>1</v>
+      </c>
+      <c r="W84">
+        <v>1</v>
+      </c>
+      <c r="Y84">
+        <v>1</v>
+      </c>
       <c r="AA84">
         <v>1</v>
       </c>
@@ -18725,19 +18749,19 @@
       </c>
       <c r="AF84">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG84" t="str">
         <f t="shared" si="25"/>
-        <v/>
+        <v>guertler2025textarena</v>
       </c>
       <c r="AH84" t="str">
         <f t="shared" si="26"/>
-        <v/>
+        <v>guertler2025textarena</v>
       </c>
       <c r="AI84" t="str">
         <f t="shared" si="27"/>
-        <v/>
+        <v>guertler2025textarena</v>
       </c>
       <c r="AK84">
         <f t="shared" si="28"/>
@@ -18757,10 +18781,10 @@
         <v>291</v>
       </c>
       <c r="D85" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="E85" s="12" t="s">
         <v>332</v>
-      </c>
-      <c r="E85" s="12" t="s">
-        <v>333</v>
       </c>
       <c r="G85">
         <v>2025</v>
@@ -18768,6 +18792,15 @@
       <c r="H85">
         <v>1</v>
       </c>
+      <c r="P85">
+        <v>1</v>
+      </c>
+      <c r="Q85">
+        <v>1</v>
+      </c>
+      <c r="S85">
+        <v>1</v>
+      </c>
       <c r="AA85">
         <v>1</v>
       </c>
@@ -18776,11 +18809,11 @@
       </c>
       <c r="AF85">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG85" t="str">
         <f t="shared" si="25"/>
-        <v/>
+        <v>zhang2025can</v>
       </c>
       <c r="AH85" t="str">
         <f t="shared" si="26"/>
@@ -18805,18 +18838,24 @@
         <v>arxiv</v>
       </c>
       <c r="C86" t="s">
+        <v>334</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="E86" s="12" t="s">
         <v>335</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="E86" s="12" t="s">
-        <v>336</v>
       </c>
       <c r="G86">
         <v>2025</v>
       </c>
       <c r="H86">
+        <v>1</v>
+      </c>
+      <c r="M86">
+        <v>1</v>
+      </c>
+      <c r="Q86">
         <v>1</v>
       </c>
       <c r="AA86">
@@ -18853,21 +18892,33 @@
       </c>
       <c r="B87" t="str" cm="1">
         <f t="array" ref="B87">_xlfn.IFS(ISBLANK(D87),"",ISBLANK(C87),"no venue",ISBLANK(E87),"no bib",ISNUMBER(SEARCH("xiv", C87)),"arxiv",SUM(I87:AA87)&lt;3,"no categories",TRUE,"")</f>
-        <v>no categories</v>
+        <v/>
       </c>
       <c r="C87" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E87" s="12" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G87">
         <v>2025</v>
       </c>
       <c r="H87">
+        <v>1</v>
+      </c>
+      <c r="O87">
+        <v>1</v>
+      </c>
+      <c r="W87">
+        <v>1</v>
+      </c>
+      <c r="Y87">
+        <v>1</v>
+      </c>
+      <c r="Z87">
         <v>1</v>
       </c>
       <c r="AA87">
@@ -18886,11 +18937,11 @@
       </c>
       <c r="AH87" t="str">
         <f t="shared" si="26"/>
-        <v/>
+        <v>zipnn</v>
       </c>
       <c r="AI87" t="str">
         <f t="shared" si="27"/>
-        <v/>
+        <v>zipnn</v>
       </c>
       <c r="AK87">
         <f t="shared" si="28"/>
@@ -18904,21 +18955,27 @@
       </c>
       <c r="B88" t="str" cm="1">
         <f t="array" ref="B88">_xlfn.IFS(ISBLANK(D88),"",ISBLANK(C88),"no venue",ISBLANK(E88),"no bib",ISNUMBER(SEARCH("xiv", C88)),"arxiv",SUM(I88:AA88)&lt;3,"no categories",TRUE,"")</f>
-        <v>no categories</v>
+        <v/>
       </c>
       <c r="C88" t="s">
         <v>292</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E88" s="9" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="G88">
         <v>2025</v>
       </c>
       <c r="H88">
+        <v>1</v>
+      </c>
+      <c r="Q88">
+        <v>1</v>
+      </c>
+      <c r="S88">
         <v>1</v>
       </c>
       <c r="AA88">
@@ -18958,18 +19015,24 @@
         <v>arxiv</v>
       </c>
       <c r="C89" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E89" s="12" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="G89">
         <v>2025</v>
       </c>
       <c r="H89">
+        <v>1</v>
+      </c>
+      <c r="Q89">
+        <v>1</v>
+      </c>
+      <c r="S89">
         <v>1</v>
       </c>
       <c r="AA89">
@@ -19005,16 +19068,16 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C90" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E90" s="12" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="G90">
         <v>2026</v>
@@ -19022,6 +19085,39 @@
       <c r="H90">
         <v>1</v>
       </c>
+      <c r="I90">
+        <v>1</v>
+      </c>
+      <c r="N90">
+        <v>1</v>
+      </c>
+      <c r="O90">
+        <v>1</v>
+      </c>
+      <c r="R90">
+        <v>1</v>
+      </c>
+      <c r="S90">
+        <v>1</v>
+      </c>
+      <c r="T90">
+        <v>1</v>
+      </c>
+      <c r="U90">
+        <v>1</v>
+      </c>
+      <c r="V90">
+        <v>1</v>
+      </c>
+      <c r="W90">
+        <v>1</v>
+      </c>
+      <c r="X90">
+        <v>1</v>
+      </c>
+      <c r="Y90">
+        <v>1</v>
+      </c>
       <c r="AA90">
         <v>1</v>
       </c>
@@ -19030,19 +19126,19 @@
       </c>
       <c r="AF90">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG90" t="str">
         <f t="shared" si="25"/>
-        <v/>
+        <v>jumelet2025babybabellm</v>
       </c>
       <c r="AH90" t="str">
         <f t="shared" si="26"/>
-        <v/>
+        <v>jumelet2025babybabellm</v>
       </c>
       <c r="AI90" t="str">
         <f t="shared" si="27"/>
-        <v/>
+        <v>jumelet2025babybabellm</v>
       </c>
       <c r="AK90">
         <f t="shared" si="28"/>
@@ -19059,13 +19155,13 @@
         <v>arxiv</v>
       </c>
       <c r="C91" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E91" s="12" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="G91">
         <v>2026</v>
@@ -19128,10 +19224,10 @@
         <v>310</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E92" s="12" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="G92">
         <v>2026</v>
@@ -19209,10 +19305,10 @@
         <v>no bib</v>
       </c>
       <c r="C93" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="G93">
         <v>2026</v>
@@ -19281,13 +19377,13 @@
         <v>arxiv</v>
       </c>
       <c r="C94" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D94" s="9" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E94" s="12" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="G94">
         <v>2026</v>
@@ -19350,13 +19446,13 @@
         <v>arxiv</v>
       </c>
       <c r="C95" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E95" s="12" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="G95">
         <v>2026</v>
@@ -19422,13 +19518,13 @@
         <v>arxiv</v>
       </c>
       <c r="C96" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E96" s="12" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="G96">
         <v>2026</v>
@@ -19482,13 +19578,13 @@
         <v>arxiv</v>
       </c>
       <c r="C97" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E97" s="12" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="G97">
         <v>2026</v>
@@ -19545,7 +19641,7 @@
         <v/>
       </c>
       <c r="C98" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G98">
         <v>2026</v>
@@ -19581,7 +19677,7 @@
         <v/>
       </c>
       <c r="C99" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G99">
         <v>2026</v>
@@ -19598,7 +19694,7 @@
         <v/>
       </c>
       <c r="C100" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AG100" s="8"/>
     </row>

--- a/Contributions_table.xlsx
+++ b/Contributions_table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lc/PycharmProjects/publications/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A9244A3-14BF-234E-B5D8-A328E44EA3C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2E6D253-99C5-964F-845D-5B52E82B72C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{5AA491FB-7947-2140-ACD9-201A623594D0}"/>
+    <workbookView xWindow="34560" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{5AA491FB-7947-2140-ACD9-201A623594D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="374">
   <si>
     <t xml:space="preserve">EMNLP (under review) </t>
   </si>
@@ -1235,12 +1235,30 @@
   <si>
     <t>singh2024global</t>
   </si>
+  <si>
+    <t>General Agent Evaluation</t>
+  </si>
+  <si>
+    <t>When AI Benchmarks Plateau: A Systematic Study of Benchmark Saturation</t>
+  </si>
+  <si>
+    <t>akhtar2026aibenchmarksplateausystematic</t>
+  </si>
+  <si>
+    <t>bandel2026generalagentevaluation</t>
+  </si>
+  <si>
+    <t>Position: Agentic Systems Should be General</t>
+  </si>
+  <si>
+    <t>bandel2026agentic</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1350,6 +1368,11 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="28"/>
+      <color rgb="FF222222"/>
+      <name val="NexusSerifWebPro"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1372,7 +1395,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
@@ -1391,6 +1414,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -19637,11 +19661,17 @@
         <v>97</v>
       </c>
       <c r="B98" t="str" cm="1">
-        <f t="array" ref="B98">_xlfn.IFS(ISBLANK(D98),"",ISBLANK(C98),"no venue",ISBLANK(E98),"no bib",ISNUMBER(SEARCH("xiv", C98)),"arxiv",SUM(I98:AA98)&lt;3,"no categories",TRUE,"")</f>
-        <v/>
+        <f t="array" ref="B98">_xlfn.IFS(ISBLANK(D99),"",ISBLANK(C98),"no venue",ISBLANK(#REF!),"no bib",ISNUMBER(SEARCH("xiv", C98)),"arxiv",SUM(I98:AA98)&lt;3,"no categories",TRUE,"")</f>
+        <v>arxiv</v>
       </c>
       <c r="C98" t="s">
         <v>342</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="E98" s="12" t="s">
+        <v>370</v>
       </c>
       <c r="G98">
         <v>2026</v>
@@ -19651,15 +19681,15 @@
         <v>0</v>
       </c>
       <c r="AG98" t="str">
-        <f t="shared" si="25"/>
+        <f>IF(AF98,#REF!,"")</f>
         <v/>
       </c>
       <c r="AH98" t="str">
-        <f t="shared" si="26"/>
+        <f>IF(W98,#REF!,"")</f>
         <v/>
       </c>
       <c r="AI98" t="str">
-        <f t="shared" si="27"/>
+        <f>IF(Y98,#REF!,"")</f>
         <v/>
       </c>
       <c r="AK98">
@@ -19673,28 +19703,43 @@
         <v>98</v>
       </c>
       <c r="B99" t="str" cm="1">
-        <f t="array" ref="B99">_xlfn.IFS(ISBLANK(D99),"",ISBLANK(C99),"no venue",ISBLANK(E99),"no bib",ISNUMBER(SEARCH("xiv", C99)),"arxiv",SUM(I99:AA99)&lt;3,"no categories",TRUE,"")</f>
-        <v/>
+        <f t="array" ref="B99">_xlfn.IFS(ISBLANK(#REF!),"",ISBLANK(C99),"no venue",ISBLANK(#REF!),"no bib",ISNUMBER(SEARCH("xiv", C99)),"arxiv",SUM(I99:AA99)&lt;3,"no categories",TRUE,"")</f>
+        <v>arxiv</v>
       </c>
       <c r="C99" t="s">
         <v>342</v>
       </c>
+      <c r="D99" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="E99" s="12" t="s">
+        <v>371</v>
+      </c>
       <c r="G99">
         <v>2026</v>
       </c>
       <c r="AG99" s="8"/>
     </row>
-    <row r="100" spans="1:37" ht="17">
+    <row r="100" spans="1:37" ht="35">
       <c r="A100">
         <f t="shared" si="23"/>
         <v>99</v>
       </c>
       <c r="B100" t="str" cm="1">
         <f t="array" ref="B100">_xlfn.IFS(ISBLANK(D100),"",ISBLANK(C100),"no venue",ISBLANK(E100),"no bib",ISNUMBER(SEARCH("xiv", C100)),"arxiv",SUM(I100:AA100)&lt;3,"no categories",TRUE,"")</f>
-        <v/>
+        <v>arxiv</v>
       </c>
       <c r="C100" t="s">
         <v>342</v>
+      </c>
+      <c r="D100" s="16" t="s">
+        <v>372</v>
+      </c>
+      <c r="E100" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="G100">
+        <v>2026</v>
       </c>
       <c r="AG100" s="8"/>
     </row>
@@ -20305,6 +20350,8 @@
     <hyperlink ref="D95" r:id="rId49" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=8b8IhUYAAAAJ&amp;sortby=pubdate&amp;citation_for_view=8b8IhUYAAAAJ:B3FOqHPlNUQC" xr:uid="{4655ADB8-FEB9-6148-99F7-03736D7EB3B9}"/>
     <hyperlink ref="D96" r:id="rId50" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=8b8IhUYAAAAJ&amp;sortby=pubdate&amp;citation_for_view=8b8IhUYAAAAJ:sSrBHYA8nusC" xr:uid="{94FB61E5-5F04-5645-A99F-119289B9E81D}"/>
     <hyperlink ref="D97" r:id="rId51" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=8b8IhUYAAAAJ&amp;sortby=pubdate&amp;citation_for_view=8b8IhUYAAAAJ:5Ul4iDaHHb8C" xr:uid="{AC018292-7C41-B947-89FB-2E8002093149}"/>
+    <hyperlink ref="D99" r:id="rId52" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=8b8IhUYAAAAJ&amp;sortby=pubdate&amp;citation_for_view=8b8IhUYAAAAJ:eflP2zaiRacC" xr:uid="{60D0073E-0896-9C4A-A723-621180E109EC}"/>
+    <hyperlink ref="D98" r:id="rId53" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=8b8IhUYAAAAJ&amp;sortby=pubdate&amp;citation_for_view=8b8IhUYAAAAJ:VOx2b1Wkg3QC" xr:uid="{1B316D5B-F142-5C4C-8594-5D8D28179250}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/Contributions_table.xlsx
+++ b/Contributions_table.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lc/PycharmProjects/publications/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2E6D253-99C5-964F-845D-5B52E82B72C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D359E718-0965-6D4D-AF45-A054575C6F7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34560" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{5AA491FB-7947-2140-ACD9-201A623594D0}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{5AA491FB-7947-2140-ACD9-201A623594D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="376">
   <si>
     <t xml:space="preserve">EMNLP (under review) </t>
   </si>
@@ -225,9 +225,6 @@
   </si>
   <si>
     <t xml:space="preserve"> Benchmark Agreement Testing Done Right: A Guide for LLM Benchmark Evaluation</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Learning from Naturally Occurring Feedback</t>
   </si>
   <si>
     <t xml:space="preserve"> NumeroLogic: Number Encoding for Enhanced LLMs' Numerical Reasoning</t>
@@ -1000,9 +997,6 @@
     <t>ICLR</t>
   </si>
   <si>
-    <t>Review</t>
-  </si>
-  <si>
     <t>Workshop-paper</t>
   </si>
   <si>
@@ -1252,6 +1246,18 @@
   </si>
   <si>
     <t>bandel2026agentic</t>
+  </si>
+  <si>
+    <t>Review, Survey and Position</t>
+  </si>
+  <si>
+    <t>Naturally occurring feedback is common, extractable and useful</t>
+  </si>
+  <si>
+    <t>fandina2025safesafetymetricautomatic</t>
+  </si>
+  <si>
+    <t>How Safe is Your Safety Metric? Automatic Concatenation Tests for Metric Reliability</t>
   </si>
 </sst>
 </file>
@@ -12260,7 +12266,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92277768-849A-7540-AC05-5E1BE041CC8E}">
-  <dimension ref="A1:AK138"/>
+  <dimension ref="A1:AK139"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="4" max="4" width="29.5" customWidth="1"/>
@@ -12276,115 +12282,115 @@
   <sheetData>
     <row r="1" spans="1:37" s="15" customFormat="1" ht="51">
       <c r="A1" s="15" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C1" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="G1" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="H1" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="I1" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="J1" s="15" t="s">
+        <v>286</v>
+      </c>
+      <c r="K1" s="15" t="s">
+        <v>283</v>
+      </c>
+      <c r="L1" s="15" t="s">
+        <v>282</v>
+      </c>
+      <c r="M1" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="N1" s="15" t="s">
+        <v>284</v>
+      </c>
+      <c r="O1" s="15" t="s">
+        <v>260</v>
+      </c>
+      <c r="P1" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="Q1" s="15" t="s">
+        <v>259</v>
+      </c>
+      <c r="R1" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="S1" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="T1" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="U1" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="V1" s="15" t="s">
+        <v>261</v>
+      </c>
+      <c r="W1" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="X1" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="Y1" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="Z1" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="AA1" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="AB1" s="15" t="s">
+        <v>292</v>
+      </c>
+      <c r="AC1" s="15" t="s">
+        <v>372</v>
+      </c>
+      <c r="AD1" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="AE1" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="AF1" s="15" t="s">
+        <v>247</v>
+      </c>
+      <c r="AG1" s="15" t="s">
+        <v>247</v>
+      </c>
+      <c r="AH1" s="15" t="s">
+        <v>248</v>
+      </c>
+      <c r="AI1" s="15" t="s">
+        <v>249</v>
+      </c>
+      <c r="AJ1" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="AK1" s="15" t="s">
         <v>289</v>
-      </c>
-      <c r="D1" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="E1" s="15" t="s">
-        <v>247</v>
-      </c>
-      <c r="F1" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="G1" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="H1" s="15" t="s">
-        <v>259</v>
-      </c>
-      <c r="I1" s="15" t="s">
-        <v>288</v>
-      </c>
-      <c r="J1" s="15" t="s">
-        <v>287</v>
-      </c>
-      <c r="K1" s="15" t="s">
-        <v>284</v>
-      </c>
-      <c r="L1" s="15" t="s">
-        <v>283</v>
-      </c>
-      <c r="M1" s="15" t="s">
-        <v>286</v>
-      </c>
-      <c r="N1" s="15" t="s">
-        <v>285</v>
-      </c>
-      <c r="O1" s="15" t="s">
-        <v>261</v>
-      </c>
-      <c r="P1" s="15" t="s">
-        <v>263</v>
-      </c>
-      <c r="Q1" s="15" t="s">
-        <v>260</v>
-      </c>
-      <c r="R1" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="S1" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="T1" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="U1" s="15" t="s">
-        <v>158</v>
-      </c>
-      <c r="V1" s="15" t="s">
-        <v>262</v>
-      </c>
-      <c r="W1" s="15" t="s">
-        <v>159</v>
-      </c>
-      <c r="X1" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="Y1" s="15" t="s">
-        <v>258</v>
-      </c>
-      <c r="Z1" s="15" t="s">
-        <v>164</v>
-      </c>
-      <c r="AA1" s="15" t="s">
-        <v>161</v>
-      </c>
-      <c r="AB1" s="15" t="s">
-        <v>294</v>
-      </c>
-      <c r="AC1" s="15" t="s">
-        <v>293</v>
-      </c>
-      <c r="AD1" s="15" t="s">
-        <v>181</v>
-      </c>
-      <c r="AE1" s="15" t="s">
-        <v>257</v>
-      </c>
-      <c r="AF1" s="15" t="s">
-        <v>248</v>
-      </c>
-      <c r="AG1" s="15" t="s">
-        <v>248</v>
-      </c>
-      <c r="AH1" s="15" t="s">
-        <v>249</v>
-      </c>
-      <c r="AI1" s="15" t="s">
-        <v>250</v>
-      </c>
-      <c r="AJ1" s="15" t="s">
-        <v>257</v>
-      </c>
-      <c r="AK1" s="15" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="2" spans="1:37">
@@ -12402,10 +12408,10 @@
         <v>48</v>
       </c>
       <c r="E2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G2">
         <v>2018</v>
@@ -12461,16 +12467,16 @@
         <v/>
       </c>
       <c r="C3" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>127</v>
-      </c>
       <c r="E3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G3">
         <v>2018</v>
@@ -12539,13 +12545,13 @@
         <v>46</v>
       </c>
       <c r="D4" t="s">
+        <v>123</v>
+      </c>
+      <c r="E4" t="s">
+        <v>205</v>
+      </c>
+      <c r="F4" t="s">
         <v>124</v>
-      </c>
-      <c r="E4" t="s">
-        <v>206</v>
-      </c>
-      <c r="F4" t="s">
-        <v>125</v>
       </c>
       <c r="G4">
         <v>2018</v>
@@ -12612,13 +12618,13 @@
         <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G5">
         <v>2018</v>
@@ -12699,13 +12705,13 @@
         <v>44</v>
       </c>
       <c r="D6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G6">
         <v>2018</v>
@@ -12774,13 +12780,13 @@
         <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G7">
         <v>2019</v>
@@ -12864,13 +12870,13 @@
         <v>42</v>
       </c>
       <c r="D8" t="s">
+        <v>117</v>
+      </c>
+      <c r="E8" t="s">
+        <v>233</v>
+      </c>
+      <c r="F8" t="s">
         <v>118</v>
-      </c>
-      <c r="E8" t="s">
-        <v>234</v>
-      </c>
-      <c r="F8" t="s">
-        <v>119</v>
       </c>
       <c r="G8">
         <v>2019</v>
@@ -12934,13 +12940,13 @@
         <v>41</v>
       </c>
       <c r="D9" t="s">
+        <v>115</v>
+      </c>
+      <c r="E9" t="s">
+        <v>232</v>
+      </c>
+      <c r="F9" t="s">
         <v>116</v>
-      </c>
-      <c r="E9" t="s">
-        <v>233</v>
-      </c>
-      <c r="F9" t="s">
-        <v>117</v>
       </c>
       <c r="G9">
         <v>2019</v>
@@ -13009,13 +13015,13 @@
         <v>40</v>
       </c>
       <c r="D10" t="s">
+        <v>113</v>
+      </c>
+      <c r="E10" t="s">
+        <v>231</v>
+      </c>
+      <c r="F10" t="s">
         <v>114</v>
-      </c>
-      <c r="E10" t="s">
-        <v>232</v>
-      </c>
-      <c r="F10" t="s">
-        <v>115</v>
       </c>
       <c r="G10">
         <v>2019</v>
@@ -13097,13 +13103,13 @@
         <v>39</v>
       </c>
       <c r="D11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G11">
         <v>2019</v>
@@ -13187,13 +13193,13 @@
         <v>38</v>
       </c>
       <c r="D12" t="s">
+        <v>109</v>
+      </c>
+      <c r="E12" t="s">
+        <v>229</v>
+      </c>
+      <c r="F12" t="s">
         <v>110</v>
-      </c>
-      <c r="E12" t="s">
-        <v>230</v>
-      </c>
-      <c r="F12" t="s">
-        <v>111</v>
       </c>
       <c r="G12">
         <v>2020</v>
@@ -13266,13 +13272,13 @@
         <v>37</v>
       </c>
       <c r="D13" t="s">
+        <v>145</v>
+      </c>
+      <c r="E13" t="s">
+        <v>228</v>
+      </c>
+      <c r="F13" t="s">
         <v>146</v>
-      </c>
-      <c r="E13" t="s">
-        <v>229</v>
-      </c>
-      <c r="F13" t="s">
-        <v>147</v>
       </c>
       <c r="G13">
         <v>2020</v>
@@ -13343,13 +13349,13 @@
         <v>36</v>
       </c>
       <c r="D14" t="s">
+        <v>143</v>
+      </c>
+      <c r="E14" t="s">
+        <v>204</v>
+      </c>
+      <c r="F14" t="s">
         <v>144</v>
-      </c>
-      <c r="E14" t="s">
-        <v>205</v>
-      </c>
-      <c r="F14" t="s">
-        <v>145</v>
       </c>
       <c r="G14">
         <v>2020</v>
@@ -13409,13 +13415,13 @@
         <v>35</v>
       </c>
       <c r="D15" t="s">
+        <v>141</v>
+      </c>
+      <c r="E15" t="s">
+        <v>227</v>
+      </c>
+      <c r="F15" t="s">
         <v>142</v>
-      </c>
-      <c r="E15" t="s">
-        <v>228</v>
-      </c>
-      <c r="F15" t="s">
-        <v>143</v>
       </c>
       <c r="G15">
         <v>2020</v>
@@ -13486,13 +13492,13 @@
         <v>34</v>
       </c>
       <c r="D16" t="s">
+        <v>139</v>
+      </c>
+      <c r="E16" t="s">
+        <v>226</v>
+      </c>
+      <c r="F16" t="s">
         <v>140</v>
-      </c>
-      <c r="E16" t="s">
-        <v>227</v>
-      </c>
-      <c r="F16" t="s">
-        <v>141</v>
       </c>
       <c r="G16">
         <v>2020</v>
@@ -13572,13 +13578,13 @@
         <v>33</v>
       </c>
       <c r="D17" t="s">
+        <v>137</v>
+      </c>
+      <c r="E17" t="s">
+        <v>203</v>
+      </c>
+      <c r="F17" t="s">
         <v>138</v>
-      </c>
-      <c r="E17" t="s">
-        <v>204</v>
-      </c>
-      <c r="F17" t="s">
-        <v>139</v>
       </c>
       <c r="G17">
         <v>2020</v>
@@ -13650,13 +13656,13 @@
         <v>32</v>
       </c>
       <c r="D18" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E18" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G18" s="4">
         <v>2021</v>
@@ -13729,13 +13735,13 @@
         <v>31</v>
       </c>
       <c r="D19" t="s">
+        <v>92</v>
+      </c>
+      <c r="E19" t="s">
+        <v>225</v>
+      </c>
+      <c r="F19" t="s">
         <v>93</v>
-      </c>
-      <c r="E19" t="s">
-        <v>226</v>
-      </c>
-      <c r="F19" t="s">
-        <v>94</v>
       </c>
       <c r="G19" s="4">
         <v>2021</v>
@@ -13797,13 +13803,13 @@
         <v>30</v>
       </c>
       <c r="D20" t="s">
+        <v>90</v>
+      </c>
+      <c r="E20" t="s">
+        <v>201</v>
+      </c>
+      <c r="F20" t="s">
         <v>91</v>
-      </c>
-      <c r="E20" t="s">
-        <v>202</v>
-      </c>
-      <c r="F20" t="s">
-        <v>92</v>
       </c>
       <c r="G20" s="4">
         <v>2021</v>
@@ -13877,13 +13883,13 @@
         <v>29</v>
       </c>
       <c r="D21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E21" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F21" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G21" s="4">
         <v>2021</v>
@@ -13948,13 +13954,13 @@
         <v>28</v>
       </c>
       <c r="D22" t="s">
+        <v>88</v>
+      </c>
+      <c r="E22" t="s">
+        <v>200</v>
+      </c>
+      <c r="F22" t="s">
         <v>89</v>
-      </c>
-      <c r="E22" t="s">
-        <v>201</v>
-      </c>
-      <c r="F22" t="s">
-        <v>90</v>
       </c>
       <c r="G22">
         <v>2022</v>
@@ -14013,13 +14019,13 @@
         <v>28</v>
       </c>
       <c r="D23" t="s">
+        <v>86</v>
+      </c>
+      <c r="E23" t="s">
+        <v>199</v>
+      </c>
+      <c r="F23" t="s">
         <v>87</v>
-      </c>
-      <c r="E23" t="s">
-        <v>200</v>
-      </c>
-      <c r="F23" t="s">
-        <v>88</v>
       </c>
       <c r="G23">
         <v>2022</v>
@@ -14081,13 +14087,13 @@
         <v>27</v>
       </c>
       <c r="D24" t="s">
+        <v>84</v>
+      </c>
+      <c r="E24" t="s">
+        <v>239</v>
+      </c>
+      <c r="F24" t="s">
         <v>85</v>
-      </c>
-      <c r="E24" t="s">
-        <v>240</v>
-      </c>
-      <c r="F24" t="s">
-        <v>86</v>
       </c>
       <c r="G24">
         <v>2022</v>
@@ -14159,13 +14165,13 @@
         <v>26</v>
       </c>
       <c r="D25" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E25" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F25" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G25">
         <v>2022</v>
@@ -14239,13 +14245,13 @@
         <v>25</v>
       </c>
       <c r="D26" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E26" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F26" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G26">
         <v>2023</v>
@@ -14315,13 +14321,13 @@
         <v>24</v>
       </c>
       <c r="D27" t="s">
+        <v>82</v>
+      </c>
+      <c r="E27" t="s">
+        <v>198</v>
+      </c>
+      <c r="F27" t="s">
         <v>83</v>
-      </c>
-      <c r="E27" t="s">
-        <v>199</v>
-      </c>
-      <c r="F27" t="s">
-        <v>84</v>
       </c>
       <c r="G27">
         <v>2023</v>
@@ -14402,13 +14408,13 @@
         <v>23</v>
       </c>
       <c r="D28" t="s">
+        <v>80</v>
+      </c>
+      <c r="E28" t="s">
+        <v>221</v>
+      </c>
+      <c r="F28" t="s">
         <v>81</v>
-      </c>
-      <c r="E28" t="s">
-        <v>222</v>
-      </c>
-      <c r="F28" t="s">
-        <v>82</v>
       </c>
       <c r="G28">
         <v>2023</v>
@@ -14473,13 +14479,13 @@
         <v>22</v>
       </c>
       <c r="D29" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E29" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F29" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G29">
         <v>2023</v>
@@ -14542,13 +14548,13 @@
         <v>18</v>
       </c>
       <c r="D30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E30" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F30" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G30">
         <v>2023</v>
@@ -14625,13 +14631,13 @@
         <v>21</v>
       </c>
       <c r="D31" t="s">
+        <v>77</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="F31" t="s">
         <v>78</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="F31" t="s">
-        <v>79</v>
       </c>
       <c r="G31">
         <v>2023</v>
@@ -14696,13 +14702,13 @@
         <v>20</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F32" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G32">
         <v>2023</v>
@@ -14776,13 +14782,13 @@
         <v>19</v>
       </c>
       <c r="D33" t="s">
+        <v>74</v>
+      </c>
+      <c r="E33" t="s">
+        <v>197</v>
+      </c>
+      <c r="F33" t="s">
         <v>75</v>
-      </c>
-      <c r="E33" t="s">
-        <v>198</v>
-      </c>
-      <c r="F33" t="s">
-        <v>76</v>
       </c>
       <c r="G33">
         <v>2023</v>
@@ -14845,13 +14851,13 @@
         <v>18</v>
       </c>
       <c r="D34" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E34" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F34" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G34">
         <v>2023</v>
@@ -14916,13 +14922,13 @@
         <v>17</v>
       </c>
       <c r="D35" t="s">
+        <v>71</v>
+      </c>
+      <c r="E35" t="s">
+        <v>216</v>
+      </c>
+      <c r="F35" t="s">
         <v>72</v>
-      </c>
-      <c r="E35" t="s">
-        <v>217</v>
-      </c>
-      <c r="F35" t="s">
-        <v>73</v>
       </c>
       <c r="G35">
         <v>2023</v>
@@ -14987,13 +14993,13 @@
         <v>16</v>
       </c>
       <c r="D36" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E36" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F36" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G36">
         <v>2023</v>
@@ -15063,16 +15069,16 @@
         <v/>
       </c>
       <c r="C37" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="D37" t="s">
         <v>268</v>
       </c>
-      <c r="D37" t="s">
-        <v>269</v>
-      </c>
       <c r="E37" t="s">
+        <v>264</v>
+      </c>
+      <c r="F37" t="s">
         <v>265</v>
-      </c>
-      <c r="F37" t="s">
-        <v>266</v>
       </c>
       <c r="G37">
         <v>2023</v>
@@ -15160,13 +15166,13 @@
         <v>13</v>
       </c>
       <c r="D38" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E38" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F38" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G38">
         <v>2023</v>
@@ -15251,13 +15257,13 @@
         <v>13</v>
       </c>
       <c r="D39" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E39" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F39" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G39">
         <v>2023</v>
@@ -15316,13 +15322,13 @@
         <v>15</v>
       </c>
       <c r="D40" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E40" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F40" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G40">
         <v>2023</v>
@@ -15391,13 +15397,13 @@
         <v>14</v>
       </c>
       <c r="D41" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E41" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F41" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G41">
         <v>2023</v>
@@ -15469,13 +15475,13 @@
         <v>13</v>
       </c>
       <c r="D42" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E42" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F42" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G42">
         <v>2023</v>
@@ -15543,13 +15549,13 @@
         <v>12</v>
       </c>
       <c r="D43" t="s">
+        <v>66</v>
+      </c>
+      <c r="E43" t="s">
+        <v>195</v>
+      </c>
+      <c r="F43" t="s">
         <v>67</v>
-      </c>
-      <c r="E43" t="s">
-        <v>196</v>
-      </c>
-      <c r="F43" t="s">
-        <v>68</v>
       </c>
       <c r="G43">
         <v>2024</v>
@@ -15627,16 +15633,16 @@
         <v/>
       </c>
       <c r="C44" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="D44" t="s">
         <v>176</v>
       </c>
-      <c r="D44" t="s">
+      <c r="E44" t="s">
+        <v>194</v>
+      </c>
+      <c r="F44" t="s">
         <v>177</v>
-      </c>
-      <c r="E44" t="s">
-        <v>195</v>
-      </c>
-      <c r="F44" t="s">
-        <v>178</v>
       </c>
       <c r="G44">
         <v>2024</v>
@@ -15699,16 +15705,16 @@
         <v/>
       </c>
       <c r="C45" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D45" t="s">
+        <v>272</v>
+      </c>
+      <c r="E45" t="s">
+        <v>271</v>
+      </c>
+      <c r="F45" t="s">
         <v>273</v>
-      </c>
-      <c r="E45" t="s">
-        <v>272</v>
-      </c>
-      <c r="F45" t="s">
-        <v>274</v>
       </c>
       <c r="G45">
         <v>2024</v>
@@ -15780,13 +15786,13 @@
         <v>11</v>
       </c>
       <c r="D46" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F46" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G46">
         <v>2024</v>
@@ -15855,13 +15861,13 @@
         <v>10</v>
       </c>
       <c r="D47" t="s">
+        <v>63</v>
+      </c>
+      <c r="E47" t="s">
+        <v>212</v>
+      </c>
+      <c r="F47" t="s">
         <v>64</v>
-      </c>
-      <c r="E47" t="s">
-        <v>213</v>
-      </c>
-      <c r="F47" t="s">
-        <v>65</v>
       </c>
       <c r="G47">
         <v>2024</v>
@@ -15926,13 +15932,13 @@
         <v>9</v>
       </c>
       <c r="D48" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E48" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F48" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G48">
         <v>2024</v>
@@ -16027,13 +16033,13 @@
         <v>8</v>
       </c>
       <c r="D49" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E49" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F49" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G49">
         <v>2024</v>
@@ -16104,13 +16110,13 @@
         <v>7</v>
       </c>
       <c r="D50" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E50" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F50" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G50">
         <v>2024</v>
@@ -16178,13 +16184,13 @@
         <v>7</v>
       </c>
       <c r="D51" t="s">
+        <v>61</v>
+      </c>
+      <c r="E51" t="s">
+        <v>209</v>
+      </c>
+      <c r="F51" t="s">
         <v>62</v>
-      </c>
-      <c r="E51" t="s">
-        <v>210</v>
-      </c>
-      <c r="F51" t="s">
-        <v>63</v>
       </c>
       <c r="G51">
         <v>2024</v>
@@ -16259,13 +16265,13 @@
         <v>6</v>
       </c>
       <c r="D52" t="s">
+        <v>59</v>
+      </c>
+      <c r="E52" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="F52" t="s">
         <v>60</v>
-      </c>
-      <c r="E52" s="14" t="s">
-        <v>194</v>
-      </c>
-      <c r="F52" t="s">
-        <v>61</v>
       </c>
       <c r="G52">
         <v>2024</v>
@@ -16346,13 +16352,13 @@
         <v>5</v>
       </c>
       <c r="D53" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E53" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F53" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G53">
         <v>2024</v>
@@ -16427,13 +16433,13 @@
         <v>4</v>
       </c>
       <c r="D54" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E54" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F54" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G54">
         <v>2024</v>
@@ -16505,16 +16511,16 @@
         <v/>
       </c>
       <c r="C55" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D55" t="s">
+        <v>56</v>
+      </c>
+      <c r="E55" t="s">
+        <v>243</v>
+      </c>
+      <c r="F55" t="s">
         <v>57</v>
-      </c>
-      <c r="E55" t="s">
-        <v>244</v>
-      </c>
-      <c r="F55" t="s">
-        <v>58</v>
       </c>
       <c r="G55">
         <v>2024</v>
@@ -16582,13 +16588,13 @@
         <v/>
       </c>
       <c r="C56" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E56" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F56" t="s">
         <v>3</v>
@@ -16663,16 +16669,16 @@
         <v/>
       </c>
       <c r="C57" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D57" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E57" s="12" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F57" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G57">
         <v>2024</v>
@@ -16741,16 +16747,16 @@
         <v/>
       </c>
       <c r="C58" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D58" t="s">
+        <v>54</v>
+      </c>
+      <c r="E58" s="12" t="s">
+        <v>309</v>
+      </c>
+      <c r="F58" t="s">
         <v>55</v>
-      </c>
-      <c r="E58" s="12" t="s">
-        <v>311</v>
-      </c>
-      <c r="F58" t="s">
-        <v>56</v>
       </c>
       <c r="G58">
         <v>2024</v>
@@ -16812,13 +16818,13 @@
         <v>1</v>
       </c>
       <c r="D59" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E59" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F59" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G59">
         <v>2024</v>
@@ -16884,16 +16890,16 @@
         <v/>
       </c>
       <c r="C60" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D60" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E60" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F60" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G60">
         <v>2024</v>
@@ -16959,7 +16965,7 @@
         <v>49</v>
       </c>
       <c r="E61" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F61" t="s">
         <v>2</v>
@@ -17022,16 +17028,16 @@
         <v/>
       </c>
       <c r="C62" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D62" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F62" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G62">
         <v>2024</v>
@@ -17110,14 +17116,14 @@
       <c r="C63" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D63" t="s">
-        <v>54</v>
+      <c r="D63" s="2" t="s">
+        <v>373</v>
       </c>
       <c r="E63" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F63" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G63">
         <v>2024</v>
@@ -17185,16 +17191,16 @@
         <v>63</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D64" t="s">
         <v>53</v>
       </c>
       <c r="E64" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F64" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G64">
         <v>2024</v>
@@ -17260,16 +17266,16 @@
         <v/>
       </c>
       <c r="C65" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D65" t="s">
         <v>52</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F65" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G65">
         <v>2024</v>
@@ -17338,16 +17344,16 @@
         <v/>
       </c>
       <c r="C66" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D66" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E66" s="12" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="F66" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G66">
         <v>2024</v>
@@ -17436,7 +17442,7 @@
         <v>50</v>
       </c>
       <c r="E67" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F67" t="s">
         <v>51</v>
@@ -17502,7 +17508,7 @@
     </row>
     <row r="68" spans="1:37">
       <c r="A68">
-        <f t="shared" ref="A68:A127" si="23">1+A67</f>
+        <f t="shared" ref="A68:A128" si="23">1+A67</f>
         <v>67</v>
       </c>
       <c r="B68" t="str" cm="1">
@@ -17510,16 +17516,16 @@
         <v/>
       </c>
       <c r="C68" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D68" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E68" t="s">
+        <v>187</v>
+      </c>
+      <c r="F68" t="s">
         <v>186</v>
-      </c>
-      <c r="E68" t="s">
-        <v>188</v>
-      </c>
-      <c r="F68" t="s">
-        <v>187</v>
       </c>
       <c r="G68">
         <v>2024</v>
@@ -17544,6 +17550,9 @@
         <v>1</v>
       </c>
       <c r="AA68">
+        <v>1</v>
+      </c>
+      <c r="AC68">
         <v>1</v>
       </c>
       <c r="AD68">
@@ -17584,16 +17593,16 @@
         <v/>
       </c>
       <c r="C69" t="s">
+        <v>250</v>
+      </c>
+      <c r="D69" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="D69" s="2" t="s">
+      <c r="E69" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="F69" s="10" t="s">
         <v>252</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="F69" s="10" t="s">
-        <v>253</v>
       </c>
       <c r="G69">
         <v>2024</v>
@@ -17652,16 +17661,16 @@
         <v/>
       </c>
       <c r="C70" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D70" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="E70" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="F70" s="10" t="s">
         <v>255</v>
-      </c>
-      <c r="E70" s="9" t="s">
-        <v>314</v>
-      </c>
-      <c r="F70" s="10" t="s">
-        <v>256</v>
       </c>
       <c r="G70">
         <v>2024</v>
@@ -17670,6 +17679,9 @@
         <v>1</v>
       </c>
       <c r="K70">
+        <v>1</v>
+      </c>
+      <c r="N70">
         <v>1</v>
       </c>
       <c r="P70">
@@ -17723,16 +17735,16 @@
         <v/>
       </c>
       <c r="C71" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D71" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E71" s="12" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F71" s="10" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="G71">
         <v>2024</v>
@@ -17817,16 +17829,16 @@
         <v/>
       </c>
       <c r="C72" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D72" s="13" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E72" t="s">
+        <v>269</v>
+      </c>
+      <c r="F72" s="10" t="s">
         <v>270</v>
-      </c>
-      <c r="F72" s="10" t="s">
-        <v>271</v>
       </c>
       <c r="G72">
         <v>2024</v>
@@ -17869,7 +17881,7 @@
         <v>0</v>
       </c>
       <c r="AF72">
-        <f t="shared" ref="AF72:AF98" si="24">IF(SUM(T72,P72)&gt;0,1,0)</f>
+        <f t="shared" ref="AF72:AF99" si="24">IF(SUM(T72,P72)&gt;0,1,0)</f>
         <v>1</v>
       </c>
       <c r="AG72" t="str">
@@ -17885,7 +17897,7 @@
         <v>knots</v>
       </c>
       <c r="AK72">
-        <f t="shared" ref="AK72:AK98" si="28">IF(Z72+T72&gt;1,1,0)</f>
+        <f t="shared" ref="AK72:AK101" si="28">IF(Z72+T72&gt;1,1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17899,16 +17911,16 @@
         <v/>
       </c>
       <c r="C73" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D73" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="E73" t="s">
+        <v>281</v>
+      </c>
+      <c r="F73" s="5" t="s">
         <v>275</v>
-      </c>
-      <c r="E73" t="s">
-        <v>282</v>
-      </c>
-      <c r="F73" s="5" t="s">
-        <v>276</v>
       </c>
       <c r="G73">
         <v>2024</v>
@@ -17987,16 +17999,16 @@
         <v/>
       </c>
       <c r="C74" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D74" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="E74" t="s">
+        <v>278</v>
+      </c>
+      <c r="F74" s="5" t="s">
         <v>277</v>
-      </c>
-      <c r="E74" t="s">
-        <v>279</v>
-      </c>
-      <c r="F74" s="5" t="s">
-        <v>278</v>
       </c>
       <c r="G74">
         <v>2024</v>
@@ -18080,16 +18092,16 @@
         <v>74</v>
       </c>
       <c r="C75" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D75" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="E75" s="12" t="s">
+        <v>296</v>
+      </c>
+      <c r="F75" s="5" t="s">
         <v>297</v>
-      </c>
-      <c r="E75" s="12" t="s">
-        <v>298</v>
-      </c>
-      <c r="F75" s="5" t="s">
-        <v>299</v>
       </c>
       <c r="G75">
         <v>2024</v>
@@ -18160,16 +18172,16 @@
         <v/>
       </c>
       <c r="C76" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D76" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="E76" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="F76" s="5" t="s">
         <v>280</v>
-      </c>
-      <c r="E76" s="9" t="s">
-        <v>315</v>
-      </c>
-      <c r="F76" s="5" t="s">
-        <v>281</v>
       </c>
       <c r="G76">
         <v>2024</v>
@@ -18224,13 +18236,13 @@
         <v/>
       </c>
       <c r="C77" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D77" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E77" s="12" t="s">
         <v>317</v>
-      </c>
-      <c r="E77" s="12" t="s">
-        <v>319</v>
       </c>
       <c r="G77">
         <v>2024</v>
@@ -18306,13 +18318,13 @@
         <v/>
       </c>
       <c r="C78" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E78" s="9" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="G78">
         <v>2024</v>
@@ -18385,13 +18397,13 @@
         <v/>
       </c>
       <c r="C79" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D79" s="11" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E79" s="12" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="G79">
         <v>2024</v>
@@ -18452,13 +18464,13 @@
         <v>79</v>
       </c>
       <c r="C80" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E80" s="12" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G80">
         <v>2025</v>
@@ -18515,13 +18527,13 @@
         <v/>
       </c>
       <c r="C81" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E81" s="12" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="G81">
         <v>2025</v>
@@ -18596,10 +18608,10 @@
         <v>28</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E82" s="12" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="G82">
         <v>2025</v>
@@ -18658,16 +18670,16 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C83" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E83" s="12" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="G83">
         <v>2026</v>
@@ -18727,13 +18739,13 @@
         <v>arxiv</v>
       </c>
       <c r="C84" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D84" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="E84" s="12" t="s">
         <v>327</v>
-      </c>
-      <c r="E84" s="12" t="s">
-        <v>329</v>
       </c>
       <c r="G84">
         <v>2025</v>
@@ -18802,13 +18814,13 @@
         <v>arxiv</v>
       </c>
       <c r="C85" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E85" s="12" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G85">
         <v>2025</v>
@@ -18862,13 +18874,13 @@
         <v>arxiv</v>
       </c>
       <c r="C86" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D86" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="E86" s="12" t="s">
         <v>333</v>
-      </c>
-      <c r="E86" s="12" t="s">
-        <v>335</v>
       </c>
       <c r="G86">
         <v>2025</v>
@@ -18919,13 +18931,13 @@
         <v/>
       </c>
       <c r="C87" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D87" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="E87" s="12" t="s">
         <v>336</v>
-      </c>
-      <c r="E87" s="12" t="s">
-        <v>338</v>
       </c>
       <c r="G87">
         <v>2025</v>
@@ -18982,13 +18994,13 @@
         <v/>
       </c>
       <c r="C88" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E88" s="9" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G88">
         <v>2025</v>
@@ -19039,13 +19051,13 @@
         <v>arxiv</v>
       </c>
       <c r="C89" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E89" s="12" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="G89">
         <v>2025</v>
@@ -19091,57 +19103,28 @@
         <f t="shared" si="23"/>
         <v>89</v>
       </c>
-      <c r="B90" t="s">
-        <v>349</v>
+      <c r="B90" t="str" cm="1">
+        <f t="array" ref="B90">_xlfn.IFS(ISBLANK(D90),"",ISBLANK(C90),"no venue",ISBLANK(E90),"no bib",ISNUMBER(SEARCH("xiv", C90)),"arxiv",SUM(I90:AA90)&lt;3,"no categories",TRUE,"")</f>
+        <v>arxiv</v>
       </c>
       <c r="C90" t="s">
-        <v>345</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>348</v>
+        <v>290</v>
+      </c>
+      <c r="D90" s="9" t="s">
+        <v>375</v>
       </c>
       <c r="E90" s="12" t="s">
-        <v>352</v>
+        <v>374</v>
       </c>
       <c r="G90">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="H90">
         <v>1</v>
       </c>
-      <c r="I90">
-        <v>1</v>
-      </c>
-      <c r="N90">
-        <v>1</v>
-      </c>
-      <c r="O90">
-        <v>1</v>
-      </c>
-      <c r="R90">
-        <v>1</v>
-      </c>
-      <c r="S90">
-        <v>1</v>
-      </c>
       <c r="T90">
         <v>1</v>
       </c>
-      <c r="U90">
-        <v>1</v>
-      </c>
-      <c r="V90">
-        <v>1</v>
-      </c>
-      <c r="W90">
-        <v>1</v>
-      </c>
-      <c r="X90">
-        <v>1</v>
-      </c>
-      <c r="Y90">
-        <v>1</v>
-      </c>
       <c r="AA90">
         <v>1</v>
       </c>
@@ -19149,23 +19132,23 @@
         <v>1</v>
       </c>
       <c r="AF90">
-        <f t="shared" si="24"/>
+        <f t="shared" ref="AF90" si="30">IF(SUM(T90,P90)&gt;0,1,0)</f>
         <v>1</v>
       </c>
       <c r="AG90" t="str">
-        <f t="shared" si="25"/>
-        <v>jumelet2025babybabellm</v>
+        <f t="shared" ref="AG90" si="31">IF(AF90,E90,"")</f>
+        <v>fandina2025safesafetymetricautomatic</v>
       </c>
       <c r="AH90" t="str">
-        <f t="shared" si="26"/>
-        <v>jumelet2025babybabellm</v>
+        <f t="shared" ref="AH90" si="32">IF(W90,E90,"")</f>
+        <v/>
       </c>
       <c r="AI90" t="str">
-        <f t="shared" si="27"/>
-        <v>jumelet2025babybabellm</v>
+        <f t="shared" ref="AI90" si="33">IF(Y90,E90,"")</f>
+        <v/>
       </c>
       <c r="AK90">
-        <f t="shared" si="28"/>
+        <f t="shared" ref="AK90" si="34">IF(Z90+T90&gt;1,1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -19174,18 +19157,17 @@
         <f t="shared" si="23"/>
         <v>90</v>
       </c>
-      <c r="B91" t="str" cm="1">
-        <f t="array" ref="B91">_xlfn.IFS(ISBLANK(D91),"",ISBLANK(C91),"no venue",ISBLANK(E91),"no bib",ISNUMBER(SEARCH("xiv", C91)),"arxiv",SUM(I91:AA91)&lt;3,"no categories",TRUE,"")</f>
-        <v>arxiv</v>
+      <c r="B91" t="s">
+        <v>347</v>
       </c>
       <c r="C91" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D91" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="E91" s="12" t="s">
         <v>350</v>
-      </c>
-      <c r="E91" s="12" t="s">
-        <v>351</v>
       </c>
       <c r="G91">
         <v>2026</v>
@@ -19193,6 +19175,9 @@
       <c r="H91">
         <v>1</v>
       </c>
+      <c r="I91">
+        <v>1</v>
+      </c>
       <c r="N91">
         <v>1</v>
       </c>
@@ -19202,7 +19187,22 @@
       <c r="R91">
         <v>1</v>
       </c>
+      <c r="S91">
+        <v>1</v>
+      </c>
+      <c r="T91">
+        <v>1</v>
+      </c>
       <c r="U91">
+        <v>1</v>
+      </c>
+      <c r="V91">
+        <v>1</v>
+      </c>
+      <c r="W91">
+        <v>1</v>
+      </c>
+      <c r="X91">
         <v>1</v>
       </c>
       <c r="Y91">
@@ -19216,19 +19216,19 @@
       </c>
       <c r="AF91">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG91" t="str">
         <f t="shared" si="25"/>
-        <v/>
+        <v>jumelet2025babybabellm</v>
       </c>
       <c r="AH91" t="str">
         <f t="shared" si="26"/>
-        <v/>
+        <v>jumelet2025babybabellm</v>
       </c>
       <c r="AI91" t="str">
         <f t="shared" si="27"/>
-        <v>chang2025globalpiqaevaluatingphysical</v>
+        <v>jumelet2025babybabellm</v>
       </c>
       <c r="AK91">
         <f t="shared" si="28"/>
@@ -19242,16 +19242,16 @@
       </c>
       <c r="B92" t="str" cm="1">
         <f t="array" ref="B92">_xlfn.IFS(ISBLANK(D92),"",ISBLANK(C92),"no venue",ISBLANK(E92),"no bib",ISNUMBER(SEARCH("xiv", C92)),"arxiv",SUM(I92:AA92)&lt;3,"no categories",TRUE,"")</f>
-        <v/>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>310</v>
+        <v>arxiv</v>
+      </c>
+      <c r="C92" t="s">
+        <v>340</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="E92" s="12" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="G92">
         <v>2026</v>
@@ -19259,40 +19259,22 @@
       <c r="H92">
         <v>1</v>
       </c>
-      <c r="I92">
-        <v>1</v>
-      </c>
       <c r="N92">
         <v>1</v>
       </c>
       <c r="O92">
         <v>1</v>
       </c>
-      <c r="Q92">
-        <v>1</v>
-      </c>
       <c r="R92">
         <v>1</v>
       </c>
-      <c r="S92">
-        <v>1</v>
-      </c>
-      <c r="T92">
-        <v>1</v>
-      </c>
       <c r="U92">
         <v>1</v>
       </c>
-      <c r="V92">
-        <v>1</v>
-      </c>
-      <c r="Z92">
+      <c r="Y92">
         <v>1</v>
       </c>
       <c r="AA92">
-        <v>1</v>
-      </c>
-      <c r="AB92">
         <v>1</v>
       </c>
       <c r="AD92">
@@ -19300,11 +19282,11 @@
       </c>
       <c r="AF92">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG92" t="str">
         <f t="shared" si="25"/>
-        <v>charpentier-etal-2025-findings</v>
+        <v/>
       </c>
       <c r="AH92" t="str">
         <f t="shared" si="26"/>
@@ -19312,11 +19294,11 @@
       </c>
       <c r="AI92" t="str">
         <f t="shared" si="27"/>
-        <v/>
+        <v>chang2025globalpiqaevaluatingphysical</v>
       </c>
       <c r="AK92">
         <f t="shared" si="28"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:37">
@@ -19326,13 +19308,16 @@
       </c>
       <c r="B93" t="str" cm="1">
         <f t="array" ref="B93">_xlfn.IFS(ISBLANK(D93),"",ISBLANK(C93),"no venue",ISBLANK(E93),"no bib",ISNUMBER(SEARCH("xiv", C93)),"arxiv",SUM(I93:AA93)&lt;3,"no categories",TRUE,"")</f>
-        <v>no bib</v>
-      </c>
-      <c r="C93" t="s">
-        <v>342</v>
+        <v/>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>308</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>356</v>
+        <v>351</v>
+      </c>
+      <c r="E93" s="12" t="s">
+        <v>352</v>
       </c>
       <c r="G93">
         <v>2026</v>
@@ -19343,28 +19328,37 @@
       <c r="I93">
         <v>1</v>
       </c>
-      <c r="L93">
-        <v>1</v>
-      </c>
       <c r="N93">
         <v>1</v>
       </c>
-      <c r="P93">
+      <c r="O93">
         <v>1</v>
       </c>
       <c r="Q93">
         <v>1</v>
       </c>
+      <c r="R93">
+        <v>1</v>
+      </c>
       <c r="S93">
         <v>1</v>
       </c>
-      <c r="Y93">
+      <c r="T93">
+        <v>1</v>
+      </c>
+      <c r="U93">
+        <v>1</v>
+      </c>
+      <c r="V93">
         <v>1</v>
       </c>
       <c r="Z93">
         <v>1</v>
       </c>
       <c r="AA93">
+        <v>1</v>
+      </c>
+      <c r="AB93">
         <v>1</v>
       </c>
       <c r="AD93">
@@ -19374,21 +19368,21 @@
         <f t="shared" si="24"/>
         <v>1</v>
       </c>
-      <c r="AG93">
+      <c r="AG93" t="str">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>charpentier-etal-2025-findings</v>
       </c>
       <c r="AH93" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="AI93">
+      <c r="AI93" t="str">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AK93">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:37">
@@ -19398,16 +19392,13 @@
       </c>
       <c r="B94" t="str" cm="1">
         <f t="array" ref="B94">_xlfn.IFS(ISBLANK(D94),"",ISBLANK(C94),"no venue",ISBLANK(E94),"no bib",ISNUMBER(SEARCH("xiv", C94)),"arxiv",SUM(I94:AA94)&lt;3,"no categories",TRUE,"")</f>
-        <v>arxiv</v>
+        <v>no bib</v>
       </c>
       <c r="C94" t="s">
-        <v>342</v>
-      </c>
-      <c r="D94" s="9" t="s">
-        <v>358</v>
-      </c>
-      <c r="E94" s="12" t="s">
-        <v>357</v>
+        <v>340</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>354</v>
       </c>
       <c r="G94">
         <v>2026</v>
@@ -19415,22 +19406,28 @@
       <c r="H94">
         <v>1</v>
       </c>
-      <c r="O94">
-        <v>1</v>
-      </c>
-      <c r="R94">
+      <c r="I94">
+        <v>1</v>
+      </c>
+      <c r="L94">
+        <v>1</v>
+      </c>
+      <c r="N94">
+        <v>1</v>
+      </c>
+      <c r="P94">
+        <v>1</v>
+      </c>
+      <c r="Q94">
         <v>1</v>
       </c>
       <c r="S94">
         <v>1</v>
       </c>
-      <c r="U94">
-        <v>1</v>
-      </c>
-      <c r="W94">
-        <v>1</v>
-      </c>
       <c r="Y94">
+        <v>1</v>
+      </c>
+      <c r="Z94">
         <v>1</v>
       </c>
       <c r="AA94">
@@ -19441,19 +19438,19 @@
       </c>
       <c r="AF94">
         <f t="shared" si="24"/>
+        <v>1</v>
+      </c>
+      <c r="AG94">
+        <f t="shared" si="25"/>
         <v>0</v>
-      </c>
-      <c r="AG94" t="str">
-        <f t="shared" si="25"/>
-        <v/>
       </c>
       <c r="AH94" t="str">
         <f t="shared" si="26"/>
-        <v>suarez2026commonlid</v>
-      </c>
-      <c r="AI94" t="str">
+        <v/>
+      </c>
+      <c r="AI94">
         <f t="shared" si="27"/>
-        <v>suarez2026commonlid</v>
+        <v>0</v>
       </c>
       <c r="AK94">
         <f t="shared" si="28"/>
@@ -19470,13 +19467,13 @@
         <v>arxiv</v>
       </c>
       <c r="C95" t="s">
-        <v>342</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>359</v>
+        <v>340</v>
+      </c>
+      <c r="D95" s="9" t="s">
+        <v>356</v>
       </c>
       <c r="E95" s="12" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="G95">
         <v>2026</v>
@@ -19484,25 +19481,22 @@
       <c r="H95">
         <v>1</v>
       </c>
-      <c r="K95">
-        <v>1</v>
-      </c>
-      <c r="P95">
-        <v>1</v>
-      </c>
-      <c r="Q95">
+      <c r="O95">
+        <v>1</v>
+      </c>
+      <c r="R95">
         <v>1</v>
       </c>
       <c r="S95">
         <v>1</v>
       </c>
+      <c r="U95">
+        <v>1</v>
+      </c>
       <c r="W95">
         <v>1</v>
       </c>
       <c r="Y95">
-        <v>1</v>
-      </c>
-      <c r="Z95">
         <v>1</v>
       </c>
       <c r="AA95">
@@ -19513,19 +19507,19 @@
       </c>
       <c r="AF95">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG95" t="str">
         <f t="shared" si="25"/>
-        <v>rahamim2026will</v>
+        <v/>
       </c>
       <c r="AH95" t="str">
         <f t="shared" si="26"/>
-        <v>rahamim2026will</v>
+        <v>suarez2026commonlid</v>
       </c>
       <c r="AI95" t="str">
         <f t="shared" si="27"/>
-        <v>rahamim2026will</v>
+        <v>suarez2026commonlid</v>
       </c>
       <c r="AK95">
         <f t="shared" si="28"/>
@@ -19542,13 +19536,13 @@
         <v>arxiv</v>
       </c>
       <c r="C96" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="E96" s="12" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="G96">
         <v>2026</v>
@@ -19556,13 +19550,25 @@
       <c r="H96">
         <v>1</v>
       </c>
-      <c r="O96">
+      <c r="K96">
+        <v>1</v>
+      </c>
+      <c r="P96">
         <v>1</v>
       </c>
       <c r="Q96">
         <v>1</v>
       </c>
-      <c r="T96">
+      <c r="S96">
+        <v>1</v>
+      </c>
+      <c r="W96">
+        <v>1</v>
+      </c>
+      <c r="Y96">
+        <v>1</v>
+      </c>
+      <c r="Z96">
         <v>1</v>
       </c>
       <c r="AA96">
@@ -19577,15 +19583,15 @@
       </c>
       <c r="AG96" t="str">
         <f t="shared" si="25"/>
-        <v>ashury2026errormap</v>
+        <v>rahamim2026will</v>
       </c>
       <c r="AH96" t="str">
         <f t="shared" si="26"/>
-        <v/>
+        <v>rahamim2026will</v>
       </c>
       <c r="AI96" t="str">
         <f t="shared" si="27"/>
-        <v/>
+        <v>rahamim2026will</v>
       </c>
       <c r="AK96">
         <f t="shared" si="28"/>
@@ -19602,13 +19608,13 @@
         <v>arxiv</v>
       </c>
       <c r="C97" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D97" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="E97" s="12" t="s">
         <v>362</v>
-      </c>
-      <c r="E97" s="12" t="s">
-        <v>363</v>
       </c>
       <c r="G97">
         <v>2026</v>
@@ -19619,13 +19625,10 @@
       <c r="O97">
         <v>1</v>
       </c>
-      <c r="P97">
+      <c r="Q97">
         <v>1</v>
       </c>
       <c r="T97">
-        <v>1</v>
-      </c>
-      <c r="X97">
         <v>1</v>
       </c>
       <c r="AA97">
@@ -19640,7 +19643,7 @@
       </c>
       <c r="AG97" t="str">
         <f t="shared" si="25"/>
-        <v>ashury2026robustness</v>
+        <v>ashury2026errormap</v>
       </c>
       <c r="AH97" t="str">
         <f t="shared" si="26"/>
@@ -19661,35 +19664,56 @@
         <v>97</v>
       </c>
       <c r="B98" t="str" cm="1">
-        <f t="array" ref="B98">_xlfn.IFS(ISBLANK(D99),"",ISBLANK(C98),"no venue",ISBLANK(#REF!),"no bib",ISNUMBER(SEARCH("xiv", C98)),"arxiv",SUM(I98:AA98)&lt;3,"no categories",TRUE,"")</f>
+        <f t="array" ref="B98">_xlfn.IFS(ISBLANK(D98),"",ISBLANK(C98),"no venue",ISBLANK(E98),"no bib",ISNUMBER(SEARCH("xiv", C98)),"arxiv",SUM(I98:AA98)&lt;3,"no categories",TRUE,"")</f>
         <v>arxiv</v>
       </c>
       <c r="C98" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="E98" s="12" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="G98">
         <v>2026</v>
       </c>
+      <c r="H98">
+        <v>1</v>
+      </c>
+      <c r="O98">
+        <v>1</v>
+      </c>
+      <c r="P98">
+        <v>1</v>
+      </c>
+      <c r="T98">
+        <v>1</v>
+      </c>
+      <c r="X98">
+        <v>1</v>
+      </c>
+      <c r="AA98">
+        <v>1</v>
+      </c>
+      <c r="AD98">
+        <v>1</v>
+      </c>
       <c r="AF98">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG98" t="str">
-        <f>IF(AF98,#REF!,"")</f>
+        <f t="shared" si="25"/>
+        <v>ashury2026robustness</v>
+      </c>
+      <c r="AH98" t="str">
+        <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="AH98" t="str">
-        <f>IF(W98,#REF!,"")</f>
-        <v/>
-      </c>
       <c r="AI98" t="str">
-        <f>IF(Y98,#REF!,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AK98">
@@ -19697,62 +19721,207 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:37" ht="17">
+    <row r="99" spans="1:37">
       <c r="A99">
         <f t="shared" si="23"/>
         <v>98</v>
       </c>
       <c r="B99" t="str" cm="1">
-        <f t="array" ref="B99">_xlfn.IFS(ISBLANK(#REF!),"",ISBLANK(C99),"no venue",ISBLANK(#REF!),"no bib",ISNUMBER(SEARCH("xiv", C99)),"arxiv",SUM(I99:AA99)&lt;3,"no categories",TRUE,"")</f>
+        <f t="array" ref="B99">_xlfn.IFS(ISBLANK(D100),"",ISBLANK(C99),"no venue",ISBLANK(#REF!),"no bib",ISNUMBER(SEARCH("xiv", C99)),"arxiv",SUM(I99:AA99)&lt;3,"no categories",TRUE,"")</f>
         <v>arxiv</v>
       </c>
       <c r="C99" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D99" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="E99" s="12" t="s">
         <v>368</v>
-      </c>
-      <c r="E99" s="12" t="s">
-        <v>371</v>
       </c>
       <c r="G99">
         <v>2026</v>
       </c>
-      <c r="AG99" s="8"/>
+      <c r="H99">
+        <v>1</v>
+      </c>
+      <c r="K99">
+        <v>1</v>
+      </c>
+      <c r="P99">
+        <v>1</v>
+      </c>
+      <c r="T99">
+        <v>1</v>
+      </c>
+      <c r="U99">
+        <v>1</v>
+      </c>
+      <c r="W99">
+        <v>1</v>
+      </c>
+      <c r="X99">
+        <v>1</v>
+      </c>
+      <c r="AA99">
+        <v>1</v>
+      </c>
+      <c r="AD99">
+        <v>1</v>
+      </c>
+      <c r="AF99">
+        <f t="shared" si="24"/>
+        <v>1</v>
+      </c>
+      <c r="AG99" t="e">
+        <f>IF(AF99,#REF!,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AH99" t="e">
+        <f>IF(W99,#REF!,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AI99" t="str">
+        <f>IF(Y99,#REF!,"")</f>
+        <v/>
+      </c>
+      <c r="AK99">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="1:37" ht="35">
+    <row r="100" spans="1:37" ht="17">
       <c r="A100">
         <f t="shared" si="23"/>
         <v>99</v>
       </c>
       <c r="B100" t="str" cm="1">
-        <f t="array" ref="B100">_xlfn.IFS(ISBLANK(D100),"",ISBLANK(C100),"no venue",ISBLANK(E100),"no bib",ISNUMBER(SEARCH("xiv", C100)),"arxiv",SUM(I100:AA100)&lt;3,"no categories",TRUE,"")</f>
+        <f t="array" ref="B100">_xlfn.IFS(ISBLANK(#REF!),"",ISBLANK(C100),"no venue",ISBLANK(#REF!),"no bib",ISNUMBER(SEARCH("xiv", C100)),"arxiv",SUM(I100:AA100)&lt;3,"no categories",TRUE,"")</f>
         <v>arxiv</v>
       </c>
       <c r="C100" t="s">
-        <v>342</v>
-      </c>
-      <c r="D100" s="16" t="s">
-        <v>372</v>
+        <v>340</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>366</v>
       </c>
       <c r="E100" s="12" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="G100">
         <v>2026</v>
       </c>
+      <c r="H100">
+        <v>1</v>
+      </c>
+      <c r="N100">
+        <v>1</v>
+      </c>
+      <c r="O100">
+        <v>1</v>
+      </c>
+      <c r="Q100">
+        <v>1</v>
+      </c>
+      <c r="R100">
+        <v>1</v>
+      </c>
+      <c r="T100">
+        <v>1</v>
+      </c>
+      <c r="W100">
+        <v>1</v>
+      </c>
+      <c r="X100">
+        <v>1</v>
+      </c>
+      <c r="Y100">
+        <v>1</v>
+      </c>
+      <c r="AA100">
+        <v>1</v>
+      </c>
+      <c r="AD100">
+        <v>1</v>
+      </c>
       <c r="AG100" s="8"/>
+      <c r="AH100" t="e">
+        <f>IF(W100,#REF!,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AK100">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="1:37" ht="17">
+    <row r="101" spans="1:37" ht="35">
       <c r="A101">
         <f t="shared" si="23"/>
         <v>100</v>
       </c>
       <c r="B101" t="str" cm="1">
         <f t="array" ref="B101">_xlfn.IFS(ISBLANK(D101),"",ISBLANK(C101),"no venue",ISBLANK(E101),"no bib",ISNUMBER(SEARCH("xiv", C101)),"arxiv",SUM(I101:AA101)&lt;3,"no categories",TRUE,"")</f>
-        <v/>
+        <v>arxiv</v>
+      </c>
+      <c r="C101" t="s">
+        <v>340</v>
+      </c>
+      <c r="D101" s="16" t="s">
+        <v>370</v>
+      </c>
+      <c r="E101" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="G101">
+        <v>2026</v>
+      </c>
+      <c r="H101">
+        <v>1</v>
+      </c>
+      <c r="O101">
+        <v>1</v>
+      </c>
+      <c r="Q101">
+        <v>1</v>
+      </c>
+      <c r="R101">
+        <v>1</v>
+      </c>
+      <c r="S101">
+        <v>1</v>
+      </c>
+      <c r="T101">
+        <v>1</v>
+      </c>
+      <c r="U101">
+        <v>1</v>
+      </c>
+      <c r="W101">
+        <v>1</v>
+      </c>
+      <c r="X101">
+        <v>1</v>
+      </c>
+      <c r="Y101">
+        <v>1</v>
+      </c>
+      <c r="Z101">
+        <v>1</v>
+      </c>
+      <c r="AA101">
+        <v>1</v>
+      </c>
+      <c r="AC101">
+        <v>1</v>
+      </c>
+      <c r="AD101">
+        <v>1</v>
       </c>
       <c r="AG101" s="8"/>
+      <c r="AK101">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="102" spans="1:37" ht="17">
       <c r="A102">
@@ -20041,6 +20210,14 @@
       <c r="AG127" s="8"/>
     </row>
     <row r="128" spans="1:33" ht="17">
+      <c r="A128">
+        <f t="shared" si="23"/>
+        <v>127</v>
+      </c>
+      <c r="B128" t="str" cm="1">
+        <f t="array" ref="B128">_xlfn.IFS(ISBLANK(D128),"",ISBLANK(C128),"no venue",ISBLANK(E128),"no bib",ISNUMBER(SEARCH("xiv", C128)),"arxiv",SUM(I128:AA128)&lt;3,"no categories",TRUE,"")</f>
+        <v/>
+      </c>
       <c r="AG128" s="8"/>
     </row>
     <row r="129" spans="7:36" ht="17">
@@ -20064,229 +20241,232 @@
     <row r="135" spans="7:36" ht="17">
       <c r="AG135" s="8"/>
     </row>
-    <row r="137" spans="7:36">
-      <c r="G137" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="H137">
-        <f>SUM(H2:H79)</f>
-        <v>77</v>
-      </c>
-      <c r="I137">
-        <f t="shared" ref="I137:N137" si="30">SUM(I2:I78)</f>
-        <v>6</v>
-      </c>
-      <c r="J137">
-        <f t="shared" si="30"/>
-        <v>5</v>
-      </c>
-      <c r="K137">
-        <f t="shared" si="30"/>
-        <v>11</v>
-      </c>
-      <c r="L137">
-        <f t="shared" si="30"/>
-        <v>2</v>
-      </c>
-      <c r="M137">
-        <f t="shared" si="30"/>
-        <v>4</v>
-      </c>
-      <c r="N137">
-        <f t="shared" si="30"/>
-        <v>4</v>
-      </c>
-      <c r="O137">
-        <f>SUM(O2:O79)</f>
-        <v>39</v>
-      </c>
-      <c r="P137">
-        <f>SUM(P2:P78)</f>
-        <v>42</v>
-      </c>
-      <c r="Q137">
-        <f>SUM(Q2:Q78)</f>
-        <v>43</v>
-      </c>
-      <c r="R137">
-        <f>SUM(R2:R78)</f>
-        <v>21</v>
-      </c>
-      <c r="S137">
-        <f>SUM(S2:S78)</f>
-        <v>32</v>
-      </c>
-      <c r="T137">
-        <f>SUM(T2:T79)</f>
-        <v>40</v>
-      </c>
-      <c r="U137">
-        <f>SUM(U2:U78)</f>
-        <v>15</v>
-      </c>
-      <c r="V137">
-        <f>SUM(V2:V78)</f>
-        <v>31</v>
-      </c>
-      <c r="W137">
-        <f>SUM(W2:W79)</f>
-        <v>33</v>
-      </c>
-      <c r="X137">
-        <f>SUM(X2:X78)</f>
-        <v>35</v>
-      </c>
-      <c r="Y137">
-        <f>SUM(Y2:Y79)</f>
-        <v>35</v>
-      </c>
-      <c r="Z137">
-        <f>SUM(Z2:Z78)</f>
-        <v>40</v>
-      </c>
-      <c r="AA137">
-        <f>SUM(AA2:AA78)</f>
-        <v>74</v>
-      </c>
-      <c r="AD137">
-        <f>COUNT(A2:A78)</f>
-        <v>77</v>
-      </c>
-      <c r="AE137">
-        <f>SUM(AE2:AE79)</f>
-        <v>7</v>
-      </c>
-      <c r="AF137">
-        <f>SUM(AF2:AF79)</f>
-        <v>63</v>
-      </c>
-      <c r="AG137" t="str">
-        <f>IF(AF137,E80,"")</f>
-        <v>ashurytahan2025mightytorrbenchmarktable</v>
-      </c>
-      <c r="AH137" t="str">
-        <f>IF(W137,E80,"")</f>
-        <v>ashurytahan2025mightytorrbenchmarktable</v>
-      </c>
-      <c r="AI137" t="str">
-        <f>IF(Y137,E80,"")</f>
-        <v>ashurytahan2025mightytorrbenchmarktable</v>
-      </c>
-      <c r="AJ137" t="str">
-        <f>IF(AE137,E80,"")</f>
-        <v>ashurytahan2025mightytorrbenchmarktable</v>
-      </c>
+    <row r="136" spans="7:36" ht="17">
+      <c r="AG136" s="8"/>
     </row>
     <row r="138" spans="7:36">
       <c r="G138" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="H138" s="7">
-        <f t="shared" ref="H138:AA138" si="31">H137/$AD$137</f>
-        <v>1</v>
-      </c>
-      <c r="I138" s="7">
-        <f t="shared" si="31"/>
+        <v>178</v>
+      </c>
+      <c r="H138">
+        <f>SUM(H2:H79)</f>
+        <v>77</v>
+      </c>
+      <c r="I138">
+        <f t="shared" ref="I138:N138" si="35">SUM(I2:I78)</f>
+        <v>6</v>
+      </c>
+      <c r="J138">
+        <f t="shared" si="35"/>
+        <v>5</v>
+      </c>
+      <c r="K138">
+        <f t="shared" si="35"/>
+        <v>11</v>
+      </c>
+      <c r="L138">
+        <f t="shared" si="35"/>
+        <v>2</v>
+      </c>
+      <c r="M138">
+        <f t="shared" si="35"/>
+        <v>4</v>
+      </c>
+      <c r="N138">
+        <f t="shared" si="35"/>
+        <v>5</v>
+      </c>
+      <c r="O138">
+        <f>SUM(O2:O79)</f>
+        <v>39</v>
+      </c>
+      <c r="P138">
+        <f>SUM(P2:P78)</f>
+        <v>42</v>
+      </c>
+      <c r="Q138">
+        <f>SUM(Q2:Q78)</f>
+        <v>43</v>
+      </c>
+      <c r="R138">
+        <f>SUM(R2:R78)</f>
+        <v>21</v>
+      </c>
+      <c r="S138">
+        <f>SUM(S2:S78)</f>
+        <v>32</v>
+      </c>
+      <c r="T138">
+        <f>SUM(T2:T79)</f>
+        <v>40</v>
+      </c>
+      <c r="U138">
+        <f>SUM(U2:U78)</f>
+        <v>15</v>
+      </c>
+      <c r="V138">
+        <f>SUM(V2:V78)</f>
+        <v>31</v>
+      </c>
+      <c r="W138">
+        <f>SUM(W2:W79)</f>
+        <v>33</v>
+      </c>
+      <c r="X138">
+        <f>SUM(X2:X78)</f>
+        <v>35</v>
+      </c>
+      <c r="Y138">
+        <f>SUM(Y2:Y79)</f>
+        <v>35</v>
+      </c>
+      <c r="Z138">
+        <f>SUM(Z2:Z78)</f>
+        <v>40</v>
+      </c>
+      <c r="AA138">
+        <f>SUM(AA2:AA78)</f>
+        <v>74</v>
+      </c>
+      <c r="AD138">
+        <f>COUNT(A2:A78)</f>
+        <v>77</v>
+      </c>
+      <c r="AE138">
+        <f>SUM(AE2:AE79)</f>
+        <v>7</v>
+      </c>
+      <c r="AF138">
+        <f>SUM(AF2:AF79)</f>
+        <v>63</v>
+      </c>
+      <c r="AG138" t="str">
+        <f>IF(AF138,E80,"")</f>
+        <v>ashurytahan2025mightytorrbenchmarktable</v>
+      </c>
+      <c r="AH138" t="str">
+        <f>IF(W138,E80,"")</f>
+        <v>ashurytahan2025mightytorrbenchmarktable</v>
+      </c>
+      <c r="AI138" t="str">
+        <f>IF(Y138,E80,"")</f>
+        <v>ashurytahan2025mightytorrbenchmarktable</v>
+      </c>
+      <c r="AJ138" t="str">
+        <f>IF(AE138,E80,"")</f>
+        <v>ashurytahan2025mightytorrbenchmarktable</v>
+      </c>
+    </row>
+    <row r="139" spans="7:36">
+      <c r="G139" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="H139" s="7">
+        <f t="shared" ref="H139:AA139" si="36">H138/$AD$138</f>
+        <v>1</v>
+      </c>
+      <c r="I139" s="7">
+        <f t="shared" si="36"/>
         <v>7.792207792207792E-2</v>
       </c>
-      <c r="J138" s="7">
-        <f t="shared" si="31"/>
+      <c r="J139" s="7">
+        <f t="shared" si="36"/>
         <v>6.4935064935064929E-2</v>
       </c>
-      <c r="K138" s="7">
-        <f t="shared" si="31"/>
+      <c r="K139" s="7">
+        <f t="shared" si="36"/>
         <v>0.14285714285714285</v>
       </c>
-      <c r="L138" s="7">
-        <f t="shared" si="31"/>
+      <c r="L139" s="7">
+        <f t="shared" si="36"/>
         <v>2.5974025974025976E-2</v>
       </c>
-      <c r="M138" s="7">
-        <f t="shared" si="31"/>
+      <c r="M139" s="7">
+        <f t="shared" si="36"/>
         <v>5.1948051948051951E-2</v>
       </c>
-      <c r="N138" s="7">
-        <f t="shared" si="31"/>
-        <v>5.1948051948051951E-2</v>
-      </c>
-      <c r="O138" s="7">
-        <f t="shared" si="31"/>
+      <c r="N139" s="7">
+        <f t="shared" si="36"/>
+        <v>6.4935064935064929E-2</v>
+      </c>
+      <c r="O139" s="7">
+        <f t="shared" si="36"/>
         <v>0.50649350649350644</v>
       </c>
-      <c r="P138" s="7">
-        <f t="shared" si="31"/>
+      <c r="P139" s="7">
+        <f t="shared" si="36"/>
         <v>0.54545454545454541</v>
       </c>
-      <c r="Q138" s="7">
-        <f t="shared" si="31"/>
+      <c r="Q139" s="7">
+        <f t="shared" si="36"/>
         <v>0.55844155844155841</v>
       </c>
-      <c r="R138" s="7">
-        <f t="shared" si="31"/>
+      <c r="R139" s="7">
+        <f t="shared" si="36"/>
         <v>0.27272727272727271</v>
       </c>
-      <c r="S138" s="7">
-        <f t="shared" si="31"/>
+      <c r="S139" s="7">
+        <f t="shared" si="36"/>
         <v>0.41558441558441561</v>
       </c>
-      <c r="T138" s="7">
-        <f t="shared" si="31"/>
+      <c r="T139" s="7">
+        <f t="shared" si="36"/>
         <v>0.51948051948051943</v>
       </c>
-      <c r="U138" s="7">
-        <f t="shared" si="31"/>
+      <c r="U139" s="7">
+        <f t="shared" si="36"/>
         <v>0.19480519480519481</v>
       </c>
-      <c r="V138" s="7">
-        <f t="shared" si="31"/>
+      <c r="V139" s="7">
+        <f t="shared" si="36"/>
         <v>0.40259740259740262</v>
       </c>
-      <c r="W138" s="7">
-        <f t="shared" si="31"/>
+      <c r="W139" s="7">
+        <f t="shared" si="36"/>
         <v>0.42857142857142855</v>
       </c>
-      <c r="X138" s="7">
-        <f t="shared" si="31"/>
+      <c r="X139" s="7">
+        <f t="shared" si="36"/>
         <v>0.45454545454545453</v>
       </c>
-      <c r="Y138" s="7">
-        <f t="shared" si="31"/>
+      <c r="Y139" s="7">
+        <f t="shared" si="36"/>
         <v>0.45454545454545453</v>
       </c>
-      <c r="Z138" s="7">
-        <f t="shared" si="31"/>
+      <c r="Z139" s="7">
+        <f t="shared" si="36"/>
         <v>0.51948051948051943</v>
       </c>
-      <c r="AA138" s="7">
-        <f t="shared" si="31"/>
+      <c r="AA139" s="7">
+        <f t="shared" si="36"/>
         <v>0.96103896103896103</v>
       </c>
-      <c r="AB138" s="7"/>
-      <c r="AC138" s="7"/>
-      <c r="AD138">
+      <c r="AB139" s="7"/>
+      <c r="AC139" s="7"/>
+      <c r="AD139">
         <f>COUNT(A3:A80)</f>
         <v>78</v>
       </c>
-      <c r="AG138" t="str">
-        <f>IF(AF138,#REF!,"")</f>
+      <c r="AG139" t="str">
+        <f>IF(AF139,#REF!,"")</f>
         <v/>
       </c>
-      <c r="AH138" t="e">
-        <f>IF(W138,#REF!,"")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AI138" t="e">
-        <f>IF(Y138,#REF!,"")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AJ138" t="str">
-        <f>IF(AE138,#REF!,"")</f>
+      <c r="AH139" t="e">
+        <f>IF(W139,#REF!,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AI139" t="e">
+        <f>IF(Y139,#REF!,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AJ139" t="str">
+        <f>IF(AE139,#REF!,"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AK78" xr:uid="{92277768-849A-7540-AC05-5E1BE041CC8E}"/>
-  <conditionalFormatting sqref="B2:B127">
+  <conditionalFormatting sqref="B2:B128">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -20342,16 +20522,17 @@
     <hyperlink ref="D87" r:id="rId41" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=8b8IhUYAAAAJ&amp;sortby=pubdate&amp;citation_for_view=8b8IhUYAAAAJ:cFHS6HbyZ2cC" xr:uid="{012D4D4B-F7DB-534F-929E-F3980EB01887}"/>
     <hyperlink ref="D89" r:id="rId42" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=8b8IhUYAAAAJ&amp;sortby=pubdate&amp;citation_for_view=8b8IhUYAAAAJ:OU6Ihb5iCvQC" xr:uid="{83F89CA5-9C53-454A-82C0-5B114240419E}"/>
     <hyperlink ref="D88" r:id="rId43" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=8b8IhUYAAAAJ&amp;sortby=pubdate&amp;citation_for_view=8b8IhUYAAAAJ:p2g8aNsByqUC" xr:uid="{F1C14A89-89CC-4F40-8425-EE9E1FA18475}"/>
-    <hyperlink ref="D90" r:id="rId44" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=8b8IhUYAAAAJ&amp;sortby=pubdate&amp;citation_for_view=8b8IhUYAAAAJ:738O_yMBCRsC" xr:uid="{7F06036E-46CB-7B4A-B5A9-01BD9FEB494D}"/>
-    <hyperlink ref="D91" r:id="rId45" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=8b8IhUYAAAAJ&amp;sortby=pubdate&amp;citation_for_view=8b8IhUYAAAAJ:K3LRdlH-MEoC" xr:uid="{E3BF1F50-9A61-BD47-80DD-3E7FA5F51488}"/>
-    <hyperlink ref="D92" r:id="rId46" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=8b8IhUYAAAAJ&amp;sortby=pubdate&amp;citation_for_view=8b8IhUYAAAAJ:tOudhMTPpwUC" xr:uid="{A1EF67F5-E28E-A14D-A57D-7545932AF158}"/>
-    <hyperlink ref="C92" r:id="rId47" display="BabyLM@EMNLP" xr:uid="{D8DDEF9E-B21E-CD40-A406-DFC0EB019B6A}"/>
-    <hyperlink ref="D93" r:id="rId48" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=8b8IhUYAAAAJ&amp;sortby=pubdate&amp;citation_for_view=8b8IhUYAAAAJ:4fKUyHm3Qg0C" xr:uid="{63AC3719-785D-4045-842F-51673617DEA4}"/>
-    <hyperlink ref="D95" r:id="rId49" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=8b8IhUYAAAAJ&amp;sortby=pubdate&amp;citation_for_view=8b8IhUYAAAAJ:B3FOqHPlNUQC" xr:uid="{4655ADB8-FEB9-6148-99F7-03736D7EB3B9}"/>
-    <hyperlink ref="D96" r:id="rId50" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=8b8IhUYAAAAJ&amp;sortby=pubdate&amp;citation_for_view=8b8IhUYAAAAJ:sSrBHYA8nusC" xr:uid="{94FB61E5-5F04-5645-A99F-119289B9E81D}"/>
-    <hyperlink ref="D97" r:id="rId51" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=8b8IhUYAAAAJ&amp;sortby=pubdate&amp;citation_for_view=8b8IhUYAAAAJ:5Ul4iDaHHb8C" xr:uid="{AC018292-7C41-B947-89FB-2E8002093149}"/>
-    <hyperlink ref="D99" r:id="rId52" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=8b8IhUYAAAAJ&amp;sortby=pubdate&amp;citation_for_view=8b8IhUYAAAAJ:eflP2zaiRacC" xr:uid="{60D0073E-0896-9C4A-A723-621180E109EC}"/>
-    <hyperlink ref="D98" r:id="rId53" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=8b8IhUYAAAAJ&amp;sortby=pubdate&amp;citation_for_view=8b8IhUYAAAAJ:VOx2b1Wkg3QC" xr:uid="{1B316D5B-F142-5C4C-8594-5D8D28179250}"/>
+    <hyperlink ref="D91" r:id="rId44" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=8b8IhUYAAAAJ&amp;sortby=pubdate&amp;citation_for_view=8b8IhUYAAAAJ:738O_yMBCRsC" xr:uid="{7F06036E-46CB-7B4A-B5A9-01BD9FEB494D}"/>
+    <hyperlink ref="D92" r:id="rId45" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=8b8IhUYAAAAJ&amp;sortby=pubdate&amp;citation_for_view=8b8IhUYAAAAJ:K3LRdlH-MEoC" xr:uid="{E3BF1F50-9A61-BD47-80DD-3E7FA5F51488}"/>
+    <hyperlink ref="D93" r:id="rId46" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=8b8IhUYAAAAJ&amp;sortby=pubdate&amp;citation_for_view=8b8IhUYAAAAJ:tOudhMTPpwUC" xr:uid="{A1EF67F5-E28E-A14D-A57D-7545932AF158}"/>
+    <hyperlink ref="C93" r:id="rId47" display="BabyLM@EMNLP" xr:uid="{D8DDEF9E-B21E-CD40-A406-DFC0EB019B6A}"/>
+    <hyperlink ref="D94" r:id="rId48" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=8b8IhUYAAAAJ&amp;sortby=pubdate&amp;citation_for_view=8b8IhUYAAAAJ:4fKUyHm3Qg0C" xr:uid="{63AC3719-785D-4045-842F-51673617DEA4}"/>
+    <hyperlink ref="D96" r:id="rId49" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=8b8IhUYAAAAJ&amp;sortby=pubdate&amp;citation_for_view=8b8IhUYAAAAJ:B3FOqHPlNUQC" xr:uid="{4655ADB8-FEB9-6148-99F7-03736D7EB3B9}"/>
+    <hyperlink ref="D97" r:id="rId50" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=8b8IhUYAAAAJ&amp;sortby=pubdate&amp;citation_for_view=8b8IhUYAAAAJ:sSrBHYA8nusC" xr:uid="{94FB61E5-5F04-5645-A99F-119289B9E81D}"/>
+    <hyperlink ref="D98" r:id="rId51" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=8b8IhUYAAAAJ&amp;sortby=pubdate&amp;citation_for_view=8b8IhUYAAAAJ:5Ul4iDaHHb8C" xr:uid="{AC018292-7C41-B947-89FB-2E8002093149}"/>
+    <hyperlink ref="D100" r:id="rId52" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=8b8IhUYAAAAJ&amp;sortby=pubdate&amp;citation_for_view=8b8IhUYAAAAJ:eflP2zaiRacC" xr:uid="{60D0073E-0896-9C4A-A723-621180E109EC}"/>
+    <hyperlink ref="D99" r:id="rId53" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=8b8IhUYAAAAJ&amp;sortby=pubdate&amp;citation_for_view=8b8IhUYAAAAJ:VOx2b1Wkg3QC" xr:uid="{1B316D5B-F142-5C4C-8594-5D8D28179250}"/>
+    <hyperlink ref="D63" r:id="rId54" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=8b8IhUYAAAAJ&amp;cstart=20&amp;pagesize=80&amp;sortby=pubdate&amp;citation_for_view=8b8IhUYAAAAJ:uWQEDVKXjbEC" xr:uid="{7F1AF470-D2BE-F040-AB43-BAACD4F06829}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -24574,7 +24755,7 @@
       </c>
       <c r="C61" t="str">
         <f>Sheet1!D63</f>
-        <v xml:space="preserve"> Learning from Naturally Occurring Feedback</v>
+        <v>Naturally occurring feedback is common, extractable and useful</v>
       </c>
       <c r="D61" t="str">
         <f>Sheet1!F63</f>
@@ -29625,7 +29806,7 @@
       </c>
       <c r="C61" t="str">
         <f>Sheet1!D63</f>
-        <v xml:space="preserve"> Learning from Naturally Occurring Feedback</v>
+        <v>Naturally occurring feedback is common, extractable and useful</v>
       </c>
       <c r="D61" t="str">
         <f>Sheet1!F63</f>

--- a/Contributions_table.xlsx
+++ b/Contributions_table.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lc/PycharmProjects/publications/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D359E718-0965-6D4D-AF45-A054575C6F7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B85019C-85BF-0946-A90F-470EED35ACAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{5AA491FB-7947-2140-ACD9-201A623594D0}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="396">
   <si>
     <t xml:space="preserve">EMNLP (under review) </t>
   </si>
@@ -1258,6 +1258,66 @@
   </si>
   <si>
     <t>How Safe is Your Safety Metric? Automatic Concatenation Tests for Metric Reliability</t>
+  </si>
+  <si>
+    <t>SURGeLLM</t>
+  </si>
+  <si>
+    <t>Do LLMs Benefit From Their Own Words?</t>
+  </si>
+  <si>
+    <t>Resolving Interference (RI): Disentangling Models for Improved Model Merging</t>
+  </si>
+  <si>
+    <t>CUBE: A Standard for Unifying Agent Benchmarks</t>
+  </si>
+  <si>
+    <t>Mediocrity is the key for LLM as a Judge Anchor Selection</t>
+  </si>
+  <si>
+    <t>Retrieval Augmented Generation Compositionality</t>
+  </si>
+  <si>
+    <t>EVALUATION CARDS: An Interpretive Layer for AI Evaluation Reporting</t>
+  </si>
+  <si>
+    <t>MindGames:A Multi-Agent Benchmark and Trajectory Dataset for Evaluating Social and Strategic Reasoning in LLMs</t>
+  </si>
+  <si>
+    <t>Every Eval Ever: A Unifying Schema and Community Repository for AI Evaluation Results</t>
+  </si>
+  <si>
+    <t>Instructions shape Production of Language, not Processing</t>
+  </si>
+  <si>
+    <t>Growing Pains: Extensible and Efficient LLM Benchmarking Via Fixed Parameter Calibration</t>
+  </si>
+  <si>
+    <t>akhtar2026ai</t>
+  </si>
+  <si>
+    <t>huang2026llmsbenefitwords</t>
+  </si>
+  <si>
+    <t>ghosh2026evaluationcardsinterpretivelayer</t>
+  </si>
+  <si>
+    <t>habba2026growing</t>
+  </si>
+  <si>
+    <t>waldis2026instructions</t>
+  </si>
+  <si>
+    <t>wang2026mindgameslivearenaevaluating</t>
+  </si>
+  <si>
+    <t>don2026mediocrity</t>
+  </si>
+  <si>
+    <t>lacoste2026cube</t>
+  </si>
+  <si>
+    <t>ramesh2026resolving</t>
   </si>
 </sst>
 </file>
@@ -18463,8 +18523,8 @@
         <f t="shared" si="23"/>
         <v>79</v>
       </c>
-      <c r="C80" t="s">
-        <v>319</v>
+      <c r="C80" s="13" t="s">
+        <v>376</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>318</v>
@@ -18491,6 +18551,9 @@
         <v>1</v>
       </c>
       <c r="AA80">
+        <v>1</v>
+      </c>
+      <c r="AB80">
         <v>1</v>
       </c>
       <c r="AD80">
@@ -19728,10 +19791,10 @@
       </c>
       <c r="B99" t="str" cm="1">
         <f t="array" ref="B99">_xlfn.IFS(ISBLANK(D100),"",ISBLANK(C99),"no venue",ISBLANK(#REF!),"no bib",ISNUMBER(SEARCH("xiv", C99)),"arxiv",SUM(I99:AA99)&lt;3,"no categories",TRUE,"")</f>
-        <v>arxiv</v>
+        <v/>
       </c>
       <c r="C99" t="s">
-        <v>340</v>
+        <v>182</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>367</v>
@@ -19861,10 +19924,10 @@
       </c>
       <c r="B101" t="str" cm="1">
         <f t="array" ref="B101">_xlfn.IFS(ISBLANK(D101),"",ISBLANK(C101),"no venue",ISBLANK(E101),"no bib",ISNUMBER(SEARCH("xiv", C101)),"arxiv",SUM(I101:AA101)&lt;3,"no categories",TRUE,"")</f>
-        <v>arxiv</v>
+        <v/>
       </c>
       <c r="C101" t="s">
-        <v>340</v>
+        <v>182</v>
       </c>
       <c r="D101" s="16" t="s">
         <v>370</v>
@@ -19930,7 +19993,22 @@
       </c>
       <c r="B102" t="str" cm="1">
         <f t="array" ref="B102">_xlfn.IFS(ISBLANK(D102),"",ISBLANK(C102),"no venue",ISBLANK(E102),"no bib",ISNUMBER(SEARCH("xiv", C102)),"arxiv",SUM(I102:AA102)&lt;3,"no categories",TRUE,"")</f>
-        <v/>
+        <v>no categories</v>
+      </c>
+      <c r="C102" t="s">
+        <v>182</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="E102" s="12" t="s">
+        <v>387</v>
+      </c>
+      <c r="G102">
+        <v>2026</v>
+      </c>
+      <c r="H102">
+        <v>1</v>
       </c>
       <c r="AG102" s="8"/>
     </row>
@@ -19941,7 +20019,22 @@
       </c>
       <c r="B103" t="str" cm="1">
         <f t="array" ref="B103">_xlfn.IFS(ISBLANK(D103),"",ISBLANK(C103),"no venue",ISBLANK(E103),"no bib",ISNUMBER(SEARCH("xiv", C103)),"arxiv",SUM(I103:AA103)&lt;3,"no categories",TRUE,"")</f>
-        <v/>
+        <v>arxiv</v>
+      </c>
+      <c r="C103" t="s">
+        <v>319</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="E103" s="12" t="s">
+        <v>388</v>
+      </c>
+      <c r="G103">
+        <v>2026</v>
+      </c>
+      <c r="H103">
+        <v>1</v>
       </c>
       <c r="AG103" s="8"/>
     </row>
@@ -19952,7 +20045,22 @@
       </c>
       <c r="B104" t="str" cm="1">
         <f t="array" ref="B104">_xlfn.IFS(ISBLANK(D104),"",ISBLANK(C104),"no venue",ISBLANK(E104),"no bib",ISNUMBER(SEARCH("xiv", C104)),"arxiv",SUM(I104:AA104)&lt;3,"no categories",TRUE,"")</f>
-        <v/>
+        <v>arxiv</v>
+      </c>
+      <c r="C104" t="s">
+        <v>319</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="E104" t="s">
+        <v>395</v>
+      </c>
+      <c r="G104">
+        <v>2026</v>
+      </c>
+      <c r="H104">
+        <v>1</v>
       </c>
       <c r="AG104" s="8"/>
     </row>
@@ -19963,7 +20071,22 @@
       </c>
       <c r="B105" t="str" cm="1">
         <f t="array" ref="B105">_xlfn.IFS(ISBLANK(D105),"",ISBLANK(C105),"no venue",ISBLANK(E105),"no bib",ISNUMBER(SEARCH("xiv", C105)),"arxiv",SUM(I105:AA105)&lt;3,"no categories",TRUE,"")</f>
-        <v/>
+        <v>arxiv</v>
+      </c>
+      <c r="C105" t="s">
+        <v>319</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="E105" t="s">
+        <v>394</v>
+      </c>
+      <c r="G105">
+        <v>2026</v>
+      </c>
+      <c r="H105">
+        <v>1</v>
       </c>
       <c r="AG105" s="8"/>
     </row>
@@ -19974,7 +20097,22 @@
       </c>
       <c r="B106" t="str" cm="1">
         <f t="array" ref="B106">_xlfn.IFS(ISBLANK(D106),"",ISBLANK(C106),"no venue",ISBLANK(E106),"no bib",ISNUMBER(SEARCH("xiv", C106)),"arxiv",SUM(I106:AA106)&lt;3,"no categories",TRUE,"")</f>
-        <v/>
+        <v>no categories</v>
+      </c>
+      <c r="C106" t="s">
+        <v>310</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="E106" s="12" t="s">
+        <v>393</v>
+      </c>
+      <c r="G106">
+        <v>2026</v>
+      </c>
+      <c r="H106">
+        <v>1</v>
       </c>
       <c r="AG106" s="8"/>
     </row>
@@ -19985,7 +20123,19 @@
       </c>
       <c r="B107" t="str" cm="1">
         <f t="array" ref="B107">_xlfn.IFS(ISBLANK(D107),"",ISBLANK(C107),"no venue",ISBLANK(E107),"no bib",ISNUMBER(SEARCH("xiv", C107)),"arxiv",SUM(I107:AA107)&lt;3,"no categories",TRUE,"")</f>
-        <v/>
+        <v>no bib</v>
+      </c>
+      <c r="C107" t="s">
+        <v>340</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="G107">
+        <v>2026</v>
+      </c>
+      <c r="H107">
+        <v>1</v>
       </c>
       <c r="AG107" s="8"/>
     </row>
@@ -19996,7 +20146,22 @@
       </c>
       <c r="B108" t="str" cm="1">
         <f t="array" ref="B108">_xlfn.IFS(ISBLANK(D108),"",ISBLANK(C108),"no venue",ISBLANK(E108),"no bib",ISNUMBER(SEARCH("xiv", C108)),"arxiv",SUM(I108:AA108)&lt;3,"no categories",TRUE,"")</f>
-        <v/>
+        <v>arxiv</v>
+      </c>
+      <c r="C108" t="s">
+        <v>340</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="E108" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="G108">
+        <v>2026</v>
+      </c>
+      <c r="H108">
+        <v>1</v>
       </c>
       <c r="AG108" s="8"/>
     </row>
@@ -20007,7 +20172,22 @@
       </c>
       <c r="B109" t="str" cm="1">
         <f t="array" ref="B109">_xlfn.IFS(ISBLANK(D109),"",ISBLANK(C109),"no venue",ISBLANK(E109),"no bib",ISNUMBER(SEARCH("xiv", C109)),"arxiv",SUM(I109:AA109)&lt;3,"no categories",TRUE,"")</f>
-        <v/>
+        <v>arxiv</v>
+      </c>
+      <c r="C109" t="s">
+        <v>340</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="E109" t="s">
+        <v>392</v>
+      </c>
+      <c r="G109">
+        <v>2026</v>
+      </c>
+      <c r="H109">
+        <v>1</v>
       </c>
       <c r="AG109" s="8"/>
     </row>
@@ -20018,7 +20198,19 @@
       </c>
       <c r="B110" t="str" cm="1">
         <f t="array" ref="B110">_xlfn.IFS(ISBLANK(D110),"",ISBLANK(C110),"no venue",ISBLANK(E110),"no bib",ISNUMBER(SEARCH("xiv", C110)),"arxiv",SUM(I110:AA110)&lt;3,"no categories",TRUE,"")</f>
-        <v/>
+        <v>no bib</v>
+      </c>
+      <c r="C110" t="s">
+        <v>340</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="G110">
+        <v>2026</v>
+      </c>
+      <c r="H110">
+        <v>1</v>
       </c>
       <c r="AG110" s="8"/>
     </row>
@@ -20029,7 +20221,22 @@
       </c>
       <c r="B111" t="str" cm="1">
         <f t="array" ref="B111">_xlfn.IFS(ISBLANK(D111),"",ISBLANK(C111),"no venue",ISBLANK(E111),"no bib",ISNUMBER(SEARCH("xiv", C111)),"arxiv",SUM(I111:AA111)&lt;3,"no categories",TRUE,"")</f>
-        <v/>
+        <v>arxiv</v>
+      </c>
+      <c r="C111" t="s">
+        <v>340</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="E111" t="s">
+        <v>391</v>
+      </c>
+      <c r="G111">
+        <v>2026</v>
+      </c>
+      <c r="H111">
+        <v>1</v>
       </c>
       <c r="AG111" s="8"/>
     </row>
@@ -20040,7 +20247,22 @@
       </c>
       <c r="B112" t="str" cm="1">
         <f t="array" ref="B112">_xlfn.IFS(ISBLANK(D112),"",ISBLANK(C112),"no venue",ISBLANK(E112),"no bib",ISNUMBER(SEARCH("xiv", C112)),"arxiv",SUM(I112:AA112)&lt;3,"no categories",TRUE,"")</f>
-        <v/>
+        <v>arxiv</v>
+      </c>
+      <c r="C112" t="s">
+        <v>340</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="E112" s="12" t="s">
+        <v>390</v>
+      </c>
+      <c r="G112">
+        <v>2026</v>
+      </c>
+      <c r="H112">
+        <v>1</v>
       </c>
       <c r="AG112" s="8"/>
     </row>
@@ -20053,6 +20275,12 @@
         <f t="array" ref="B113">_xlfn.IFS(ISBLANK(D113),"",ISBLANK(C113),"no venue",ISBLANK(E113),"no bib",ISNUMBER(SEARCH("xiv", C113)),"arxiv",SUM(I113:AA113)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
+      <c r="G113">
+        <v>2026</v>
+      </c>
+      <c r="H113">
+        <v>1</v>
+      </c>
       <c r="AG113" s="8"/>
     </row>
     <row r="114" spans="1:33" ht="17">
@@ -20064,6 +20292,12 @@
         <f t="array" ref="B114">_xlfn.IFS(ISBLANK(D114),"",ISBLANK(C114),"no venue",ISBLANK(E114),"no bib",ISNUMBER(SEARCH("xiv", C114)),"arxiv",SUM(I114:AA114)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
+      <c r="G114">
+        <v>2026</v>
+      </c>
+      <c r="H114">
+        <v>1</v>
+      </c>
       <c r="AG114" s="8"/>
     </row>
     <row r="115" spans="1:33" ht="17">
@@ -20075,6 +20309,12 @@
         <f t="array" ref="B115">_xlfn.IFS(ISBLANK(D115),"",ISBLANK(C115),"no venue",ISBLANK(E115),"no bib",ISNUMBER(SEARCH("xiv", C115)),"arxiv",SUM(I115:AA115)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
+      <c r="G115">
+        <v>2026</v>
+      </c>
+      <c r="H115">
+        <v>1</v>
+      </c>
       <c r="AG115" s="8"/>
     </row>
     <row r="116" spans="1:33" ht="17">
@@ -20085,6 +20325,12 @@
       <c r="B116" t="str" cm="1">
         <f t="array" ref="B116">_xlfn.IFS(ISBLANK(D116),"",ISBLANK(C116),"no venue",ISBLANK(E116),"no bib",ISNUMBER(SEARCH("xiv", C116)),"arxiv",SUM(I116:AA116)&lt;3,"no categories",TRUE,"")</f>
         <v/>
+      </c>
+      <c r="G116">
+        <v>2026</v>
+      </c>
+      <c r="H116">
+        <v>1</v>
       </c>
       <c r="AG116" s="8"/>
     </row>
@@ -20533,6 +20779,17 @@
     <hyperlink ref="D100" r:id="rId52" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=8b8IhUYAAAAJ&amp;sortby=pubdate&amp;citation_for_view=8b8IhUYAAAAJ:eflP2zaiRacC" xr:uid="{60D0073E-0896-9C4A-A723-621180E109EC}"/>
     <hyperlink ref="D99" r:id="rId53" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=8b8IhUYAAAAJ&amp;sortby=pubdate&amp;citation_for_view=8b8IhUYAAAAJ:VOx2b1Wkg3QC" xr:uid="{1B316D5B-F142-5C4C-8594-5D8D28179250}"/>
     <hyperlink ref="D63" r:id="rId54" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=8b8IhUYAAAAJ&amp;cstart=20&amp;pagesize=80&amp;sortby=pubdate&amp;citation_for_view=8b8IhUYAAAAJ:uWQEDVKXjbEC" xr:uid="{7F1AF470-D2BE-F040-AB43-BAACD4F06829}"/>
+    <hyperlink ref="D102" r:id="rId55" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=8b8IhUYAAAAJ&amp;sortby=pubdate&amp;citation_for_view=8b8IhUYAAAAJ:VOx2b1Wkg3QC" xr:uid="{88882A9D-71EC-B14C-A2F2-D36F2D913217}"/>
+    <hyperlink ref="D103" r:id="rId56" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=8b8IhUYAAAAJ&amp;sortby=pubdate&amp;citation_for_view=8b8IhUYAAAAJ:BrmTIyaxlBUC" xr:uid="{40A95974-4931-1347-B1EA-931DF866B8B8}"/>
+    <hyperlink ref="D104" r:id="rId57" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=8b8IhUYAAAAJ&amp;sortby=pubdate&amp;citation_for_view=8b8IhUYAAAAJ:eJXPG6dFmWUC" xr:uid="{4277D77C-BEE6-9943-B001-B6431DE5101A}"/>
+    <hyperlink ref="D105" r:id="rId58" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=8b8IhUYAAAAJ&amp;sortby=pubdate&amp;citation_for_view=8b8IhUYAAAAJ:olpn-zPbct0C" xr:uid="{CDEFCD25-5DC1-994B-86C9-4F01AD212B01}"/>
+    <hyperlink ref="D106" r:id="rId59" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=8b8IhUYAAAAJ&amp;sortby=pubdate&amp;citation_for_view=8b8IhUYAAAAJ:XiVPGOgt02cC" xr:uid="{63456DBE-F5FD-E341-BD9E-0B5379B18121}"/>
+    <hyperlink ref="D107" r:id="rId60" display="https://openreview.net/forum?id=U3y1Frmoe1&amp;referrer=%5BAuthor%20Console%5D(%2Fgroup%3Fid%3DNeurIPS.cc%2F2026%2FConference%2FAuthors%23your-submissions)" xr:uid="{2B7B4B89-8273-BF4F-A5DB-C60614571009}"/>
+    <hyperlink ref="D108" r:id="rId61" display="https://openreview.net/forum?id=jGvGY7wh7Q&amp;referrer=%5BAuthor%20Console%5D(%2Fgroup%3Fid%3DNeurIPS.cc%2F2026%2FEvaluations_and_Datasets_Track%2FAuthors%23your-submissions)" xr:uid="{3D552B99-CE16-8A42-A283-D779E3763777}"/>
+    <hyperlink ref="D109" r:id="rId62" display="https://openreview.net/forum?id=4WI2wAgqbO&amp;referrer=%5BAuthor%20Console%5D(%2Fgroup%3Fid%3DNeurIPS.cc%2F2026%2FEvaluations_and_Datasets_Track%2FAuthors%23your-submissions)" xr:uid="{BED8F70D-B43B-3C49-88DA-FC9B8CBF4297}"/>
+    <hyperlink ref="D110" r:id="rId63" display="https://openreview.net/forum?id=oJ2jfLaMhc&amp;referrer=%5BAuthor%20Console%5D(%2Fgroup%3Fid%3DNeurIPS.cc%2F2026%2FEvaluations_and_Datasets_Track%2FAuthors%23your-submissions)" xr:uid="{081D8B67-674B-A44E-925D-085EC394DF0D}"/>
+    <hyperlink ref="D111" r:id="rId64" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=8b8IhUYAAAAJ&amp;sortby=pubdate&amp;citation_for_view=8b8IhUYAAAAJ:eMMeJKvmdy0C" xr:uid="{98F1A3BF-BA8A-204C-8C02-DF70061D6776}"/>
+    <hyperlink ref="D112" r:id="rId65" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=8b8IhUYAAAAJ&amp;sortby=pubdate&amp;citation_for_view=8b8IhUYAAAAJ:HE397vMXCloC" xr:uid="{C7AA973C-294C-D344-BE65-3529A85E213A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/Contributions_table.xlsx
+++ b/Contributions_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lc/PycharmProjects/publications/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B85019C-85BF-0946-A90F-470EED35ACAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91506202-1311-DE49-B8E5-89AC03A88D16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{5AA491FB-7947-2140-ACD9-201A623594D0}"/>
   </bookViews>
@@ -14023,7 +14023,7 @@
         <v>89</v>
       </c>
       <c r="G22">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H22">
         <v>1</v>
@@ -14088,7 +14088,7 @@
         <v>87</v>
       </c>
       <c r="G23">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H23">
         <v>1</v>
@@ -22290,7 +22290,7 @@
       </c>
       <c r="E22">
         <f>Sheet1!G22</f>
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F22" t="e">
         <f>F23+Sheet1!O22</f>
@@ -22360,7 +22360,7 @@
       </c>
       <c r="E23">
         <f>Sheet1!G23</f>
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F23" t="e">
         <f>F24+Sheet1!O23</f>
@@ -27341,7 +27341,7 @@
       </c>
       <c r="E22">
         <f>Sheet1!G22</f>
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F22" t="e">
         <f>Commulative!F22/Commulative!$A22</f>
@@ -27411,7 +27411,7 @@
       </c>
       <c r="E23">
         <f>Sheet1!G23</f>
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F23" t="e">
         <f>Commulative!F23/Commulative!$A23</f>

--- a/Contributions_table.xlsx
+++ b/Contributions_table.xlsx
@@ -555,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK152"/>
+  <dimension ref="A1:AK153"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="29.5" customWidth="1" min="4" max="4"/>
@@ -9654,29 +9654,38 @@
       </c>
     </row>
     <row r="126" ht="17" customHeight="1">
-      <c r="A126">
-        <f>1+A112</f>
-        <v/>
-      </c>
-      <c r="B126">
-        <f>_xlfn.IFS(ISBLANK(D113),"",ISBLANK(C113),"no venue",ISBLANK(E113),"no bib",ISNUMBER(SEARCH("xiv", C113)),"arxiv",SUM(I113:AA113)&lt;3,"no categories",TRUE,"")</f>
-        <v/>
+      <c r="A126" t="n">
+        <v>16</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>arXiv preprint arXiv:2606.24579, 2026</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Cross-Lingual Exploration for Parametric Knowledge</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>E Diskind, I Trainin, U Shaham, L Choshen, I Szpektor, O Abend</t>
+        </is>
       </c>
       <c r="G126" t="n">
         <v>2026</v>
       </c>
-      <c r="H126" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG126" s="8" t="n"/>
+      <c r="AA126" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="127" ht="17" customHeight="1">
       <c r="A127">
-        <f>1+A113</f>
+        <f>1+A112</f>
         <v/>
       </c>
       <c r="B127">
-        <f>_xlfn.IFS(ISBLANK(D114),"",ISBLANK(C114),"no venue",ISBLANK(E114),"no bib",ISNUMBER(SEARCH("xiv", C114)),"arxiv",SUM(I114:AA114)&lt;3,"no categories",TRUE,"")</f>
+        <f>_xlfn.IFS(ISBLANK(D113),"",ISBLANK(C113),"no venue",ISBLANK(E113),"no bib",ISNUMBER(SEARCH("xiv", C113)),"arxiv",SUM(I113:AA113)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="G127" t="n">
@@ -9689,11 +9698,11 @@
     </row>
     <row r="128" ht="17" customHeight="1">
       <c r="A128">
-        <f>1+A114</f>
+        <f>1+A113</f>
         <v/>
       </c>
       <c r="B128">
-        <f>_xlfn.IFS(ISBLANK(D115),"",ISBLANK(C115),"no venue",ISBLANK(E115),"no bib",ISNUMBER(SEARCH("xiv", C115)),"arxiv",SUM(I115:AA115)&lt;3,"no categories",TRUE,"")</f>
+        <f>_xlfn.IFS(ISBLANK(D114),"",ISBLANK(C114),"no venue",ISBLANK(E114),"no bib",ISNUMBER(SEARCH("xiv", C114)),"arxiv",SUM(I114:AA114)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="G128" t="n">
@@ -9706,11 +9715,11 @@
     </row>
     <row r="129" ht="17" customHeight="1">
       <c r="A129">
-        <f>1+A115</f>
+        <f>1+A114</f>
         <v/>
       </c>
       <c r="B129">
-        <f>_xlfn.IFS(ISBLANK(D116),"",ISBLANK(C116),"no venue",ISBLANK(E116),"no bib",ISNUMBER(SEARCH("xiv", C116)),"arxiv",SUM(I116:AA116)&lt;3,"no categories",TRUE,"")</f>
+        <f>_xlfn.IFS(ISBLANK(D115),"",ISBLANK(C115),"no venue",ISBLANK(E115),"no bib",ISNUMBER(SEARCH("xiv", C115)),"arxiv",SUM(I115:AA115)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="G129" t="n">
@@ -9723,137 +9732,151 @@
     </row>
     <row r="130" ht="17" customHeight="1">
       <c r="A130">
-        <f>1+A116</f>
+        <f>1+A115</f>
         <v/>
       </c>
       <c r="B130">
-        <f>_xlfn.IFS(ISBLANK(D117),"",ISBLANK(C117),"no venue",ISBLANK(E117),"no bib",ISNUMBER(SEARCH("xiv", C117)),"arxiv",SUM(I117:AA117)&lt;3,"no categories",TRUE,"")</f>
-        <v/>
+        <f>_xlfn.IFS(ISBLANK(D116),"",ISBLANK(C116),"no venue",ISBLANK(E116),"no bib",ISNUMBER(SEARCH("xiv", C116)),"arxiv",SUM(I116:AA116)&lt;3,"no categories",TRUE,"")</f>
+        <v/>
+      </c>
+      <c r="G130" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H130" t="n">
+        <v>1</v>
       </c>
       <c r="AG130" s="8" t="n"/>
     </row>
     <row r="131" ht="17" customHeight="1">
       <c r="A131">
-        <f>1+A117</f>
+        <f>1+A116</f>
         <v/>
       </c>
       <c r="B131">
-        <f>_xlfn.IFS(ISBLANK(D118),"",ISBLANK(C118),"no venue",ISBLANK(E118),"no bib",ISNUMBER(SEARCH("xiv", C118)),"arxiv",SUM(I118:AA118)&lt;3,"no categories",TRUE,"")</f>
+        <f>_xlfn.IFS(ISBLANK(D117),"",ISBLANK(C117),"no venue",ISBLANK(E117),"no bib",ISNUMBER(SEARCH("xiv", C117)),"arxiv",SUM(I117:AA117)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="AG131" s="8" t="n"/>
     </row>
     <row r="132" ht="17" customHeight="1">
       <c r="A132">
-        <f>1+A118</f>
+        <f>1+A117</f>
         <v/>
       </c>
       <c r="B132">
-        <f>_xlfn.IFS(ISBLANK(D119),"",ISBLANK(C119),"no venue",ISBLANK(E119),"no bib",ISNUMBER(SEARCH("xiv", C119)),"arxiv",SUM(I119:AA119)&lt;3,"no categories",TRUE,"")</f>
+        <f>_xlfn.IFS(ISBLANK(D118),"",ISBLANK(C118),"no venue",ISBLANK(E118),"no bib",ISNUMBER(SEARCH("xiv", C118)),"arxiv",SUM(I118:AA118)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="AG132" s="8" t="n"/>
     </row>
     <row r="133" ht="17" customHeight="1">
       <c r="A133">
-        <f>1+A119</f>
+        <f>1+A118</f>
         <v/>
       </c>
       <c r="B133">
-        <f>_xlfn.IFS(ISBLANK(D120),"",ISBLANK(C120),"no venue",ISBLANK(E120),"no bib",ISNUMBER(SEARCH("xiv", C120)),"arxiv",SUM(I120:AA120)&lt;3,"no categories",TRUE,"")</f>
+        <f>_xlfn.IFS(ISBLANK(D119),"",ISBLANK(C119),"no venue",ISBLANK(E119),"no bib",ISNUMBER(SEARCH("xiv", C119)),"arxiv",SUM(I119:AA119)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="AG133" s="8" t="n"/>
     </row>
     <row r="134" ht="17" customHeight="1">
       <c r="A134">
-        <f>1+A120</f>
+        <f>1+A119</f>
         <v/>
       </c>
       <c r="B134">
-        <f>_xlfn.IFS(ISBLANK(D121),"",ISBLANK(C121),"no venue",ISBLANK(E121),"no bib",ISNUMBER(SEARCH("xiv", C121)),"arxiv",SUM(I121:AA121)&lt;3,"no categories",TRUE,"")</f>
+        <f>_xlfn.IFS(ISBLANK(D120),"",ISBLANK(C120),"no venue",ISBLANK(E120),"no bib",ISNUMBER(SEARCH("xiv", C120)),"arxiv",SUM(I120:AA120)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="AG134" s="8" t="n"/>
     </row>
     <row r="135" ht="17" customHeight="1">
       <c r="A135">
-        <f>1+A121</f>
+        <f>1+A120</f>
         <v/>
       </c>
       <c r="B135">
-        <f>_xlfn.IFS(ISBLANK(D122),"",ISBLANK(C122),"no venue",ISBLANK(E122),"no bib",ISNUMBER(SEARCH("xiv", C122)),"arxiv",SUM(I122:AA122)&lt;3,"no categories",TRUE,"")</f>
+        <f>_xlfn.IFS(ISBLANK(D121),"",ISBLANK(C121),"no venue",ISBLANK(E121),"no bib",ISNUMBER(SEARCH("xiv", C121)),"arxiv",SUM(I121:AA121)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="AG135" s="8" t="n"/>
     </row>
     <row r="136" ht="17" customHeight="1">
       <c r="A136">
-        <f>1+A122</f>
+        <f>1+A121</f>
         <v/>
       </c>
       <c r="B136">
-        <f>_xlfn.IFS(ISBLANK(D123),"",ISBLANK(C123),"no venue",ISBLANK(E123),"no bib",ISNUMBER(SEARCH("xiv", C123)),"arxiv",SUM(I123:AA123)&lt;3,"no categories",TRUE,"")</f>
+        <f>_xlfn.IFS(ISBLANK(D122),"",ISBLANK(C122),"no venue",ISBLANK(E122),"no bib",ISNUMBER(SEARCH("xiv", C122)),"arxiv",SUM(I122:AA122)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="AG136" s="8" t="n"/>
     </row>
     <row r="137" ht="17" customHeight="1">
       <c r="A137">
-        <f>1+A123</f>
+        <f>1+A122</f>
         <v/>
       </c>
       <c r="B137">
-        <f>_xlfn.IFS(ISBLANK(D124),"",ISBLANK(C124),"no venue",ISBLANK(E124),"no bib",ISNUMBER(SEARCH("xiv", C124)),"arxiv",SUM(I124:AA124)&lt;3,"no categories",TRUE,"")</f>
+        <f>_xlfn.IFS(ISBLANK(D123),"",ISBLANK(C123),"no venue",ISBLANK(E123),"no bib",ISNUMBER(SEARCH("xiv", C123)),"arxiv",SUM(I123:AA123)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="AG137" s="8" t="n"/>
     </row>
     <row r="138" ht="17" customHeight="1">
       <c r="A138">
-        <f>1+A124</f>
+        <f>1+A123</f>
         <v/>
       </c>
       <c r="B138">
-        <f>_xlfn.IFS(ISBLANK(D125),"",ISBLANK(C125),"no venue",ISBLANK(E125),"no bib",ISNUMBER(SEARCH("xiv", C125)),"arxiv",SUM(I125:AA125)&lt;3,"no categories",TRUE,"")</f>
+        <f>_xlfn.IFS(ISBLANK(D124),"",ISBLANK(C124),"no venue",ISBLANK(E124),"no bib",ISNUMBER(SEARCH("xiv", C124)),"arxiv",SUM(I124:AA124)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="AG138" s="8" t="n"/>
     </row>
     <row r="139" ht="17" customHeight="1">
       <c r="A139">
-        <f>1+A125</f>
+        <f>1+A124</f>
         <v/>
       </c>
       <c r="B139">
-        <f>_xlfn.IFS(ISBLANK(D126),"",ISBLANK(C126),"no venue",ISBLANK(E126),"no bib",ISNUMBER(SEARCH("xiv", C126)),"arxiv",SUM(I126:AA126)&lt;3,"no categories",TRUE,"")</f>
+        <f>_xlfn.IFS(ISBLANK(D125),"",ISBLANK(C125),"no venue",ISBLANK(E125),"no bib",ISNUMBER(SEARCH("xiv", C125)),"arxiv",SUM(I125:AA125)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="AG139" s="8" t="n"/>
     </row>
     <row r="140" ht="17" customHeight="1">
       <c r="A140">
-        <f>1+A126</f>
+        <f>1+A125</f>
         <v/>
       </c>
       <c r="B140">
-        <f>_xlfn.IFS(ISBLANK(D127),"",ISBLANK(C127),"no venue",ISBLANK(E127),"no bib",ISNUMBER(SEARCH("xiv", C127)),"arxiv",SUM(I127:AA127)&lt;3,"no categories",TRUE,"")</f>
+        <f>_xlfn.IFS(ISBLANK(D126),"",ISBLANK(C126),"no venue",ISBLANK(E126),"no bib",ISNUMBER(SEARCH("xiv", C126)),"arxiv",SUM(I126:AA126)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
       <c r="AG140" s="8" t="n"/>
     </row>
     <row r="141" ht="17" customHeight="1">
       <c r="A141">
+        <f>1+A126</f>
+        <v/>
+      </c>
+      <c r="B141">
+        <f>_xlfn.IFS(ISBLANK(D127),"",ISBLANK(C127),"no venue",ISBLANK(E127),"no bib",ISNUMBER(SEARCH("xiv", C127)),"arxiv",SUM(I127:AA127)&lt;3,"no categories",TRUE,"")</f>
+        <v/>
+      </c>
+      <c r="AG141" s="8" t="n"/>
+    </row>
+    <row r="142" ht="17" customHeight="1">
+      <c r="A142">
         <f>1+A127</f>
         <v/>
       </c>
-      <c r="B141">
+      <c r="B142">
         <f>_xlfn.IFS(ISBLANK(D128),"",ISBLANK(C128),"no venue",ISBLANK(E128),"no bib",ISNUMBER(SEARCH("xiv", C128)),"arxiv",SUM(I128:AA128)&lt;3,"no categories",TRUE,"")</f>
         <v/>
       </c>
-      <c r="AG141" s="8" t="n"/>
-    </row>
-    <row r="142" ht="17" customHeight="1">
       <c r="AG142" s="8" t="n"/>
     </row>
     <row r="143" ht="17" customHeight="1">
@@ -9877,227 +9900,230 @@
     <row r="149" ht="17" customHeight="1">
       <c r="AG149" s="8" t="n"/>
     </row>
-    <row r="150" ht="17" customHeight="1"/>
-    <row r="151">
-      <c r="G151" s="1" t="inlineStr">
-        <is>
-          <t>sum:</t>
-        </is>
-      </c>
-      <c r="H151">
-        <f>SUM(H2:H79)</f>
-        <v/>
-      </c>
-      <c r="I151">
-        <f>SUM(I2:I78)</f>
-        <v/>
-      </c>
-      <c r="J151">
-        <f>SUM(J2:J78)</f>
-        <v/>
-      </c>
-      <c r="K151">
-        <f>SUM(K2:K78)</f>
-        <v/>
-      </c>
-      <c r="L151">
-        <f>SUM(L2:L78)</f>
-        <v/>
-      </c>
-      <c r="M151">
-        <f>SUM(M2:M78)</f>
-        <v/>
-      </c>
-      <c r="N151">
-        <f>SUM(N2:N78)</f>
-        <v/>
-      </c>
-      <c r="O151">
-        <f>SUM(O2:O79)</f>
-        <v/>
-      </c>
-      <c r="P151">
-        <f>SUM(P2:P78)</f>
-        <v/>
-      </c>
-      <c r="Q151">
-        <f>SUM(Q2:Q78)</f>
-        <v/>
-      </c>
-      <c r="R151">
-        <f>SUM(R2:R78)</f>
-        <v/>
-      </c>
-      <c r="S151">
-        <f>SUM(S2:S78)</f>
-        <v/>
-      </c>
-      <c r="T151">
-        <f>SUM(T2:T79)</f>
-        <v/>
-      </c>
-      <c r="U151">
-        <f>SUM(U2:U78)</f>
-        <v/>
-      </c>
-      <c r="V151">
-        <f>SUM(V2:V78)</f>
-        <v/>
-      </c>
-      <c r="W151">
-        <f>SUM(W2:W79)</f>
-        <v/>
-      </c>
-      <c r="X151">
-        <f>SUM(X2:X78)</f>
-        <v/>
-      </c>
-      <c r="Y151">
-        <f>SUM(Y2:Y79)</f>
-        <v/>
-      </c>
-      <c r="Z151">
-        <f>SUM(Z2:Z78)</f>
-        <v/>
-      </c>
-      <c r="AA151">
-        <f>SUM(AA2:AA78)</f>
-        <v/>
-      </c>
-      <c r="AD151">
-        <f>COUNT(A2:A78)</f>
-        <v/>
-      </c>
-      <c r="AE151">
-        <f>SUM(AE2:AE79)</f>
-        <v/>
-      </c>
-      <c r="AF151">
-        <f>SUM(AF2:AF79)</f>
-        <v/>
-      </c>
-      <c r="AG151">
-        <f>IF(AF138,E80,"")</f>
-        <v/>
-      </c>
-      <c r="AH151">
-        <f>IF(W138,E80,"")</f>
-        <v/>
-      </c>
-      <c r="AI151">
-        <f>IF(Y138,E80,"")</f>
-        <v/>
-      </c>
-      <c r="AJ151">
-        <f>IF(AE138,E80,"")</f>
-        <v/>
-      </c>
-    </row>
+    <row r="150" ht="17" customHeight="1">
+      <c r="AG150" s="8" t="n"/>
+    </row>
+    <row r="151"/>
     <row r="152">
       <c r="G152" s="1" t="inlineStr">
         <is>
+          <t>sum:</t>
+        </is>
+      </c>
+      <c r="H152">
+        <f>SUM(H2:H79)</f>
+        <v/>
+      </c>
+      <c r="I152">
+        <f>SUM(I2:I78)</f>
+        <v/>
+      </c>
+      <c r="J152">
+        <f>SUM(J2:J78)</f>
+        <v/>
+      </c>
+      <c r="K152">
+        <f>SUM(K2:K78)</f>
+        <v/>
+      </c>
+      <c r="L152">
+        <f>SUM(L2:L78)</f>
+        <v/>
+      </c>
+      <c r="M152">
+        <f>SUM(M2:M78)</f>
+        <v/>
+      </c>
+      <c r="N152">
+        <f>SUM(N2:N78)</f>
+        <v/>
+      </c>
+      <c r="O152">
+        <f>SUM(O2:O79)</f>
+        <v/>
+      </c>
+      <c r="P152">
+        <f>SUM(P2:P78)</f>
+        <v/>
+      </c>
+      <c r="Q152">
+        <f>SUM(Q2:Q78)</f>
+        <v/>
+      </c>
+      <c r="R152">
+        <f>SUM(R2:R78)</f>
+        <v/>
+      </c>
+      <c r="S152">
+        <f>SUM(S2:S78)</f>
+        <v/>
+      </c>
+      <c r="T152">
+        <f>SUM(T2:T79)</f>
+        <v/>
+      </c>
+      <c r="U152">
+        <f>SUM(U2:U78)</f>
+        <v/>
+      </c>
+      <c r="V152">
+        <f>SUM(V2:V78)</f>
+        <v/>
+      </c>
+      <c r="W152">
+        <f>SUM(W2:W79)</f>
+        <v/>
+      </c>
+      <c r="X152">
+        <f>SUM(X2:X78)</f>
+        <v/>
+      </c>
+      <c r="Y152">
+        <f>SUM(Y2:Y79)</f>
+        <v/>
+      </c>
+      <c r="Z152">
+        <f>SUM(Z2:Z78)</f>
+        <v/>
+      </c>
+      <c r="AA152">
+        <f>SUM(AA2:AA78)</f>
+        <v/>
+      </c>
+      <c r="AD152">
+        <f>COUNT(A2:A78)</f>
+        <v/>
+      </c>
+      <c r="AE152">
+        <f>SUM(AE2:AE79)</f>
+        <v/>
+      </c>
+      <c r="AF152">
+        <f>SUM(AF2:AF79)</f>
+        <v/>
+      </c>
+      <c r="AG152">
+        <f>IF(AF138,E80,"")</f>
+        <v/>
+      </c>
+      <c r="AH152">
+        <f>IF(W138,E80,"")</f>
+        <v/>
+      </c>
+      <c r="AI152">
+        <f>IF(Y138,E80,"")</f>
+        <v/>
+      </c>
+      <c r="AJ152">
+        <f>IF(AE138,E80,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="153">
+      <c r="G153" s="1" t="inlineStr">
+        <is>
           <t>AVG:</t>
         </is>
       </c>
-      <c r="H152" s="7">
+      <c r="H153" s="7">
         <f>H138/$AD$138</f>
         <v/>
       </c>
-      <c r="I152" s="7">
+      <c r="I153" s="7">
         <f>I138/$AD$138</f>
         <v/>
       </c>
-      <c r="J152" s="7">
+      <c r="J153" s="7">
         <f>J138/$AD$138</f>
         <v/>
       </c>
-      <c r="K152" s="7">
+      <c r="K153" s="7">
         <f>K138/$AD$138</f>
         <v/>
       </c>
-      <c r="L152" s="7">
+      <c r="L153" s="7">
         <f>L138/$AD$138</f>
         <v/>
       </c>
-      <c r="M152" s="7">
+      <c r="M153" s="7">
         <f>M138/$AD$138</f>
         <v/>
       </c>
-      <c r="N152" s="7">
+      <c r="N153" s="7">
         <f>N138/$AD$138</f>
         <v/>
       </c>
-      <c r="O152" s="7">
+      <c r="O153" s="7">
         <f>O138/$AD$138</f>
         <v/>
       </c>
-      <c r="P152" s="7">
+      <c r="P153" s="7">
         <f>P138/$AD$138</f>
         <v/>
       </c>
-      <c r="Q152" s="7">
+      <c r="Q153" s="7">
         <f>Q138/$AD$138</f>
         <v/>
       </c>
-      <c r="R152" s="7">
+      <c r="R153" s="7">
         <f>R138/$AD$138</f>
         <v/>
       </c>
-      <c r="S152" s="7">
+      <c r="S153" s="7">
         <f>S138/$AD$138</f>
         <v/>
       </c>
-      <c r="T152" s="7">
+      <c r="T153" s="7">
         <f>T138/$AD$138</f>
         <v/>
       </c>
-      <c r="U152" s="7">
+      <c r="U153" s="7">
         <f>U138/$AD$138</f>
         <v/>
       </c>
-      <c r="V152" s="7">
+      <c r="V153" s="7">
         <f>V138/$AD$138</f>
         <v/>
       </c>
-      <c r="W152" s="7">
+      <c r="W153" s="7">
         <f>W138/$AD$138</f>
         <v/>
       </c>
-      <c r="X152" s="7">
+      <c r="X153" s="7">
         <f>X138/$AD$138</f>
         <v/>
       </c>
-      <c r="Y152" s="7">
+      <c r="Y153" s="7">
         <f>Y138/$AD$138</f>
         <v/>
       </c>
-      <c r="Z152" s="7">
+      <c r="Z153" s="7">
         <f>Z138/$AD$138</f>
         <v/>
       </c>
-      <c r="AA152" s="7">
+      <c r="AA153" s="7">
         <f>AA138/$AD$138</f>
         <v/>
       </c>
-      <c r="AB152" s="7" t="n"/>
-      <c r="AC152" s="7" t="n"/>
-      <c r="AD152">
+      <c r="AB153" s="7" t="n"/>
+      <c r="AC153" s="7" t="n"/>
+      <c r="AD153">
         <f>COUNT(A3:A80)</f>
         <v/>
       </c>
-      <c r="AG152">
+      <c r="AG153">
         <f>IF(AF139,#REF!,"")</f>
         <v/>
       </c>
-      <c r="AH152">
+      <c r="AH153">
         <f>IF(W139,#REF!,"")</f>
         <v/>
       </c>
-      <c r="AI152">
+      <c r="AI153">
         <f>IF(Y139,#REF!,"")</f>
         <v/>
       </c>
-      <c r="AJ152">
+      <c r="AJ153">
         <f>IF(AE139,#REF!,"")</f>
         <v/>
       </c>
